--- a/Daily challenge drafts.xlsx
+++ b/Daily challenge drafts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kurtl\Desktop\statstreaks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92A42396-7466-4534-A1F0-5C54A7C30CE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E5292DF-2B99-48E4-A0DA-3DB73760F799}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{09488A7D-DFB6-4DD5-964F-0B9C4180CBFA}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="10170" xr2:uid="{09488A7D-DFB6-4DD5-964F-0B9C4180CBFA}"/>
   </bookViews>
   <sheets>
     <sheet name="Mine" sheetId="3" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="393">
   <si>
     <t>#</t>
   </si>
@@ -1161,6 +1161,63 @@
   </si>
   <si>
     <t>Roma/Lazio 0 Stadio Olimpico - 70,634</t>
+  </si>
+  <si>
+    <t>WC26 Host countries</t>
+  </si>
+  <si>
+    <t>Brazil</t>
+  </si>
+  <si>
+    <t>Argentina</t>
+  </si>
+  <si>
+    <t>Germany</t>
+  </si>
+  <si>
+    <t>Belgium</t>
+  </si>
+  <si>
+    <t>Croatia</t>
+  </si>
+  <si>
+    <t>Czechia</t>
+  </si>
+  <si>
+    <t>Scotland</t>
+  </si>
+  <si>
+    <t>Netherlands</t>
+  </si>
+  <si>
+    <t>Sweden</t>
+  </si>
+  <si>
+    <t>Spain</t>
+  </si>
+  <si>
+    <t>Uruguay</t>
+  </si>
+  <si>
+    <t>France</t>
+  </si>
+  <si>
+    <t>Senegal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portugal </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colombia </t>
+  </si>
+  <si>
+    <t>England</t>
+  </si>
+  <si>
+    <t>Turkey</t>
+  </si>
+  <si>
+    <t>Ivory Coast</t>
   </si>
 </sst>
 </file>
@@ -1237,10 +1294,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6900B876-E2B4-49A6-830A-971694437239}" name="Table1" displayName="Table1" ref="B2:P92" totalsRowShown="0">
-  <autoFilter ref="B2:P92" xr:uid="{6900B876-E2B4-49A6-830A-971694437239}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6900B876-E2B4-49A6-830A-971694437239}" name="Table1" displayName="Table1" ref="B2:P76" totalsRowShown="0">
+  <autoFilter ref="B2:P76" xr:uid="{6900B876-E2B4-49A6-830A-971694437239}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:P32">
-    <sortCondition ref="B2:B92"/>
+    <sortCondition ref="B2:B32"/>
   </sortState>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{B2E13536-26C2-417A-891A-410A021F4570}" name="#"/>
@@ -1580,7 +1637,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4D10FEC-F30E-46F2-B39D-480DD703DE99}">
-  <dimension ref="B2:P96"/>
+  <dimension ref="B2:P76"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="7.54296875" bestFit="1" customWidth="1"/>
@@ -3038,311 +3095,619 @@
         <v>364</v>
       </c>
     </row>
-    <row r="33" spans="2:2" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B33">
         <v>31</v>
       </c>
-    </row>
-    <row r="34" spans="2:2" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C33" t="s">
+        <v>271</v>
+      </c>
+      <c r="D33" t="s">
+        <v>14</v>
+      </c>
+      <c r="E33" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B34">
         <v>32</v>
       </c>
-    </row>
-    <row r="35" spans="2:2" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C34" t="s">
+        <v>271</v>
+      </c>
+      <c r="D34" t="s">
+        <v>237</v>
+      </c>
+      <c r="E34" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B35">
         <v>33</v>
       </c>
-    </row>
-    <row r="36" spans="2:2" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C35" t="s">
+        <v>271</v>
+      </c>
+      <c r="D35" t="s">
+        <v>14</v>
+      </c>
+      <c r="E35" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="36" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B36">
         <v>34</v>
       </c>
-    </row>
-    <row r="37" spans="2:2" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C36" t="s">
+        <v>271</v>
+      </c>
+      <c r="D36" t="s">
+        <v>237</v>
+      </c>
+      <c r="E36" t="s">
+        <v>380</v>
+      </c>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="K36" s="1"/>
+      <c r="L36" s="1"/>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B37">
         <v>35</v>
       </c>
-    </row>
-    <row r="38" spans="2:2" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C37" t="s">
+        <v>271</v>
+      </c>
+      <c r="D37" t="s">
+        <v>14</v>
+      </c>
+      <c r="E37" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="38" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B38">
         <v>36</v>
       </c>
-    </row>
-    <row r="39" spans="2:2" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C38" t="s">
+        <v>271</v>
+      </c>
+      <c r="D38" t="s">
+        <v>237</v>
+      </c>
+      <c r="E38" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B39">
         <v>37</v>
       </c>
-    </row>
-    <row r="40" spans="2:2" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C39" t="s">
+        <v>271</v>
+      </c>
+      <c r="D39" t="s">
+        <v>14</v>
+      </c>
+      <c r="E39" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B40">
         <v>38</v>
       </c>
-    </row>
-    <row r="41" spans="2:2" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C40" t="s">
+        <v>271</v>
+      </c>
+      <c r="D40" t="s">
+        <v>237</v>
+      </c>
+      <c r="E40" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B41">
         <v>39</v>
       </c>
-    </row>
-    <row r="42" spans="2:2" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C41" t="s">
+        <v>271</v>
+      </c>
+      <c r="D41" t="s">
+        <v>14</v>
+      </c>
+      <c r="E41" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B42">
         <v>40</v>
       </c>
-    </row>
-    <row r="43" spans="2:2" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C42" t="s">
+        <v>271</v>
+      </c>
+      <c r="D42" t="s">
+        <v>237</v>
+      </c>
+      <c r="E42" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B43">
         <v>41</v>
       </c>
-    </row>
-    <row r="44" spans="2:2" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C43" t="s">
+        <v>271</v>
+      </c>
+      <c r="D43" t="s">
+        <v>14</v>
+      </c>
+      <c r="E43" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B44">
         <v>42</v>
       </c>
-    </row>
-    <row r="45" spans="2:2" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C44" t="s">
+        <v>271</v>
+      </c>
+      <c r="D44" t="s">
+        <v>237</v>
+      </c>
+      <c r="E44" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B45">
         <v>43</v>
       </c>
-    </row>
-    <row r="46" spans="2:2" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C45" t="s">
+        <v>271</v>
+      </c>
+      <c r="D45" t="s">
+        <v>14</v>
+      </c>
+      <c r="E45" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B46">
         <v>44</v>
       </c>
-    </row>
-    <row r="47" spans="2:2" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C46" t="s">
+        <v>271</v>
+      </c>
+      <c r="D46" t="s">
+        <v>237</v>
+      </c>
+      <c r="E46" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B47">
         <v>45</v>
       </c>
-    </row>
-    <row r="48" spans="2:2" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C47" t="s">
+        <v>271</v>
+      </c>
+      <c r="D47" t="s">
+        <v>14</v>
+      </c>
+      <c r="E47" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B48">
         <v>46</v>
       </c>
-    </row>
-    <row r="49" spans="2:2" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C48" t="s">
+        <v>271</v>
+      </c>
+      <c r="D48" t="s">
+        <v>237</v>
+      </c>
+      <c r="E48" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="49" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B49">
         <v>47</v>
       </c>
-    </row>
-    <row r="50" spans="2:2" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C49" t="s">
+        <v>271</v>
+      </c>
+      <c r="D49" t="s">
+        <v>14</v>
+      </c>
+      <c r="E49" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="50" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B50">
         <v>48</v>
       </c>
-    </row>
-    <row r="51" spans="2:2" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C50" t="s">
+        <v>271</v>
+      </c>
+      <c r="D50" t="s">
+        <v>237</v>
+      </c>
+      <c r="E50" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="51" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B51">
         <v>49</v>
       </c>
-    </row>
-    <row r="52" spans="2:2" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C51" t="s">
+        <v>271</v>
+      </c>
+      <c r="D51" t="s">
+        <v>14</v>
+      </c>
+      <c r="E51" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="52" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B52">
         <v>50</v>
       </c>
-    </row>
-    <row r="53" spans="2:2" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C52" t="s">
+        <v>271</v>
+      </c>
+      <c r="D52" t="s">
+        <v>237</v>
+      </c>
+      <c r="E52" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="53" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B53">
         <v>51</v>
       </c>
-    </row>
-    <row r="54" spans="2:2" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C53" t="s">
+        <v>271</v>
+      </c>
+      <c r="D53" t="s">
+        <v>14</v>
+      </c>
+      <c r="E53" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="54" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B54">
         <v>52</v>
       </c>
-    </row>
-    <row r="55" spans="2:2" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C54" t="s">
+        <v>271</v>
+      </c>
+      <c r="D54" t="s">
+        <v>237</v>
+      </c>
+      <c r="E54" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="55" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B55">
         <v>53</v>
       </c>
-    </row>
-    <row r="56" spans="2:2" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C55" t="s">
+        <v>271</v>
+      </c>
+      <c r="D55" t="s">
+        <v>14</v>
+      </c>
+      <c r="E55" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="56" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B56">
         <v>54</v>
       </c>
-    </row>
-    <row r="57" spans="2:2" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C56" t="s">
+        <v>271</v>
+      </c>
+      <c r="D56" t="s">
+        <v>237</v>
+      </c>
+      <c r="E56" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="57" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B57">
         <v>55</v>
       </c>
-    </row>
-    <row r="58" spans="2:2" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C57" t="s">
+        <v>271</v>
+      </c>
+      <c r="D57" t="s">
+        <v>14</v>
+      </c>
+      <c r="E57" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="58" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B58">
         <v>56</v>
       </c>
-    </row>
-    <row r="59" spans="2:2" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C58" t="s">
+        <v>271</v>
+      </c>
+      <c r="D58" t="s">
+        <v>237</v>
+      </c>
+      <c r="E58" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="59" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B59">
         <v>57</v>
       </c>
-    </row>
-    <row r="60" spans="2:2" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C59" t="s">
+        <v>271</v>
+      </c>
+      <c r="D59" t="s">
+        <v>14</v>
+      </c>
+      <c r="E59" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="60" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B60">
         <v>58</v>
       </c>
-    </row>
-    <row r="61" spans="2:2" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C60" t="s">
+        <v>271</v>
+      </c>
+      <c r="D60" t="s">
+        <v>237</v>
+      </c>
+      <c r="E60" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="61" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B61">
         <v>59</v>
       </c>
-    </row>
-    <row r="62" spans="2:2" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C61" t="s">
+        <v>271</v>
+      </c>
+      <c r="D61" t="s">
+        <v>14</v>
+      </c>
+      <c r="E61" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="62" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B62">
         <v>60</v>
       </c>
-    </row>
-    <row r="63" spans="2:2" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C62" t="s">
+        <v>271</v>
+      </c>
+      <c r="D62" t="s">
+        <v>237</v>
+      </c>
+      <c r="E62" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="63" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B63">
         <v>61</v>
       </c>
-    </row>
-    <row r="64" spans="2:2" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C63" t="s">
+        <v>271</v>
+      </c>
+      <c r="D63" t="s">
+        <v>14</v>
+      </c>
+      <c r="E63" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="64" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B64">
         <v>62</v>
       </c>
-    </row>
-    <row r="65" spans="2:2" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C64" t="s">
+        <v>271</v>
+      </c>
+      <c r="D64" t="s">
+        <v>237</v>
+      </c>
+      <c r="E64" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="65" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B65">
         <v>63</v>
       </c>
-    </row>
-    <row r="66" spans="2:2" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C65" t="s">
+        <v>271</v>
+      </c>
+      <c r="D65" t="s">
+        <v>14</v>
+      </c>
+      <c r="E65" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="66" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B66">
         <v>64</v>
       </c>
-    </row>
-    <row r="67" spans="2:2" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C66" t="s">
+        <v>271</v>
+      </c>
+      <c r="D66" t="s">
+        <v>237</v>
+      </c>
+      <c r="E66" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="67" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B67">
         <v>65</v>
       </c>
-    </row>
-    <row r="68" spans="2:2" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C67" t="s">
+        <v>271</v>
+      </c>
+      <c r="D67" t="s">
+        <v>14</v>
+      </c>
+      <c r="E67" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="68" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B68">
         <v>66</v>
       </c>
-    </row>
-    <row r="69" spans="2:2" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C68" t="s">
+        <v>271</v>
+      </c>
+      <c r="D68" t="s">
+        <v>237</v>
+      </c>
+      <c r="E68" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="69" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B69">
         <v>67</v>
       </c>
-    </row>
-    <row r="70" spans="2:2" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C69" t="s">
+        <v>271</v>
+      </c>
+      <c r="D69" t="s">
+        <v>14</v>
+      </c>
+      <c r="E69" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="70" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B70">
         <v>68</v>
       </c>
-    </row>
-    <row r="71" spans="2:2" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C70" t="s">
+        <v>271</v>
+      </c>
+      <c r="D70" t="s">
+        <v>237</v>
+      </c>
+      <c r="E70" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="71" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B71">
         <v>69</v>
       </c>
-    </row>
-    <row r="72" spans="2:2" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C71" t="s">
+        <v>271</v>
+      </c>
+      <c r="D71" t="s">
+        <v>14</v>
+      </c>
+      <c r="E71" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="72" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B72">
         <v>70</v>
       </c>
-    </row>
-    <row r="73" spans="2:2" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C72" t="s">
+        <v>271</v>
+      </c>
+      <c r="D72" t="s">
+        <v>237</v>
+      </c>
+      <c r="E72" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="73" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B73">
         <v>71</v>
       </c>
-    </row>
-    <row r="74" spans="2:2" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C73" t="s">
+        <v>271</v>
+      </c>
+      <c r="D73" t="s">
+        <v>14</v>
+      </c>
+      <c r="E73" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="74" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B74">
         <v>72</v>
       </c>
-    </row>
-    <row r="75" spans="2:2" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C74" t="s">
+        <v>271</v>
+      </c>
+      <c r="D74" t="s">
+        <v>237</v>
+      </c>
+      <c r="E74" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="75" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B75">
         <v>73</v>
       </c>
-    </row>
-    <row r="76" spans="2:2" hidden="1" x14ac:dyDescent="0.35">
+      <c r="C75" t="s">
+        <v>199</v>
+      </c>
+      <c r="D75" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="76" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B76">
         <v>74</v>
       </c>
-    </row>
-    <row r="77" spans="2:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B77">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="78" spans="2:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B78">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="79" spans="2:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B79">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="80" spans="2:2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B80">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="81" spans="2:12" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B81">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="82" spans="2:12" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B82">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="83" spans="2:12" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B83">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="84" spans="2:12" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B84">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="85" spans="2:12" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B85">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="86" spans="2:12" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B86">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="87" spans="2:12" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B87">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="88" spans="2:12" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B88">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="89" spans="2:12" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B89">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="90" spans="2:12" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B90">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="91" spans="2:12" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B91">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="92" spans="2:12" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B92">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="96" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="G96" s="1"/>
-      <c r="H96" s="1"/>
-      <c r="K96" s="1"/>
-      <c r="L96" s="1"/>
+      <c r="C76" t="s">
+        <v>199</v>
+      </c>
+      <c r="D76" t="s">
+        <v>237</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Daily challenge drafts.xlsx
+++ b/Daily challenge drafts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kurtl\Desktop\statstreaks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E5292DF-2B99-48E4-A0DA-3DB73760F799}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01E8FB4C-49AB-4D47-8A2D-7772D36FC0CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="10170" xr2:uid="{09488A7D-DFB6-4DD5-964F-0B9C4180CBFA}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{09488A7D-DFB6-4DD5-964F-0B9C4180CBFA}"/>
   </bookViews>
   <sheets>
     <sheet name="Mine" sheetId="3" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="985" uniqueCount="605">
   <si>
     <t>#</t>
   </si>
@@ -137,9 +137,6 @@
     <t>David Silva - 60</t>
   </si>
   <si>
-    <t>Rodri  - 22</t>
-  </si>
-  <si>
     <t>Xabi Alonso - 14</t>
   </si>
   <si>
@@ -224,9 +221,6 @@
     <t>Timo Werner - 12</t>
   </si>
   <si>
-    <t>Emre Can  - 10</t>
-  </si>
-  <si>
     <t>Mesut Ozil - 33</t>
   </si>
   <si>
@@ -239,9 +233,6 @@
     <t>Robert Huth - 21</t>
   </si>
   <si>
-    <t>Michael Ballack  -17</t>
-  </si>
-  <si>
     <t>Dietmar Hamann - 12</t>
   </si>
   <si>
@@ -542,18 +533,6 @@
     <t>El Hadj Diouf - 28</t>
   </si>
   <si>
-    <t>Pierre-Emerick Aubameyang  - 69</t>
-  </si>
-  <si>
-    <t>Kelechi Iheanacho  - 42</t>
-  </si>
-  <si>
-    <t>Didier Drogba  - 104</t>
-  </si>
-  <si>
-    <t>Nwankwo Kanu  - 54</t>
-  </si>
-  <si>
     <t>Demba Ba - 43</t>
   </si>
   <si>
@@ -614,9 +593,6 @@
     <t>Juventus - 2</t>
   </si>
   <si>
-    <t>Barecelona - 5</t>
-  </si>
-  <si>
     <t>Borussia Dortmund - 1</t>
   </si>
   <si>
@@ -635,9 +611,6 @@
     <t>AC Milan - 7</t>
   </si>
   <si>
-    <t xml:space="preserve">Ajax -4 </t>
-  </si>
-  <si>
     <t>World Cup</t>
   </si>
   <si>
@@ -707,9 +680,6 @@
     <t>David Beckham - 80</t>
   </si>
   <si>
-    <t>Paul Scholes  - 55</t>
-  </si>
-  <si>
     <t>Peter Crouch - 57</t>
   </si>
   <si>
@@ -821,189 +791,24 @@
     <t>Dwight Yorke - 375</t>
   </si>
   <si>
-    <t xml:space="preserve">Cristiano Ronaldo – 226 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Luis Suárez – 132 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Luka Modrić – 176 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Laurent Blanc – 97 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Xavi – 133 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Gareth Bale – 111 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Robert Lewandowski – 153 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Ashley Cole – 107 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Fabio Cannavaro – 136 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Kevin Kilbane – 110 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Gianluigi Buffon – 176</t>
-  </si>
-  <si>
     <t>International</t>
   </si>
   <si>
-    <t xml:space="preserve">Lionel Messi – 198 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Pavel Nedvěd – 91 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Sergio Ramos – 180 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Hakan Şükür – 112 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Wesley Sneijder – 134 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Bobby Charlton – 106 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Javier Mascherano – 147 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Nani – 112 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Leonardo Bonucci – 121 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Thierry Henry – 123 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Paolo Maldini – 126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iker Casillas – 167 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Andrés Iniesta – 131 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Lothar Matthäus – 150 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Henrik Larsson – 106 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Miroslav Klose – 137 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Xabi Alonso – 114 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Lilian Thuram – 142</t>
-  </si>
-  <si>
     <t>Sergia Aguero - 101</t>
   </si>
   <si>
-    <t xml:space="preserve">Igor Akinfeev – 111 </t>
-  </si>
-  <si>
     <t>Brian Laudrup - 82</t>
   </si>
   <si>
     <t>George Best - 37</t>
   </si>
   <si>
-    <t xml:space="preserve"> Zlatan Ibrahimović – 62 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Edinson Cavani – 58 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Gerd Müller – 68 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Robert Lewandowski – 82 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Gary Lineker – 48 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Michael Owen – 40 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Pelé – 77</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Miroslav Klose – 71 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Henrik Larsson – 37 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Luis Suárez – 68 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Eden Hazard – 33 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Romelu Lukaku – 85 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> David Villa – 59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Neymar – 79 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Patrick Kluivert – 40 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Karim Benzema – 37 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Dries Mertens – 21 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Fernando Torres – 38 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Robin van Persie – 50 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Arjen Robben – 37 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Olivier Giroud – 57 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Nani – 24 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Thierry Henry – 51</t>
-  </si>
-  <si>
     <t>Eusebio - 41</t>
   </si>
   <si>
-    <t>Diego Forlan -  36</t>
-  </si>
-  <si>
     <t>Ruud van Nistlerooy - 35</t>
   </si>
   <si>
-    <t xml:space="preserve">Gabriel Batistuta – 56 </t>
-  </si>
-  <si>
     <t>Xavi - 12</t>
   </si>
   <si>
@@ -1019,75 +824,6 @@
     <t>Robbie Keane - 68</t>
   </si>
   <si>
-    <t xml:space="preserve">Raul – 44 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Harry Kane – 2015/16 – 25 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Harry Kane – 2016/17 – 29 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Mohamed Salah – 2017/18 – 32 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Jamie Vardy – 2019/20 – 23 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Erling Haaland – 2022/23 – 36 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Erling Haaland – 2023/24 – 27 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Mohamed Salah – 2024/25 – 29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sergio Agüero – 2014/15 – 26 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thierry Henry – 2003/04 – 30 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Thierry Henry – 2004/05 – 25 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Thierry Henry – 2005/06 – 27 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Didier Drogba – 2006/07 – 20 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Cristiano Ronaldo – 2007/08 – 31 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Nicolas Anelka – 2008/09 – 19 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Didier Drogba – 2009/10 – 29 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Robin van Persie – 2011/12 – 30 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Robin van Persie – 2012/13 – 26 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Luis Suárez – 2013/14 – 31</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Kevin Phillips – 1999/00 – 30 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Jimmy Floyd Hasselbaink – 2000/01 – 23 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Thierry Henry – 2001/02 – 24 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Ruud van Nistelrooy – 2002/03 – 25</t>
-  </si>
-  <si>
     <t xml:space="preserve">Golden boot </t>
   </si>
   <si>
@@ -1097,57 +833,6 @@
     <t>Stadium capacity</t>
   </si>
   <si>
-    <t xml:space="preserve">Manchester United – Old Trafford – 74,879 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Tottenham Hotspur – Tottenham Hotspur Stadium – 62,850 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Bournemouth – Vitality Stadium – 11,329 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> West Ham – London Stadium – 62,500 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Leeds United – Elland Road – 37,792 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Arsenal – Emirates Stadium – 60,704 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Wolves – Molineux – 32,050 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Aston Villa – Villa Park – 42,749 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Fulham – Craven Cottage – 25,700 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Manchester City – Etihad Stadium – 55,017 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Liverpool – Anfield – 53,394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barcelona – Camp Nou – 99,354 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Juventus – Allianz Stadium – 41,507 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Chelsea – Stamford Bridge – 40,341 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> AC Milan / Inter – San Siro – 80,018 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Rangers – Ibrox Stadium – 50,817 </t>
-  </si>
-  <si>
-    <t>England  - Wembley - 90,000</t>
-  </si>
-  <si>
     <t>Real Madrid - Bernabeu - 83,186</t>
   </si>
   <si>
@@ -1157,9 +842,6 @@
     <t>Young Boys - Wankdorf - 31,783</t>
   </si>
   <si>
-    <t xml:space="preserve"> Besiktas– Vodafone Park – 42,590 </t>
-  </si>
-  <si>
     <t>Roma/Lazio 0 Stadio Olimpico - 70,634</t>
   </si>
   <si>
@@ -1214,17 +896,971 @@
     <t>England</t>
   </si>
   <si>
-    <t>Turkey</t>
-  </si>
-  <si>
     <t>Ivory Coast</t>
+  </si>
+  <si>
+    <t>UCL</t>
+  </si>
+  <si>
+    <t>Cristiano Ronaldo - 140</t>
+  </si>
+  <si>
+    <t>Thierry Henry - 50</t>
+  </si>
+  <si>
+    <t>Alessandro Del Piero - 42</t>
+  </si>
+  <si>
+    <t>Eden Hazard - 10</t>
+  </si>
+  <si>
+    <t>Luis Suarex - 27</t>
+  </si>
+  <si>
+    <t>Michael Owen - 11</t>
+  </si>
+  <si>
+    <t>Robin van Persie - 25</t>
+  </si>
+  <si>
+    <t>Zlatan Ibrahimović - 124</t>
+  </si>
+  <si>
+    <t>Frank Lampard - 105</t>
+  </si>
+  <si>
+    <t>David Beckham - 98</t>
+  </si>
+  <si>
+    <t>Rio Ferdinand - 85</t>
+  </si>
+  <si>
+    <t>Deco - 89</t>
+  </si>
+  <si>
+    <t>Claude Makelele - 78</t>
+  </si>
+  <si>
+    <t>Ronaldo - 40</t>
+  </si>
+  <si>
+    <t>Ronaldinho - 47</t>
+  </si>
+  <si>
+    <t>Zinedine Zidane - 80</t>
+  </si>
+  <si>
+    <t>Francesco Totti - 57</t>
+  </si>
+  <si>
+    <t>Dimitar Berbatov - 33</t>
+  </si>
+  <si>
+    <t>Carlos Tevez - 73</t>
+  </si>
+  <si>
+    <t>Edison Cavani - 35</t>
+  </si>
+  <si>
+    <t>Petr Cech - 124</t>
+  </si>
+  <si>
+    <t>Pavel Nedved - 91</t>
+  </si>
+  <si>
+    <t>Diego Godín - 161</t>
+  </si>
+  <si>
+    <t>Gustavo Poyet - 26</t>
+  </si>
+  <si>
+    <t>Sebastian Coates - 51</t>
+  </si>
+  <si>
+    <t>Jonas Olsson - 25</t>
+  </si>
+  <si>
+    <t>Marcus Allback - 74</t>
+  </si>
+  <si>
+    <t>Divock Origi - 32</t>
+  </si>
+  <si>
+    <t>Kevin Mirallas - 60</t>
+  </si>
+  <si>
+    <t>Edouard Mendy - 36</t>
+  </si>
+  <si>
+    <t>Barcelona - 5</t>
+  </si>
+  <si>
+    <t>Juan Pablo Angel - 33</t>
+  </si>
+  <si>
+    <t>Dejan Lovren - 78</t>
+  </si>
+  <si>
+    <t>Julio Cesar - 87</t>
+  </si>
+  <si>
+    <t>Adriano - 48</t>
+  </si>
+  <si>
+    <t>Sergio Aguero - 101</t>
+  </si>
+  <si>
+    <t>Hernan Crespo - 64</t>
+  </si>
+  <si>
+    <t>Diego Simeone - 106</t>
+  </si>
+  <si>
+    <t>Angel Di Maria - 140</t>
+  </si>
+  <si>
+    <t>James McFadden - 48</t>
+  </si>
+  <si>
+    <t>Ally McCoist - 61</t>
+  </si>
+  <si>
+    <t>Gary McAllister -57</t>
+  </si>
+  <si>
+    <t>Kenny Miller - 69</t>
+  </si>
+  <si>
+    <t>Cristiano Ronaldo – 226</t>
+  </si>
+  <si>
+    <t>Luis Suárez – 132</t>
+  </si>
+  <si>
+    <t>Ashley Cole – 107</t>
+  </si>
+  <si>
+    <t>Laurent Blanc – 97</t>
+  </si>
+  <si>
+    <t>Luka Modrić – 176</t>
+  </si>
+  <si>
+    <t>Xavi – 133</t>
+  </si>
+  <si>
+    <t>Gianluigi Buffon – 176</t>
+  </si>
+  <si>
+    <t>Robert Lewandowski – 153</t>
+  </si>
+  <si>
+    <t>Fabio Cannavaro – 136</t>
+  </si>
+  <si>
+    <t>Kevin Kilbane – 110</t>
+  </si>
+  <si>
+    <t>Gareth Bale – 111</t>
+  </si>
+  <si>
+    <t>Lionel Messi – 198</t>
+  </si>
+  <si>
+    <t>Javier Mascherano – 147</t>
+  </si>
+  <si>
+    <t>Hakan Şükür – 112</t>
+  </si>
+  <si>
+    <t>Pavel Nedvěd – 91</t>
+  </si>
+  <si>
+    <t>Sergio Ramos – 180</t>
+  </si>
+  <si>
+    <t>Leonardo Bonucci – 121</t>
+  </si>
+  <si>
+    <t>Bobby Charlton – 106</t>
+  </si>
+  <si>
+    <t>Nani – 112</t>
+  </si>
+  <si>
+    <t>Thierry Henry – 123</t>
+  </si>
+  <si>
+    <t>Wesley Sneijder – 134</t>
+  </si>
+  <si>
+    <t>Paolo Maldini – 126</t>
+  </si>
+  <si>
+    <t>Iker Casillas – 167</t>
+  </si>
+  <si>
+    <t>Andrés Iniesta – 131</t>
+  </si>
+  <si>
+    <t>Lothar Matthäus – 150</t>
+  </si>
+  <si>
+    <t>Igor Akinfeev – 111</t>
+  </si>
+  <si>
+    <t>Henrik Larsson – 106</t>
+  </si>
+  <si>
+    <t>Xabi Alonso – 114</t>
+  </si>
+  <si>
+    <t>Miroslav Klose – 137</t>
+  </si>
+  <si>
+    <t>Lilian Thuram – 142</t>
+  </si>
+  <si>
+    <t>Atiba Hutchinson (Canada) – 104</t>
+  </si>
+  <si>
+    <t>Rafael Márquez (Mexico)– 147</t>
+  </si>
+  <si>
+    <t>Paul Stalteri (Canada) – 84</t>
+  </si>
+  <si>
+    <t>Landon Donovan (USA)– 157</t>
+  </si>
+  <si>
+    <t>Tomasz Radzinski (Canada) – 46</t>
+  </si>
+  <si>
+    <t>Guillermo Ochoa (Mexico)– 150</t>
+  </si>
+  <si>
+    <t>Andres Guardado (Mexico)– 179</t>
+  </si>
+  <si>
+    <t>Javier Hernández (Mexico) – 109</t>
+  </si>
+  <si>
+    <t>Luis Hernandez (Mexico)– 85</t>
+  </si>
+  <si>
+    <t>Clint Dempsey (USA)– 141</t>
+  </si>
+  <si>
+    <t>Michael Bradley (USA) – 151</t>
+  </si>
+  <si>
+    <t>Vladimir Smicer - 81</t>
+  </si>
+  <si>
+    <t>Patrik Berger - 44</t>
+  </si>
+  <si>
+    <t>Antonin Panenka - 59</t>
+  </si>
+  <si>
+    <t>Karel Poborsky - 118</t>
+  </si>
+  <si>
+    <t>Jan Koller - 91</t>
+  </si>
+  <si>
+    <t>Vladimir Darida - 76</t>
+  </si>
+  <si>
+    <t>Tomas Rosicky - 105</t>
+  </si>
+  <si>
+    <t>Jaroslav Plasil - 103</t>
+  </si>
+  <si>
+    <t>Milan Baros - 93</t>
+  </si>
+  <si>
+    <t>Zico – 71</t>
+  </si>
+  <si>
+    <t>Roberto Carlos – 125</t>
+  </si>
+  <si>
+    <t>Cafu – 142</t>
+  </si>
+  <si>
+    <t>Kaka – 92</t>
+  </si>
+  <si>
+    <t>Rivaldo – 74</t>
+  </si>
+  <si>
+    <t>Ronaldinho – 97</t>
+  </si>
+  <si>
+    <t>Romário – 70</t>
+  </si>
+  <si>
+    <t>Ronaldo – 98</t>
+  </si>
+  <si>
+    <t>Pele – 92</t>
+  </si>
+  <si>
+    <t>Kenny Dalglish – 102</t>
+  </si>
+  <si>
+    <t>Darren Fletcher – 80</t>
+  </si>
+  <si>
+    <t>Paul Lambert – 40</t>
+  </si>
+  <si>
+    <t>Graeme Souness – 54</t>
+  </si>
+  <si>
+    <t>Archie Gemmill – 43</t>
+  </si>
+  <si>
+    <t>Denis Law – 55</t>
+  </si>
+  <si>
+    <t>Gordon Strachan – 50</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Max Gradel – 97</t>
+  </si>
+  <si>
+    <t>Cheick Tiote – 52</t>
+  </si>
+  <si>
+    <t>Didier Zokora – 123</t>
+  </si>
+  <si>
+    <t>Aruna Dindane – 62</t>
+  </si>
+  <si>
+    <t>Kolo Toure – 120</t>
+  </si>
+  <si>
+    <t>Yaya Toure – 102</t>
+  </si>
+  <si>
+    <t>Emmanuel Eboue – 79</t>
+  </si>
+  <si>
+    <t>Wilfried Bony – 52</t>
+  </si>
+  <si>
+    <t>Gervinho – 88</t>
+  </si>
+  <si>
+    <t>Salomon Kalou – 97</t>
+  </si>
+  <si>
+    <t>Didier Drogba – 105</t>
+  </si>
+  <si>
+    <t>Martin Dahlin – 60</t>
+  </si>
+  <si>
+    <t>Anders Svensson – 148</t>
+  </si>
+  <si>
+    <t>Jesper Blomqvist - 30</t>
+  </si>
+  <si>
+    <t>Zlatan Ibrahimović – 122</t>
+  </si>
+  <si>
+    <t>Patrik Andersson – 96</t>
+  </si>
+  <si>
+    <t>Olof Mellberg – 117</t>
+  </si>
+  <si>
+    <t>Sebastian Larsson – 133</t>
+  </si>
+  <si>
+    <t>Freddie Ljungberg – 75</t>
+  </si>
+  <si>
+    <t>Vincent Kompany – 89</t>
+  </si>
+  <si>
+    <t>Dries Mertens – 109</t>
+  </si>
+  <si>
+    <t>Eden Hazard – 126</t>
+  </si>
+  <si>
+    <t>Jan Vertonghen – 154</t>
+  </si>
+  <si>
+    <t>Romelu Lukaku – 114</t>
+  </si>
+  <si>
+    <t>Axel Witsel – 130</t>
+  </si>
+  <si>
+    <t>Toby Alderweireld – 127</t>
+  </si>
+  <si>
+    <t>Marouane Fellaini – 87</t>
+  </si>
+  <si>
+    <t>Mousa Dembélé – 82</t>
+  </si>
+  <si>
+    <t>Fernando Muslera - 139</t>
+  </si>
+  <si>
+    <t>Maxi Pereira - 125</t>
+  </si>
+  <si>
+    <t>Diego Forlan - 112</t>
+  </si>
+  <si>
+    <t>Luis Suarez - 143</t>
+  </si>
+  <si>
+    <t>Cristian Rodriguez - 116</t>
+  </si>
+  <si>
+    <t>Enzo Francescoli - 73</t>
+  </si>
+  <si>
+    <t>Edinson Cavani - 136</t>
+  </si>
+  <si>
+    <t>Diego Lugano - 95</t>
+  </si>
+  <si>
+    <t>Cheikhou Kouyaté – 86</t>
+  </si>
+  <si>
+    <t>Sadio Mané – 105</t>
+  </si>
+  <si>
+    <t>El Hadji Diouf – 69</t>
+  </si>
+  <si>
+    <t>Papa Bouba Diop – 63</t>
+  </si>
+  <si>
+    <t>Kalidou Koulibaly – 83</t>
+  </si>
+  <si>
+    <t>Idrissa Gana Gueye – 104</t>
+  </si>
+  <si>
+    <t>Moussa Sow – 50</t>
+  </si>
+  <si>
+    <t>Mame Biram Diouf – 47</t>
+  </si>
+  <si>
+    <t>Salif Diao – 39</t>
+  </si>
+  <si>
+    <t>Demba Ba – 22</t>
+  </si>
+  <si>
+    <t>Pablo Aimar – 52</t>
+  </si>
+  <si>
+    <t>Diego Maradona – 91</t>
+  </si>
+  <si>
+    <t>Juan Sebastián Verón – 73</t>
+  </si>
+  <si>
+    <t>Walter Samuel – 56</t>
+  </si>
+  <si>
+    <t>Carlos Tevez – 76</t>
+  </si>
+  <si>
+    <t>Gabriel Batistuta – 78</t>
+  </si>
+  <si>
+    <t>Abel Aguilar – 71</t>
+  </si>
+  <si>
+    <t>Faustino Asprilla – 57</t>
+  </si>
+  <si>
+    <t>Jackson Martínez – 40</t>
+  </si>
+  <si>
+    <t>Freddy Rincón – 84</t>
+  </si>
+  <si>
+    <t>David Ospina – 127</t>
+  </si>
+  <si>
+    <t>Juan Cuadrado – 116</t>
+  </si>
+  <si>
+    <t>Carlos Valderrama – 111</t>
+  </si>
+  <si>
+    <t>Mario Yepes – 102</t>
+  </si>
+  <si>
+    <t>James Rodríguez – 101</t>
+  </si>
+  <si>
+    <t>Radamel Falcao – 104</t>
+  </si>
+  <si>
+    <t>Stipe Pletikosa – 114</t>
+  </si>
+  <si>
+    <t>Darijo Srna – 134</t>
+  </si>
+  <si>
+    <t>Xavi - 151</t>
+  </si>
+  <si>
+    <t>Sergio Busquets - 129</t>
+  </si>
+  <si>
+    <t>Roberto Carlos - 120</t>
+  </si>
+  <si>
+    <t>Karim Benzema - 152</t>
+  </si>
+  <si>
+    <t>Sergio Ramos - 142</t>
+  </si>
+  <si>
+    <t>Cristiano Ronaldo - 183</t>
+  </si>
+  <si>
+    <t>Paolo Maldini - 135</t>
+  </si>
+  <si>
+    <t>Philipp Lahm - 112</t>
+  </si>
+  <si>
+    <t>Paul Scholes - 124</t>
+  </si>
+  <si>
+    <t>Clarence Seedorf - 125</t>
+  </si>
+  <si>
+    <t>Paul Scholes - 55</t>
+  </si>
+  <si>
+    <t>Manchester United – Old Trafford – 74,879</t>
+  </si>
+  <si>
+    <t>Tottenham Hotspur – Tottenham Hotspur Stadium – 62,850</t>
+  </si>
+  <si>
+    <t>Bournemouth – Vitality Stadium – 11,329</t>
+  </si>
+  <si>
+    <t>West Ham – London Stadium – 62,500</t>
+  </si>
+  <si>
+    <t>Leeds United – Elland Road – 37,792</t>
+  </si>
+  <si>
+    <t>Arsenal – Emirates Stadium – 60,704</t>
+  </si>
+  <si>
+    <t>Wolves – Molineux – 32,050</t>
+  </si>
+  <si>
+    <t>Fulham – Craven Cottage – 25,700</t>
+  </si>
+  <si>
+    <t>Aston Villa – Villa Park – 42,749</t>
+  </si>
+  <si>
+    <t>Manchester City – Etihad Stadium – 55,017</t>
+  </si>
+  <si>
+    <t>Liverpool – Anfield – 53,394</t>
+  </si>
+  <si>
+    <t>Barcelona – Camp Nou – 99,354</t>
+  </si>
+  <si>
+    <t>Rangers – Ibrox Stadium – 50,817</t>
+  </si>
+  <si>
+    <t>AC Milan / Inter – San Siro – 80,018</t>
+  </si>
+  <si>
+    <t>England - Wembley - 90,000</t>
+  </si>
+  <si>
+    <t>Besiktas– Vodafone Park – 42,590</t>
+  </si>
+  <si>
+    <t>Chelsea – Stamford Bridge – 40,341</t>
+  </si>
+  <si>
+    <t>Juventus – Allianz Stadium – 41,507</t>
+  </si>
+  <si>
+    <t>Emre Can - 10</t>
+  </si>
+  <si>
+    <t>Michael Ballack -17</t>
+  </si>
+  <si>
+    <t>Rodri - 22</t>
+  </si>
+  <si>
+    <t>Pierre-Emerick Aubameyang - 69</t>
+  </si>
+  <si>
+    <t>Kelechi Iheanacho - 42</t>
+  </si>
+  <si>
+    <t>Didier Drogba - 104</t>
+  </si>
+  <si>
+    <t>Nwankwo Kanu - 54</t>
+  </si>
+  <si>
+    <t>Dries Mertens – 21</t>
+  </si>
+  <si>
+    <t>Miroslav Klose – 71</t>
+  </si>
+  <si>
+    <t>Eden Hazard – 33</t>
+  </si>
+  <si>
+    <t>Robin van Persie – 50</t>
+  </si>
+  <si>
+    <t>Patrick Kluivert – 40</t>
+  </si>
+  <si>
+    <t>Karim Benzema – 37</t>
+  </si>
+  <si>
+    <t>Luis Suárez – 68</t>
+  </si>
+  <si>
+    <t>Gary Lineker – 48</t>
+  </si>
+  <si>
+    <t>Michael Owen – 40</t>
+  </si>
+  <si>
+    <t>Fernando Torres – 38</t>
+  </si>
+  <si>
+    <t>Neymar – 79</t>
+  </si>
+  <si>
+    <t>Henrik Larsson – 37</t>
+  </si>
+  <si>
+    <t>Robert Lewandowski – 82</t>
+  </si>
+  <si>
+    <t>Arjen Robben – 37</t>
+  </si>
+  <si>
+    <t>Gerd Müller – 68</t>
+  </si>
+  <si>
+    <t>David Villa – 59</t>
+  </si>
+  <si>
+    <t>Edinson Cavani – 58</t>
+  </si>
+  <si>
+    <t>Diego Forlan - 36</t>
+  </si>
+  <si>
+    <t>Gabriel Batistuta – 56</t>
+  </si>
+  <si>
+    <t>Romelu Lukaku – 85</t>
+  </si>
+  <si>
+    <t>Raul – 44</t>
+  </si>
+  <si>
+    <t>Nani – 24</t>
+  </si>
+  <si>
+    <t>Pelé – 77</t>
+  </si>
+  <si>
+    <t>Zlatan Ibrahimović – 62</t>
+  </si>
+  <si>
+    <t>Olivier Giroud – 57</t>
+  </si>
+  <si>
+    <t>Thierry Henry – 51</t>
+  </si>
+  <si>
+    <t>Robin van Persie – 2011/12 – 30</t>
+  </si>
+  <si>
+    <t>Robin van Persie – 2012/13 – 26</t>
+  </si>
+  <si>
+    <t>Luis Suárez – 2013/14 – 31</t>
+  </si>
+  <si>
+    <t>Sergio Agüero – 2014/15 – 26</t>
+  </si>
+  <si>
+    <t>Harry Kane – 2015/16 – 25</t>
+  </si>
+  <si>
+    <t>Harry Kane – 2016/17 – 29</t>
+  </si>
+  <si>
+    <t>Mohamed Salah – 2017/18 – 32</t>
+  </si>
+  <si>
+    <t>Jamie Vardy – 2019/20 – 23</t>
+  </si>
+  <si>
+    <t>Erling Haaland – 2022/23 – 36</t>
+  </si>
+  <si>
+    <t>Erling Haaland – 2023/24 – 27</t>
+  </si>
+  <si>
+    <t>Mohamed Salah – 2024/25 – 29</t>
+  </si>
+  <si>
+    <t>Kevin Phillips – 1999/00 – 30</t>
+  </si>
+  <si>
+    <t>Jimmy Floyd Hasselbaink – 2000/01 – 23</t>
+  </si>
+  <si>
+    <t>Thierry Henry – 2001/02 – 24</t>
+  </si>
+  <si>
+    <t>Ruud van Nistelrooy – 2002/03 – 25</t>
+  </si>
+  <si>
+    <t>Thierry Henry – 2003/04 – 30</t>
+  </si>
+  <si>
+    <t>Thierry Henry – 2004/05 – 25</t>
+  </si>
+  <si>
+    <t>Thierry Henry – 2005/06 – 27</t>
+  </si>
+  <si>
+    <t>Didier Drogba – 2006/07 – 20</t>
+  </si>
+  <si>
+    <t>Cristiano Ronaldo – 2007/08 – 31</t>
+  </si>
+  <si>
+    <t>Nicolas Anelka – 2008/09 – 19</t>
+  </si>
+  <si>
+    <t>Didier Drogba – 2009/10 – 29</t>
+  </si>
+  <si>
+    <t>Lionel Messi - 129</t>
+  </si>
+  <si>
+    <t>Neymar - 43</t>
+  </si>
+  <si>
+    <t>Karim Benzema - 90</t>
+  </si>
+  <si>
+    <t>Steven Gerrard - 21</t>
+  </si>
+  <si>
+    <t>Ruud van Nistelrooy - 56</t>
+  </si>
+  <si>
+    <t>Wayne Rooney - 30</t>
+  </si>
+  <si>
+    <t>Fernando Torres - 20</t>
+  </si>
+  <si>
+    <t>Roberto Carlos - 14</t>
+  </si>
+  <si>
+    <t>Andriy Shevchenko - 48</t>
+  </si>
+  <si>
+    <t>Sergio Agüero - 41</t>
+  </si>
+  <si>
+    <t>Raúl - 71</t>
+  </si>
+  <si>
+    <t>Didier Drogba - 44</t>
+  </si>
+  <si>
+    <t>Arjen Robben - 31</t>
+  </si>
+  <si>
+    <t>Samuel Eto'o - 30</t>
+  </si>
+  <si>
+    <t>Ajax -4</t>
+  </si>
+  <si>
+    <t>Jaap Stam -67</t>
+  </si>
+  <si>
+    <t>Mesut Ozil - 92</t>
+  </si>
+  <si>
+    <t>Mats Hummels - 78</t>
+  </si>
+  <si>
+    <t>Andre Schurrle - 57</t>
+  </si>
+  <si>
+    <t>Dennis Bergkamp – 79</t>
+  </si>
+  <si>
+    <t>Johan Cruyff – 48</t>
+  </si>
+  <si>
+    <t>Edwin van der Sar – 130</t>
+  </si>
+  <si>
+    <t>Ruud Gullit – 66</t>
+  </si>
+  <si>
+    <t>Marco van Basten – 58</t>
+  </si>
+  <si>
+    <t>Arjen Robben – 96</t>
+  </si>
+  <si>
+    <t>Edgar Davids – 74</t>
+  </si>
+  <si>
+    <t>Ruud van Nistelrooy – 70</t>
+  </si>
+  <si>
+    <t>Boudewijn Zenden – 54</t>
+  </si>
+  <si>
+    <t>Gerd Muller – 62</t>
+  </si>
+  <si>
+    <t>Lothar Matthaus – 150</t>
+  </si>
+  <si>
+    <t>Michael Ballack – 98</t>
+  </si>
+  <si>
+    <t>Rudi Voller – 90</t>
+  </si>
+  <si>
+    <t>Mario Gotze – 66</t>
+  </si>
+  <si>
+    <t>Franz Beckenbauer – 103</t>
+  </si>
+  <si>
+    <t>Sami Khedira - 77</t>
+  </si>
+  <si>
+    <t>Patrick Kluivert - 79</t>
+  </si>
+  <si>
+    <t>Luka ModriC – 166</t>
+  </si>
+  <si>
+    <t>Milan Rapaic – 49</t>
+  </si>
+  <si>
+    <t>Ivan Perisic – 129</t>
+  </si>
+  <si>
+    <t>Mario Mandzukic – 89</t>
+  </si>
+  <si>
+    <t>Vedran Corluka – 103</t>
+  </si>
+  <si>
+    <t>Ivan Rakitic – 106</t>
+  </si>
+  <si>
+    <t>Davor Suker – 69</t>
+  </si>
+  <si>
+    <t>Alen Boksic – 40</t>
+  </si>
+  <si>
+    <t>Finals</t>
+  </si>
+  <si>
+    <t>FA Cup</t>
+  </si>
+  <si>
+    <t>Manchester United</t>
+  </si>
+  <si>
+    <t>All time</t>
+  </si>
+  <si>
+    <t>Liverpool</t>
+  </si>
+  <si>
+    <t>Arsenal</t>
+  </si>
+  <si>
+    <t>Chelsea</t>
+  </si>
+  <si>
+    <t>Barcelona</t>
+  </si>
+  <si>
+    <t>Real Madrid</t>
+  </si>
+  <si>
+    <t>Bayern Munich</t>
+  </si>
+  <si>
+    <t>PSG</t>
+  </si>
+  <si>
+    <t>Manchester City</t>
+  </si>
+  <si>
+    <t>Tottenham Hotspur</t>
+  </si>
+  <si>
+    <t>Juventus</t>
+  </si>
+  <si>
+    <t>Womens international</t>
+  </si>
+  <si>
+    <t>Transfer fee</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1234,19 +1870,6 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1272,10 +1895,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1294,10 +1915,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6900B876-E2B4-49A6-830A-971694437239}" name="Table1" displayName="Table1" ref="B2:P76" totalsRowShown="0">
-  <autoFilter ref="B2:P76" xr:uid="{6900B876-E2B4-49A6-830A-971694437239}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:P32">
-    <sortCondition ref="B2:B32"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6900B876-E2B4-49A6-830A-971694437239}" name="Table1" displayName="Table1" ref="B2:P116" totalsRowShown="0">
+  <autoFilter ref="B2:P116" xr:uid="{6900B876-E2B4-49A6-830A-971694437239}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:P116">
+    <sortCondition ref="B2:B116"/>
   </sortState>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{B2E13536-26C2-417A-891A-410A021F4570}" name="#"/>
@@ -1637,13 +2258,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4D10FEC-F30E-46F2-B39D-480DD703DE99}">
-  <dimension ref="B2:P76"/>
+  <dimension ref="B2:T237"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="7.54296875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.26953125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="43" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="59.36328125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="40.81640625" bestFit="1" customWidth="1"/>
@@ -1661,7 +2282,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D2" t="s">
         <v>1</v>
@@ -1714,40 +2335,40 @@
         <v>14</v>
       </c>
       <c r="E3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F3" t="s">
+        <v>78</v>
+      </c>
+      <c r="G3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H3" t="s">
+        <v>83</v>
+      </c>
+      <c r="I3" t="s">
+        <v>84</v>
+      </c>
+      <c r="J3" t="s">
+        <v>82</v>
+      </c>
+      <c r="K3" t="s">
+        <v>88</v>
+      </c>
+      <c r="L3" t="s">
+        <v>81</v>
+      </c>
+      <c r="M3" t="s">
+        <v>86</v>
+      </c>
+      <c r="N3" t="s">
+        <v>87</v>
+      </c>
+      <c r="O3" t="s">
+        <v>79</v>
+      </c>
+      <c r="P3" t="s">
         <v>80</v>
-      </c>
-      <c r="F3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G3" t="s">
-        <v>88</v>
-      </c>
-      <c r="H3" t="s">
-        <v>86</v>
-      </c>
-      <c r="I3" t="s">
-        <v>87</v>
-      </c>
-      <c r="J3" t="s">
-        <v>85</v>
-      </c>
-      <c r="K3" t="s">
-        <v>91</v>
-      </c>
-      <c r="L3" t="s">
-        <v>84</v>
-      </c>
-      <c r="M3" t="s">
-        <v>89</v>
-      </c>
-      <c r="N3" t="s">
-        <v>90</v>
-      </c>
-      <c r="O3" t="s">
-        <v>82</v>
-      </c>
-      <c r="P3" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.35">
@@ -1764,37 +2385,37 @@
         <v>16</v>
       </c>
       <c r="F4" t="s">
+        <v>67</v>
+      </c>
+      <c r="G4" t="s">
+        <v>68</v>
+      </c>
+      <c r="H4" t="s">
+        <v>69</v>
+      </c>
+      <c r="I4" t="s">
         <v>70</v>
       </c>
-      <c r="G4" t="s">
+      <c r="J4" t="s">
+        <v>74</v>
+      </c>
+      <c r="K4" t="s">
+        <v>75</v>
+      </c>
+      <c r="L4" t="s">
         <v>71</v>
       </c>
-      <c r="H4" t="s">
+      <c r="M4" t="s">
         <v>72</v>
       </c>
-      <c r="I4" t="s">
+      <c r="N4" t="s">
+        <v>76</v>
+      </c>
+      <c r="O4" t="s">
         <v>73</v>
       </c>
-      <c r="J4" t="s">
-        <v>77</v>
-      </c>
-      <c r="K4" t="s">
-        <v>78</v>
-      </c>
-      <c r="L4" t="s">
-        <v>74</v>
-      </c>
-      <c r="M4" t="s">
-        <v>75</v>
-      </c>
-      <c r="N4" t="s">
-        <v>79</v>
-      </c>
-      <c r="O4" t="s">
-        <v>76</v>
-      </c>
       <c r="P4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.35">
@@ -1808,40 +2429,40 @@
         <v>14</v>
       </c>
       <c r="E5" t="s">
+        <v>122</v>
+      </c>
+      <c r="F5" t="s">
         <v>125</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
+        <v>124</v>
+      </c>
+      <c r="H5" t="s">
         <v>128</v>
       </c>
-      <c r="G5" t="s">
+      <c r="I5" t="s">
+        <v>126</v>
+      </c>
+      <c r="J5" t="s">
+        <v>129</v>
+      </c>
+      <c r="K5" t="s">
+        <v>130</v>
+      </c>
+      <c r="L5" t="s">
+        <v>131</v>
+      </c>
+      <c r="M5" t="s">
+        <v>132</v>
+      </c>
+      <c r="N5" t="s">
+        <v>133</v>
+      </c>
+      <c r="O5" t="s">
+        <v>123</v>
+      </c>
+      <c r="P5" t="s">
         <v>127</v>
-      </c>
-      <c r="H5" t="s">
-        <v>131</v>
-      </c>
-      <c r="I5" t="s">
-        <v>129</v>
-      </c>
-      <c r="J5" t="s">
-        <v>132</v>
-      </c>
-      <c r="K5" t="s">
-        <v>133</v>
-      </c>
-      <c r="L5" t="s">
-        <v>134</v>
-      </c>
-      <c r="M5" t="s">
-        <v>135</v>
-      </c>
-      <c r="N5" t="s">
-        <v>136</v>
-      </c>
-      <c r="O5" t="s">
-        <v>126</v>
-      </c>
-      <c r="P5" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.35">
@@ -1858,37 +2479,37 @@
         <v>17</v>
       </c>
       <c r="F6" t="s">
+        <v>57</v>
+      </c>
+      <c r="G6" t="s">
+        <v>490</v>
+      </c>
+      <c r="H6" t="s">
         <v>58</v>
       </c>
-      <c r="G6" t="s">
+      <c r="I6" t="s">
+        <v>59</v>
+      </c>
+      <c r="J6" t="s">
+        <v>65</v>
+      </c>
+      <c r="K6" t="s">
+        <v>60</v>
+      </c>
+      <c r="L6" t="s">
         <v>61</v>
       </c>
-      <c r="H6" t="s">
-        <v>59</v>
-      </c>
-      <c r="I6" t="s">
-        <v>60</v>
-      </c>
-      <c r="J6" t="s">
-        <v>68</v>
-      </c>
-      <c r="K6" t="s">
+      <c r="M6" t="s">
         <v>62</v>
       </c>
-      <c r="L6" t="s">
+      <c r="N6" t="s">
+        <v>64</v>
+      </c>
+      <c r="O6" t="s">
         <v>63</v>
       </c>
-      <c r="M6" t="s">
-        <v>64</v>
-      </c>
-      <c r="N6" t="s">
-        <v>67</v>
-      </c>
-      <c r="O6" t="s">
-        <v>65</v>
-      </c>
       <c r="P6" t="s">
-        <v>66</v>
+        <v>491</v>
       </c>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.35">
@@ -1911,10 +2532,10 @@
         <v>30</v>
       </c>
       <c r="H7" t="s">
+        <v>492</v>
+      </c>
+      <c r="I7" t="s">
         <v>32</v>
-      </c>
-      <c r="I7" t="s">
-        <v>33</v>
       </c>
       <c r="J7" t="s">
         <v>27</v>
@@ -1926,7 +2547,7 @@
         <v>28</v>
       </c>
       <c r="M7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N7" t="s">
         <v>29</v>
@@ -1952,37 +2573,37 @@
         <v>19</v>
       </c>
       <c r="F8" t="s">
+        <v>89</v>
+      </c>
+      <c r="G8" t="s">
+        <v>95</v>
+      </c>
+      <c r="H8" t="s">
+        <v>91</v>
+      </c>
+      <c r="I8" t="s">
         <v>92</v>
       </c>
-      <c r="G8" t="s">
+      <c r="J8" t="s">
+        <v>93</v>
+      </c>
+      <c r="K8" t="s">
+        <v>94</v>
+      </c>
+      <c r="L8" t="s">
+        <v>96</v>
+      </c>
+      <c r="M8" t="s">
+        <v>90</v>
+      </c>
+      <c r="N8" t="s">
+        <v>99</v>
+      </c>
+      <c r="O8" t="s">
         <v>98</v>
       </c>
-      <c r="H8" t="s">
-        <v>94</v>
-      </c>
-      <c r="I8" t="s">
-        <v>95</v>
-      </c>
-      <c r="J8" t="s">
-        <v>96</v>
-      </c>
-      <c r="K8" t="s">
+      <c r="P8" t="s">
         <v>97</v>
-      </c>
-      <c r="L8" t="s">
-        <v>99</v>
-      </c>
-      <c r="M8" t="s">
-        <v>93</v>
-      </c>
-      <c r="N8" t="s">
-        <v>102</v>
-      </c>
-      <c r="O8" t="s">
-        <v>101</v>
-      </c>
-      <c r="P8" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.35">
@@ -1999,37 +2620,37 @@
         <v>20</v>
       </c>
       <c r="F9" t="s">
+        <v>34</v>
+      </c>
+      <c r="G9" t="s">
         <v>35</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>36</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
+        <v>38</v>
+      </c>
+      <c r="J9" t="s">
+        <v>39</v>
+      </c>
+      <c r="K9" t="s">
+        <v>40</v>
+      </c>
+      <c r="L9" t="s">
+        <v>41</v>
+      </c>
+      <c r="M9" t="s">
+        <v>42</v>
+      </c>
+      <c r="N9" t="s">
+        <v>44</v>
+      </c>
+      <c r="O9" t="s">
         <v>37</v>
       </c>
-      <c r="I9" t="s">
-        <v>39</v>
-      </c>
-      <c r="J9" t="s">
-        <v>40</v>
-      </c>
-      <c r="K9" t="s">
-        <v>41</v>
-      </c>
-      <c r="L9" t="s">
-        <v>42</v>
-      </c>
-      <c r="M9" t="s">
+      <c r="P9" t="s">
         <v>43</v>
-      </c>
-      <c r="N9" t="s">
-        <v>45</v>
-      </c>
-      <c r="O9" t="s">
-        <v>38</v>
-      </c>
-      <c r="P9" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.35">
@@ -2046,37 +2667,37 @@
         <v>21</v>
       </c>
       <c r="F10" t="s">
+        <v>111</v>
+      </c>
+      <c r="G10" t="s">
+        <v>112</v>
+      </c>
+      <c r="H10" t="s">
+        <v>113</v>
+      </c>
+      <c r="I10" t="s">
         <v>114</v>
       </c>
-      <c r="G10" t="s">
+      <c r="J10" t="s">
         <v>115</v>
       </c>
-      <c r="H10" t="s">
+      <c r="K10" t="s">
         <v>116</v>
       </c>
-      <c r="I10" t="s">
+      <c r="L10" t="s">
+        <v>119</v>
+      </c>
+      <c r="M10" t="s">
+        <v>121</v>
+      </c>
+      <c r="N10" t="s">
+        <v>120</v>
+      </c>
+      <c r="O10" t="s">
         <v>117</v>
       </c>
-      <c r="J10" t="s">
+      <c r="P10" t="s">
         <v>118</v>
-      </c>
-      <c r="K10" t="s">
-        <v>119</v>
-      </c>
-      <c r="L10" t="s">
-        <v>122</v>
-      </c>
-      <c r="M10" t="s">
-        <v>124</v>
-      </c>
-      <c r="N10" t="s">
-        <v>123</v>
-      </c>
-      <c r="O10" t="s">
-        <v>120</v>
-      </c>
-      <c r="P10" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.35">
@@ -2093,37 +2714,37 @@
         <v>22</v>
       </c>
       <c r="F11" t="s">
+        <v>100</v>
+      </c>
+      <c r="G11" t="s">
+        <v>101</v>
+      </c>
+      <c r="H11" t="s">
+        <v>102</v>
+      </c>
+      <c r="I11" t="s">
+        <v>106</v>
+      </c>
+      <c r="J11" t="s">
+        <v>105</v>
+      </c>
+      <c r="K11" t="s">
+        <v>107</v>
+      </c>
+      <c r="L11" t="s">
+        <v>108</v>
+      </c>
+      <c r="M11" t="s">
+        <v>110</v>
+      </c>
+      <c r="N11" t="s">
+        <v>109</v>
+      </c>
+      <c r="O11" t="s">
         <v>103</v>
       </c>
-      <c r="G11" t="s">
+      <c r="P11" t="s">
         <v>104</v>
-      </c>
-      <c r="H11" t="s">
-        <v>105</v>
-      </c>
-      <c r="I11" t="s">
-        <v>109</v>
-      </c>
-      <c r="J11" t="s">
-        <v>108</v>
-      </c>
-      <c r="K11" t="s">
-        <v>110</v>
-      </c>
-      <c r="L11" t="s">
-        <v>111</v>
-      </c>
-      <c r="M11" t="s">
-        <v>113</v>
-      </c>
-      <c r="N11" t="s">
-        <v>112</v>
-      </c>
-      <c r="O11" t="s">
-        <v>106</v>
-      </c>
-      <c r="P11" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.35">
@@ -2140,37 +2761,37 @@
         <v>23</v>
       </c>
       <c r="F12" t="s">
+        <v>160</v>
+      </c>
+      <c r="G12" t="s">
+        <v>161</v>
+      </c>
+      <c r="H12" t="s">
+        <v>162</v>
+      </c>
+      <c r="I12" t="s">
         <v>163</v>
       </c>
-      <c r="G12" t="s">
+      <c r="J12" t="s">
+        <v>493</v>
+      </c>
+      <c r="K12" t="s">
+        <v>494</v>
+      </c>
+      <c r="L12" t="s">
+        <v>495</v>
+      </c>
+      <c r="M12" t="s">
+        <v>496</v>
+      </c>
+      <c r="N12" t="s">
         <v>164</v>
       </c>
-      <c r="H12" t="s">
+      <c r="O12" t="s">
         <v>165</v>
       </c>
-      <c r="I12" t="s">
+      <c r="P12" t="s">
         <v>166</v>
-      </c>
-      <c r="J12" t="s">
-        <v>167</v>
-      </c>
-      <c r="K12" t="s">
-        <v>168</v>
-      </c>
-      <c r="L12" t="s">
-        <v>169</v>
-      </c>
-      <c r="M12" t="s">
-        <v>170</v>
-      </c>
-      <c r="N12" t="s">
-        <v>171</v>
-      </c>
-      <c r="O12" t="s">
-        <v>172</v>
-      </c>
-      <c r="P12" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="13" spans="2:16" x14ac:dyDescent="0.35">
@@ -2184,40 +2805,40 @@
         <v>14</v>
       </c>
       <c r="E13" t="s">
+        <v>45</v>
+      </c>
+      <c r="F13" t="s">
+        <v>50</v>
+      </c>
+      <c r="G13" t="s">
         <v>46</v>
       </c>
-      <c r="F13" t="s">
+      <c r="H13" t="s">
+        <v>47</v>
+      </c>
+      <c r="I13" t="s">
         <v>51</v>
       </c>
-      <c r="G13" t="s">
-        <v>47</v>
-      </c>
-      <c r="H13" t="s">
+      <c r="J13" t="s">
+        <v>53</v>
+      </c>
+      <c r="K13" t="s">
+        <v>52</v>
+      </c>
+      <c r="L13" t="s">
+        <v>54</v>
+      </c>
+      <c r="M13" t="s">
+        <v>55</v>
+      </c>
+      <c r="N13" t="s">
+        <v>56</v>
+      </c>
+      <c r="O13" t="s">
+        <v>49</v>
+      </c>
+      <c r="P13" t="s">
         <v>48</v>
-      </c>
-      <c r="I13" t="s">
-        <v>52</v>
-      </c>
-      <c r="J13" t="s">
-        <v>54</v>
-      </c>
-      <c r="K13" t="s">
-        <v>53</v>
-      </c>
-      <c r="L13" t="s">
-        <v>55</v>
-      </c>
-      <c r="M13" t="s">
-        <v>56</v>
-      </c>
-      <c r="N13" t="s">
-        <v>57</v>
-      </c>
-      <c r="O13" t="s">
-        <v>50</v>
-      </c>
-      <c r="P13" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="14" spans="2:16" x14ac:dyDescent="0.35">
@@ -2231,40 +2852,40 @@
         <v>14</v>
       </c>
       <c r="E14" t="s">
+        <v>134</v>
+      </c>
+      <c r="F14" t="s">
+        <v>135</v>
+      </c>
+      <c r="G14" t="s">
+        <v>136</v>
+      </c>
+      <c r="H14" t="s">
         <v>137</v>
       </c>
-      <c r="F14" t="s">
+      <c r="I14" t="s">
         <v>138</v>
       </c>
-      <c r="G14" t="s">
+      <c r="J14" t="s">
+        <v>142</v>
+      </c>
+      <c r="K14" t="s">
+        <v>143</v>
+      </c>
+      <c r="L14" t="s">
+        <v>144</v>
+      </c>
+      <c r="M14" t="s">
+        <v>145</v>
+      </c>
+      <c r="N14" t="s">
+        <v>141</v>
+      </c>
+      <c r="O14" t="s">
+        <v>140</v>
+      </c>
+      <c r="P14" t="s">
         <v>139</v>
-      </c>
-      <c r="H14" t="s">
-        <v>140</v>
-      </c>
-      <c r="I14" t="s">
-        <v>141</v>
-      </c>
-      <c r="J14" t="s">
-        <v>145</v>
-      </c>
-      <c r="K14" t="s">
-        <v>146</v>
-      </c>
-      <c r="L14" t="s">
-        <v>147</v>
-      </c>
-      <c r="M14" t="s">
-        <v>148</v>
-      </c>
-      <c r="N14" t="s">
-        <v>144</v>
-      </c>
-      <c r="O14" t="s">
-        <v>143</v>
-      </c>
-      <c r="P14" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="15" spans="2:16" x14ac:dyDescent="0.35">
@@ -2278,40 +2899,40 @@
         <v>14</v>
       </c>
       <c r="E15" t="s">
+        <v>146</v>
+      </c>
+      <c r="F15" t="s">
+        <v>150</v>
+      </c>
+      <c r="G15" t="s">
+        <v>151</v>
+      </c>
+      <c r="H15" t="s">
+        <v>152</v>
+      </c>
+      <c r="I15" t="s">
+        <v>156</v>
+      </c>
+      <c r="J15" t="s">
+        <v>154</v>
+      </c>
+      <c r="K15" t="s">
+        <v>155</v>
+      </c>
+      <c r="L15" t="s">
+        <v>153</v>
+      </c>
+      <c r="M15" t="s">
+        <v>157</v>
+      </c>
+      <c r="N15" t="s">
         <v>149</v>
       </c>
-      <c r="F15" t="s">
-        <v>153</v>
-      </c>
-      <c r="G15" t="s">
-        <v>154</v>
-      </c>
-      <c r="H15" t="s">
-        <v>155</v>
-      </c>
-      <c r="I15" t="s">
-        <v>159</v>
-      </c>
-      <c r="J15" t="s">
-        <v>157</v>
-      </c>
-      <c r="K15" t="s">
-        <v>158</v>
-      </c>
-      <c r="L15" t="s">
-        <v>156</v>
-      </c>
-      <c r="M15" t="s">
-        <v>160</v>
-      </c>
-      <c r="N15" t="s">
-        <v>152</v>
-      </c>
       <c r="O15" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="P15" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="16" spans="2:16" x14ac:dyDescent="0.35">
@@ -2319,46 +2940,46 @@
         <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D16" t="s">
+        <v>168</v>
+      </c>
+      <c r="E16" t="s">
+        <v>169</v>
+      </c>
+      <c r="F16" t="s">
+        <v>170</v>
+      </c>
+      <c r="G16" t="s">
+        <v>171</v>
+      </c>
+      <c r="H16" t="s">
         <v>175</v>
       </c>
-      <c r="E16" t="s">
+      <c r="I16" t="s">
+        <v>167</v>
+      </c>
+      <c r="J16" t="s">
+        <v>174</v>
+      </c>
+      <c r="K16" t="s">
         <v>176</v>
       </c>
-      <c r="F16" t="s">
+      <c r="L16" t="s">
+        <v>178</v>
+      </c>
+      <c r="M16" t="s">
         <v>177</v>
       </c>
-      <c r="G16" t="s">
-        <v>178</v>
-      </c>
-      <c r="H16" t="s">
-        <v>182</v>
-      </c>
-      <c r="I16" t="s">
-        <v>174</v>
-      </c>
-      <c r="J16" t="s">
-        <v>181</v>
-      </c>
-      <c r="K16" t="s">
-        <v>183</v>
-      </c>
-      <c r="L16" t="s">
-        <v>185</v>
-      </c>
-      <c r="M16" t="s">
-        <v>184</v>
-      </c>
       <c r="N16" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="O16" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="P16" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
     </row>
     <row r="17" spans="2:16" x14ac:dyDescent="0.35">
@@ -2366,46 +2987,46 @@
         <v>15</v>
       </c>
       <c r="C17" t="s">
+        <v>286</v>
+      </c>
+      <c r="D17" t="s">
+        <v>168</v>
+      </c>
+      <c r="E17" t="s">
+        <v>180</v>
+      </c>
+      <c r="F17" t="s">
+        <v>181</v>
+      </c>
+      <c r="G17" t="s">
+        <v>184</v>
+      </c>
+      <c r="H17" t="s">
+        <v>317</v>
+      </c>
+      <c r="I17" t="s">
+        <v>186</v>
+      </c>
+      <c r="J17" t="s">
+        <v>185</v>
+      </c>
+      <c r="K17" t="s">
+        <v>188</v>
+      </c>
+      <c r="L17" t="s">
+        <v>559</v>
+      </c>
+      <c r="M17" t="s">
+        <v>189</v>
+      </c>
+      <c r="N17" t="s">
         <v>187</v>
       </c>
-      <c r="D17" t="s">
-        <v>175</v>
-      </c>
-      <c r="E17" t="s">
-        <v>187</v>
-      </c>
-      <c r="F17" t="s">
-        <v>188</v>
-      </c>
-      <c r="G17" t="s">
-        <v>192</v>
-      </c>
-      <c r="H17" t="s">
-        <v>191</v>
-      </c>
-      <c r="I17" t="s">
-        <v>194</v>
-      </c>
-      <c r="J17" t="s">
-        <v>193</v>
-      </c>
-      <c r="K17" t="s">
-        <v>196</v>
-      </c>
-      <c r="L17" t="s">
-        <v>198</v>
-      </c>
-      <c r="M17" t="s">
-        <v>197</v>
-      </c>
-      <c r="N17" t="s">
-        <v>195</v>
-      </c>
       <c r="O17" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="P17" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.35">
@@ -2413,46 +3034,46 @@
         <v>16</v>
       </c>
       <c r="C18" t="s">
+        <v>190</v>
+      </c>
+      <c r="D18" t="s">
+        <v>168</v>
+      </c>
+      <c r="E18" t="s">
+        <v>191</v>
+      </c>
+      <c r="F18" t="s">
+        <v>192</v>
+      </c>
+      <c r="G18" t="s">
+        <v>193</v>
+      </c>
+      <c r="H18" t="s">
+        <v>194</v>
+      </c>
+      <c r="I18" t="s">
+        <v>195</v>
+      </c>
+      <c r="J18" t="s">
+        <v>196</v>
+      </c>
+      <c r="K18" t="s">
+        <v>197</v>
+      </c>
+      <c r="L18" t="s">
+        <v>201</v>
+      </c>
+      <c r="M18" t="s">
+        <v>202</v>
+      </c>
+      <c r="N18" t="s">
+        <v>200</v>
+      </c>
+      <c r="O18" t="s">
+        <v>198</v>
+      </c>
+      <c r="P18" t="s">
         <v>199</v>
-      </c>
-      <c r="D18" t="s">
-        <v>175</v>
-      </c>
-      <c r="E18" t="s">
-        <v>200</v>
-      </c>
-      <c r="F18" t="s">
-        <v>201</v>
-      </c>
-      <c r="G18" t="s">
-        <v>202</v>
-      </c>
-      <c r="H18" t="s">
-        <v>203</v>
-      </c>
-      <c r="I18" t="s">
-        <v>204</v>
-      </c>
-      <c r="J18" t="s">
-        <v>205</v>
-      </c>
-      <c r="K18" t="s">
-        <v>206</v>
-      </c>
-      <c r="L18" t="s">
-        <v>210</v>
-      </c>
-      <c r="M18" t="s">
-        <v>211</v>
-      </c>
-      <c r="N18" t="s">
-        <v>209</v>
-      </c>
-      <c r="O18" t="s">
-        <v>207</v>
-      </c>
-      <c r="P18" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.35">
@@ -2463,43 +3084,43 @@
         <v>13</v>
       </c>
       <c r="D19" t="s">
+        <v>203</v>
+      </c>
+      <c r="E19" t="s">
+        <v>204</v>
+      </c>
+      <c r="F19" t="s">
+        <v>206</v>
+      </c>
+      <c r="G19" t="s">
+        <v>207</v>
+      </c>
+      <c r="H19" t="s">
+        <v>208</v>
+      </c>
+      <c r="I19" t="s">
+        <v>209</v>
+      </c>
+      <c r="J19" t="s">
+        <v>210</v>
+      </c>
+      <c r="K19" t="s">
+        <v>211</v>
+      </c>
+      <c r="L19" t="s">
         <v>212</v>
       </c>
-      <c r="E19" t="s">
+      <c r="M19" t="s">
+        <v>214</v>
+      </c>
+      <c r="N19" t="s">
+        <v>215</v>
+      </c>
+      <c r="O19" t="s">
         <v>213</v>
       </c>
-      <c r="F19" t="s">
-        <v>215</v>
-      </c>
-      <c r="G19" t="s">
-        <v>216</v>
-      </c>
-      <c r="H19" t="s">
-        <v>217</v>
-      </c>
-      <c r="I19" t="s">
-        <v>218</v>
-      </c>
-      <c r="J19" t="s">
-        <v>219</v>
-      </c>
-      <c r="K19" t="s">
-        <v>220</v>
-      </c>
-      <c r="L19" t="s">
-        <v>221</v>
-      </c>
-      <c r="M19" t="s">
-        <v>224</v>
-      </c>
-      <c r="N19" t="s">
-        <v>225</v>
-      </c>
-      <c r="O19" t="s">
-        <v>223</v>
-      </c>
       <c r="P19" t="s">
-        <v>222</v>
+        <v>471</v>
       </c>
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.35">
@@ -2510,43 +3131,43 @@
         <v>13</v>
       </c>
       <c r="D20" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="E20" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="F20" t="s">
+        <v>216</v>
+      </c>
+      <c r="G20" t="s">
+        <v>217</v>
+      </c>
+      <c r="H20" t="s">
+        <v>218</v>
+      </c>
+      <c r="I20" t="s">
+        <v>219</v>
+      </c>
+      <c r="J20" t="s">
+        <v>220</v>
+      </c>
+      <c r="K20" t="s">
+        <v>223</v>
+      </c>
+      <c r="L20" t="s">
+        <v>224</v>
+      </c>
+      <c r="M20" t="s">
+        <v>225</v>
+      </c>
+      <c r="N20" t="s">
         <v>226</v>
       </c>
-      <c r="G20" t="s">
-        <v>227</v>
-      </c>
-      <c r="H20" t="s">
-        <v>228</v>
-      </c>
-      <c r="I20" t="s">
-        <v>229</v>
-      </c>
-      <c r="J20" t="s">
-        <v>230</v>
-      </c>
-      <c r="K20" t="s">
-        <v>233</v>
-      </c>
-      <c r="L20" t="s">
-        <v>234</v>
-      </c>
-      <c r="M20" t="s">
-        <v>235</v>
-      </c>
-      <c r="N20" t="s">
-        <v>236</v>
-      </c>
       <c r="O20" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="P20" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
     </row>
     <row r="21" spans="2:16" x14ac:dyDescent="0.35">
@@ -2557,43 +3178,43 @@
         <v>13</v>
       </c>
       <c r="D21" t="s">
+        <v>227</v>
+      </c>
+      <c r="E21" t="s">
+        <v>204</v>
+      </c>
+      <c r="F21" t="s">
+        <v>231</v>
+      </c>
+      <c r="G21" t="s">
+        <v>229</v>
+      </c>
+      <c r="H21" t="s">
+        <v>230</v>
+      </c>
+      <c r="I21" t="s">
+        <v>232</v>
+      </c>
+      <c r="J21" t="s">
+        <v>228</v>
+      </c>
+      <c r="K21" t="s">
+        <v>234</v>
+      </c>
+      <c r="L21" t="s">
+        <v>233</v>
+      </c>
+      <c r="M21" t="s">
+        <v>235</v>
+      </c>
+      <c r="N21" t="s">
+        <v>236</v>
+      </c>
+      <c r="O21" t="s">
+        <v>238</v>
+      </c>
+      <c r="P21" t="s">
         <v>237</v>
-      </c>
-      <c r="E21" t="s">
-        <v>213</v>
-      </c>
-      <c r="F21" t="s">
-        <v>241</v>
-      </c>
-      <c r="G21" t="s">
-        <v>239</v>
-      </c>
-      <c r="H21" t="s">
-        <v>240</v>
-      </c>
-      <c r="I21" t="s">
-        <v>242</v>
-      </c>
-      <c r="J21" t="s">
-        <v>238</v>
-      </c>
-      <c r="K21" t="s">
-        <v>244</v>
-      </c>
-      <c r="L21" t="s">
-        <v>243</v>
-      </c>
-      <c r="M21" t="s">
-        <v>245</v>
-      </c>
-      <c r="N21" t="s">
-        <v>246</v>
-      </c>
-      <c r="O21" t="s">
-        <v>248</v>
-      </c>
-      <c r="P21" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.35">
@@ -2604,43 +3225,43 @@
         <v>13</v>
       </c>
       <c r="D22" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="E22" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="F22" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="G22" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="H22" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="I22" t="s">
+        <v>239</v>
+      </c>
+      <c r="J22" t="s">
+        <v>240</v>
+      </c>
+      <c r="K22" t="s">
+        <v>248</v>
+      </c>
+      <c r="L22" t="s">
+        <v>246</v>
+      </c>
+      <c r="M22" t="s">
         <v>249</v>
       </c>
-      <c r="J22" t="s">
-        <v>250</v>
-      </c>
-      <c r="K22" t="s">
-        <v>258</v>
-      </c>
-      <c r="L22" t="s">
-        <v>256</v>
-      </c>
-      <c r="M22" t="s">
-        <v>259</v>
-      </c>
       <c r="N22" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="O22" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="P22" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
     </row>
     <row r="23" spans="2:16" x14ac:dyDescent="0.35">
@@ -2648,43 +3269,46 @@
         <v>21</v>
       </c>
       <c r="C23" t="s">
-        <v>271</v>
+        <v>250</v>
       </c>
       <c r="D23" t="s">
-        <v>237</v>
+        <v>227</v>
+      </c>
+      <c r="E23" t="s">
+        <v>592</v>
       </c>
       <c r="F23" t="s">
-        <v>260</v>
+        <v>330</v>
       </c>
       <c r="G23" t="s">
-        <v>261</v>
+        <v>331</v>
       </c>
       <c r="H23" t="s">
-        <v>267</v>
+        <v>332</v>
       </c>
       <c r="I23" t="s">
-        <v>263</v>
+        <v>333</v>
       </c>
       <c r="J23" t="s">
-        <v>262</v>
+        <v>334</v>
       </c>
       <c r="K23" t="s">
-        <v>264</v>
+        <v>335</v>
       </c>
       <c r="L23" t="s">
-        <v>270</v>
+        <v>336</v>
       </c>
       <c r="M23" t="s">
-        <v>266</v>
+        <v>337</v>
       </c>
       <c r="N23" t="s">
-        <v>268</v>
+        <v>338</v>
       </c>
       <c r="O23" t="s">
-        <v>269</v>
+        <v>339</v>
       </c>
       <c r="P23" t="s">
-        <v>265</v>
+        <v>340</v>
       </c>
     </row>
     <row r="24" spans="2:16" x14ac:dyDescent="0.35">
@@ -2692,43 +3316,46 @@
         <v>22</v>
       </c>
       <c r="C24" t="s">
-        <v>271</v>
+        <v>250</v>
       </c>
       <c r="D24" t="s">
-        <v>237</v>
+        <v>227</v>
+      </c>
+      <c r="E24" t="s">
+        <v>592</v>
       </c>
       <c r="F24" t="s">
-        <v>272</v>
+        <v>341</v>
       </c>
       <c r="G24" t="s">
-        <v>278</v>
+        <v>342</v>
       </c>
       <c r="H24" t="s">
-        <v>275</v>
+        <v>343</v>
       </c>
       <c r="I24" t="s">
-        <v>273</v>
+        <v>344</v>
       </c>
       <c r="J24" t="s">
-        <v>274</v>
+        <v>345</v>
       </c>
       <c r="K24" t="s">
-        <v>280</v>
+        <v>346</v>
       </c>
       <c r="L24" t="s">
-        <v>277</v>
+        <v>347</v>
       </c>
       <c r="M24" t="s">
-        <v>279</v>
+        <v>348</v>
       </c>
       <c r="N24" t="s">
-        <v>281</v>
+        <v>349</v>
       </c>
       <c r="O24" t="s">
-        <v>276</v>
+        <v>350</v>
       </c>
       <c r="P24" t="s">
-        <v>282</v>
+        <v>351</v>
       </c>
     </row>
     <row r="25" spans="2:16" x14ac:dyDescent="0.35">
@@ -2736,43 +3363,46 @@
         <v>23</v>
       </c>
       <c r="C25" t="s">
-        <v>271</v>
+        <v>250</v>
       </c>
       <c r="D25" t="s">
-        <v>237</v>
+        <v>227</v>
+      </c>
+      <c r="E25" t="s">
+        <v>592</v>
       </c>
       <c r="F25" t="s">
-        <v>283</v>
+        <v>352</v>
       </c>
       <c r="G25" t="s">
-        <v>290</v>
+        <v>251</v>
       </c>
       <c r="H25" t="s">
-        <v>284</v>
+        <v>353</v>
       </c>
       <c r="I25" t="s">
-        <v>285</v>
+        <v>354</v>
       </c>
       <c r="J25" t="s">
-        <v>291</v>
+        <v>355</v>
       </c>
       <c r="K25" t="s">
-        <v>286</v>
+        <v>356</v>
       </c>
       <c r="L25" t="s">
-        <v>288</v>
+        <v>357</v>
       </c>
       <c r="M25" t="s">
-        <v>292</v>
+        <v>252</v>
       </c>
       <c r="N25" t="s">
-        <v>293</v>
+        <v>253</v>
       </c>
       <c r="O25" t="s">
-        <v>287</v>
+        <v>358</v>
       </c>
       <c r="P25" t="s">
-        <v>289</v>
+        <v>359</v>
       </c>
     </row>
     <row r="26" spans="2:16" x14ac:dyDescent="0.35">
@@ -2780,43 +3410,46 @@
         <v>24</v>
       </c>
       <c r="C26" t="s">
-        <v>271</v>
+        <v>250</v>
       </c>
       <c r="D26" t="s">
         <v>14</v>
       </c>
+      <c r="E26" t="s">
+        <v>592</v>
+      </c>
       <c r="F26" t="s">
-        <v>310</v>
+        <v>497</v>
       </c>
       <c r="G26" t="s">
-        <v>301</v>
+        <v>498</v>
       </c>
       <c r="H26" t="s">
-        <v>304</v>
+        <v>499</v>
       </c>
       <c r="I26" t="s">
-        <v>321</v>
+        <v>256</v>
       </c>
       <c r="J26" t="s">
-        <v>312</v>
+        <v>500</v>
       </c>
       <c r="K26" t="s">
-        <v>308</v>
+        <v>501</v>
       </c>
       <c r="L26" t="s">
-        <v>309</v>
+        <v>502</v>
       </c>
       <c r="M26" t="s">
-        <v>303</v>
+        <v>503</v>
       </c>
       <c r="N26" t="s">
-        <v>298</v>
+        <v>504</v>
       </c>
       <c r="O26" t="s">
-        <v>299</v>
+        <v>505</v>
       </c>
       <c r="P26" t="s">
-        <v>311</v>
+        <v>506</v>
       </c>
     </row>
     <row r="27" spans="2:16" x14ac:dyDescent="0.35">
@@ -2824,43 +3457,46 @@
         <v>25</v>
       </c>
       <c r="C27" t="s">
-        <v>271</v>
+        <v>250</v>
       </c>
       <c r="D27" t="s">
         <v>14</v>
       </c>
+      <c r="E27" t="s">
+        <v>592</v>
+      </c>
       <c r="F27" t="s">
-        <v>307</v>
+        <v>507</v>
       </c>
       <c r="G27" t="s">
-        <v>302</v>
+        <v>508</v>
       </c>
       <c r="H27" t="s">
-        <v>297</v>
+        <v>509</v>
       </c>
       <c r="I27" t="s">
-        <v>313</v>
+        <v>510</v>
       </c>
       <c r="J27" t="s">
-        <v>296</v>
+        <v>511</v>
       </c>
       <c r="K27" t="s">
-        <v>317</v>
+        <v>254</v>
       </c>
       <c r="L27" t="s">
-        <v>306</v>
+        <v>512</v>
       </c>
       <c r="M27" t="s">
-        <v>295</v>
+        <v>513</v>
       </c>
       <c r="N27" t="s">
-        <v>318</v>
+        <v>514</v>
       </c>
       <c r="O27" t="s">
-        <v>322</v>
+        <v>257</v>
       </c>
       <c r="P27" t="s">
-        <v>323</v>
+        <v>258</v>
       </c>
     </row>
     <row r="28" spans="2:16" x14ac:dyDescent="0.35">
@@ -2868,43 +3504,46 @@
         <v>26</v>
       </c>
       <c r="C28" t="s">
-        <v>271</v>
+        <v>250</v>
       </c>
       <c r="D28" t="s">
         <v>14</v>
       </c>
+      <c r="E28" t="s">
+        <v>592</v>
+      </c>
       <c r="F28" t="s">
-        <v>320</v>
+        <v>515</v>
       </c>
       <c r="G28" t="s">
-        <v>305</v>
+        <v>516</v>
       </c>
       <c r="H28" t="s">
-        <v>326</v>
+        <v>517</v>
       </c>
       <c r="I28" t="s">
-        <v>324</v>
+        <v>259</v>
       </c>
       <c r="J28" t="s">
-        <v>315</v>
+        <v>518</v>
       </c>
       <c r="K28" t="s">
-        <v>325</v>
+        <v>260</v>
       </c>
       <c r="L28" t="s">
-        <v>300</v>
+        <v>519</v>
       </c>
       <c r="M28" t="s">
-        <v>294</v>
+        <v>520</v>
       </c>
       <c r="N28" t="s">
-        <v>319</v>
+        <v>255</v>
       </c>
       <c r="O28" t="s">
-        <v>314</v>
+        <v>521</v>
       </c>
       <c r="P28" t="s">
-        <v>316</v>
+        <v>522</v>
       </c>
     </row>
     <row r="29" spans="2:16" x14ac:dyDescent="0.35">
@@ -2918,40 +3557,40 @@
         <v>14</v>
       </c>
       <c r="E29" t="s">
-        <v>349</v>
+        <v>261</v>
       </c>
       <c r="F29" t="s">
-        <v>342</v>
+        <v>523</v>
       </c>
       <c r="G29" t="s">
-        <v>343</v>
+        <v>524</v>
       </c>
       <c r="H29" t="s">
-        <v>344</v>
+        <v>525</v>
       </c>
       <c r="I29" t="s">
-        <v>334</v>
+        <v>526</v>
       </c>
       <c r="J29" t="s">
-        <v>327</v>
+        <v>527</v>
       </c>
       <c r="K29" t="s">
-        <v>328</v>
+        <v>528</v>
       </c>
       <c r="L29" t="s">
-        <v>329</v>
-      </c>
-      <c r="M29" s="2" t="s">
-        <v>330</v>
+        <v>529</v>
+      </c>
+      <c r="M29" t="s">
+        <v>530</v>
       </c>
       <c r="N29" t="s">
-        <v>331</v>
+        <v>531</v>
       </c>
       <c r="O29" t="s">
-        <v>332</v>
+        <v>532</v>
       </c>
       <c r="P29" t="s">
-        <v>333</v>
+        <v>533</v>
       </c>
     </row>
     <row r="30" spans="2:16" x14ac:dyDescent="0.35">
@@ -2965,40 +3604,40 @@
         <v>14</v>
       </c>
       <c r="E30" t="s">
-        <v>349</v>
+        <v>261</v>
       </c>
       <c r="F30" t="s">
-        <v>345</v>
+        <v>534</v>
       </c>
       <c r="G30" t="s">
-        <v>346</v>
+        <v>535</v>
       </c>
       <c r="H30" t="s">
-        <v>347</v>
+        <v>536</v>
       </c>
       <c r="I30" t="s">
-        <v>348</v>
+        <v>537</v>
       </c>
       <c r="J30" t="s">
-        <v>335</v>
+        <v>538</v>
       </c>
       <c r="K30" t="s">
-        <v>336</v>
+        <v>539</v>
       </c>
       <c r="L30" t="s">
-        <v>337</v>
+        <v>540</v>
       </c>
       <c r="M30" t="s">
-        <v>338</v>
+        <v>541</v>
       </c>
       <c r="N30" t="s">
-        <v>339</v>
+        <v>542</v>
       </c>
       <c r="O30" t="s">
-        <v>340</v>
+        <v>543</v>
       </c>
       <c r="P30" t="s">
-        <v>341</v>
+        <v>544</v>
       </c>
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.35">
@@ -3009,43 +3648,43 @@
         <v>13</v>
       </c>
       <c r="D31" t="s">
-        <v>350</v>
+        <v>262</v>
       </c>
       <c r="E31" t="s">
-        <v>351</v>
+        <v>263</v>
       </c>
       <c r="F31" t="s">
-        <v>352</v>
+        <v>472</v>
       </c>
       <c r="G31" t="s">
-        <v>353</v>
+        <v>473</v>
       </c>
       <c r="H31" t="s">
-        <v>354</v>
+        <v>474</v>
       </c>
       <c r="I31" t="s">
-        <v>355</v>
+        <v>475</v>
       </c>
       <c r="J31" t="s">
-        <v>356</v>
+        <v>476</v>
       </c>
       <c r="K31" t="s">
-        <v>357</v>
+        <v>477</v>
       </c>
       <c r="L31" t="s">
-        <v>358</v>
+        <v>478</v>
       </c>
       <c r="M31" t="s">
-        <v>360</v>
+        <v>479</v>
       </c>
       <c r="N31" t="s">
-        <v>359</v>
+        <v>480</v>
       </c>
       <c r="O31" t="s">
-        <v>361</v>
+        <v>481</v>
       </c>
       <c r="P31" t="s">
-        <v>362</v>
+        <v>482</v>
       </c>
     </row>
     <row r="32" spans="2:16" x14ac:dyDescent="0.35">
@@ -3053,660 +3692,2910 @@
         <v>30</v>
       </c>
       <c r="C32" t="s">
-        <v>271</v>
+        <v>250</v>
       </c>
       <c r="D32" t="s">
-        <v>350</v>
+        <v>262</v>
       </c>
       <c r="E32" t="s">
-        <v>351</v>
+        <v>263</v>
       </c>
       <c r="F32" t="s">
-        <v>363</v>
+        <v>483</v>
       </c>
       <c r="G32" t="s">
-        <v>369</v>
+        <v>264</v>
       </c>
       <c r="H32" t="s">
-        <v>367</v>
+        <v>484</v>
       </c>
       <c r="I32" t="s">
-        <v>366</v>
+        <v>485</v>
       </c>
       <c r="J32" t="s">
-        <v>371</v>
+        <v>266</v>
       </c>
       <c r="K32" t="s">
-        <v>368</v>
+        <v>486</v>
       </c>
       <c r="L32" t="s">
-        <v>372</v>
+        <v>487</v>
       </c>
       <c r="M32" t="s">
-        <v>370</v>
+        <v>488</v>
       </c>
       <c r="N32" t="s">
-        <v>373</v>
+        <v>267</v>
       </c>
       <c r="O32" t="s">
-        <v>365</v>
+        <v>265</v>
       </c>
       <c r="P32" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.35">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B33">
         <v>31</v>
       </c>
       <c r="C33" t="s">
-        <v>271</v>
+        <v>250</v>
       </c>
       <c r="D33" t="s">
-        <v>14</v>
+        <v>227</v>
       </c>
       <c r="E33" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.35">
+        <v>268</v>
+      </c>
+      <c r="F33" t="s">
+        <v>360</v>
+      </c>
+      <c r="G33" t="s">
+        <v>361</v>
+      </c>
+      <c r="H33" t="s">
+        <v>362</v>
+      </c>
+      <c r="I33" t="s">
+        <v>363</v>
+      </c>
+      <c r="J33" t="s">
+        <v>364</v>
+      </c>
+      <c r="K33" t="s">
+        <v>365</v>
+      </c>
+      <c r="L33" t="s">
+        <v>366</v>
+      </c>
+      <c r="M33" t="s">
+        <v>367</v>
+      </c>
+      <c r="N33" t="s">
+        <v>368</v>
+      </c>
+      <c r="O33" t="s">
+        <v>369</v>
+      </c>
+      <c r="P33" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B34">
         <v>32</v>
       </c>
       <c r="C34" t="s">
-        <v>271</v>
+        <v>250</v>
       </c>
       <c r="D34" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="E34" t="s">
+        <v>274</v>
+      </c>
+      <c r="F34" t="s">
+        <v>371</v>
+      </c>
+      <c r="G34" t="s">
+        <v>307</v>
+      </c>
+      <c r="H34" t="s">
+        <v>372</v>
+      </c>
+      <c r="I34" t="s">
+        <v>373</v>
+      </c>
+      <c r="J34" t="s">
         <v>374</v>
       </c>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="K34" t="s">
+        <v>375</v>
+      </c>
+      <c r="L34" t="s">
+        <v>376</v>
+      </c>
+      <c r="M34" t="s">
+        <v>377</v>
+      </c>
+      <c r="N34" t="s">
+        <v>378</v>
+      </c>
+      <c r="O34" t="s">
+        <v>379</v>
+      </c>
+      <c r="P34" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B35">
         <v>33</v>
       </c>
       <c r="C35" t="s">
-        <v>271</v>
+        <v>250</v>
       </c>
       <c r="D35" t="s">
         <v>14</v>
       </c>
       <c r="E35" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.35">
+        <v>269</v>
+      </c>
+      <c r="F35" t="s">
+        <v>396</v>
+      </c>
+      <c r="G35" t="s">
+        <v>396</v>
+      </c>
+      <c r="H35" t="s">
+        <v>396</v>
+      </c>
+      <c r="I35" t="s">
+        <v>396</v>
+      </c>
+      <c r="J35" t="s">
+        <v>396</v>
+      </c>
+      <c r="K35" t="s">
+        <v>396</v>
+      </c>
+      <c r="L35" t="s">
+        <v>396</v>
+      </c>
+      <c r="M35" t="s">
+        <v>396</v>
+      </c>
+      <c r="N35" t="s">
+        <v>396</v>
+      </c>
+      <c r="O35" t="s">
+        <v>396</v>
+      </c>
+      <c r="P35" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="36" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B36">
         <v>34</v>
       </c>
       <c r="C36" t="s">
-        <v>271</v>
+        <v>250</v>
       </c>
       <c r="D36" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="E36" t="s">
+        <v>269</v>
+      </c>
+      <c r="F36" t="s">
         <v>380</v>
       </c>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
-      <c r="K36" s="1"/>
-      <c r="L36" s="1"/>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="G36" t="s">
+        <v>381</v>
+      </c>
+      <c r="H36" t="s">
+        <v>382</v>
+      </c>
+      <c r="I36" t="s">
+        <v>383</v>
+      </c>
+      <c r="J36" t="s">
+        <v>321</v>
+      </c>
+      <c r="K36" t="s">
+        <v>384</v>
+      </c>
+      <c r="L36" t="s">
+        <v>320</v>
+      </c>
+      <c r="M36" t="s">
+        <v>385</v>
+      </c>
+      <c r="N36" t="s">
+        <v>386</v>
+      </c>
+      <c r="O36" t="s">
+        <v>387</v>
+      </c>
+      <c r="P36" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B37">
         <v>35</v>
       </c>
       <c r="C37" t="s">
-        <v>271</v>
+        <v>250</v>
       </c>
       <c r="D37" t="s">
         <v>14</v>
       </c>
       <c r="E37" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.35">
+        <v>275</v>
+      </c>
+      <c r="F37" t="s">
+        <v>396</v>
+      </c>
+      <c r="G37" t="s">
+        <v>396</v>
+      </c>
+      <c r="H37" t="s">
+        <v>396</v>
+      </c>
+      <c r="I37" t="s">
+        <v>396</v>
+      </c>
+      <c r="J37" t="s">
+        <v>396</v>
+      </c>
+      <c r="K37" t="s">
+        <v>396</v>
+      </c>
+      <c r="L37" t="s">
+        <v>396</v>
+      </c>
+      <c r="M37" t="s">
+        <v>396</v>
+      </c>
+      <c r="N37" t="s">
+        <v>396</v>
+      </c>
+      <c r="O37" t="s">
+        <v>396</v>
+      </c>
+      <c r="P37" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="38" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B38">
         <v>36</v>
       </c>
       <c r="C38" t="s">
-        <v>271</v>
+        <v>250</v>
       </c>
       <c r="D38" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="E38" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.35">
+        <v>275</v>
+      </c>
+      <c r="F38" t="s">
+        <v>389</v>
+      </c>
+      <c r="G38" t="s">
+        <v>390</v>
+      </c>
+      <c r="H38" t="s">
+        <v>326</v>
+      </c>
+      <c r="I38" t="s">
+        <v>327</v>
+      </c>
+      <c r="J38" t="s">
+        <v>391</v>
+      </c>
+      <c r="K38" t="s">
+        <v>328</v>
+      </c>
+      <c r="L38" t="s">
+        <v>329</v>
+      </c>
+      <c r="M38" t="s">
+        <v>392</v>
+      </c>
+      <c r="N38" t="s">
+        <v>393</v>
+      </c>
+      <c r="O38" t="s">
+        <v>394</v>
+      </c>
+      <c r="P38" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B39">
         <v>37</v>
       </c>
       <c r="C39" t="s">
-        <v>271</v>
+        <v>250</v>
       </c>
       <c r="D39" t="s">
         <v>14</v>
       </c>
       <c r="E39" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.35">
+        <v>271</v>
+      </c>
+      <c r="F39" t="s">
+        <v>396</v>
+      </c>
+      <c r="G39" t="s">
+        <v>396</v>
+      </c>
+      <c r="H39" t="s">
+        <v>396</v>
+      </c>
+      <c r="I39" t="s">
+        <v>396</v>
+      </c>
+      <c r="J39" t="s">
+        <v>396</v>
+      </c>
+      <c r="K39" t="s">
+        <v>396</v>
+      </c>
+      <c r="L39" t="s">
+        <v>396</v>
+      </c>
+      <c r="M39" t="s">
+        <v>396</v>
+      </c>
+      <c r="N39" t="s">
+        <v>396</v>
+      </c>
+      <c r="O39" t="s">
+        <v>396</v>
+      </c>
+      <c r="P39" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B40">
         <v>38</v>
       </c>
       <c r="C40" t="s">
+        <v>250</v>
+      </c>
+      <c r="D40" t="s">
+        <v>227</v>
+      </c>
+      <c r="E40" t="s">
         <v>271</v>
       </c>
-      <c r="D40" t="s">
-        <v>237</v>
-      </c>
-      <c r="E40" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="F40" t="s">
+        <v>573</v>
+      </c>
+      <c r="G40" t="s">
+        <v>574</v>
+      </c>
+      <c r="H40" t="s">
+        <v>358</v>
+      </c>
+      <c r="I40" t="s">
+        <v>575</v>
+      </c>
+      <c r="J40" t="s">
+        <v>576</v>
+      </c>
+      <c r="K40" t="s">
+        <v>577</v>
+      </c>
+      <c r="L40" t="s">
+        <v>563</v>
+      </c>
+      <c r="M40" t="s">
+        <v>578</v>
+      </c>
+      <c r="N40" t="s">
+        <v>561</v>
+      </c>
+      <c r="O40" t="s">
+        <v>562</v>
+      </c>
+      <c r="P40" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B41">
         <v>39</v>
       </c>
       <c r="C41" t="s">
-        <v>271</v>
+        <v>250</v>
       </c>
       <c r="D41" t="s">
+        <v>227</v>
+      </c>
+      <c r="E41" t="s">
+        <v>285</v>
+      </c>
+      <c r="F41" t="s">
+        <v>397</v>
+      </c>
+      <c r="G41" t="s">
+        <v>398</v>
+      </c>
+      <c r="H41" t="s">
+        <v>399</v>
+      </c>
+      <c r="I41" t="s">
+        <v>400</v>
+      </c>
+      <c r="J41" t="s">
+        <v>401</v>
+      </c>
+      <c r="K41" t="s">
+        <v>402</v>
+      </c>
+      <c r="L41" t="s">
+        <v>403</v>
+      </c>
+      <c r="M41" t="s">
+        <v>404</v>
+      </c>
+      <c r="N41" t="s">
+        <v>405</v>
+      </c>
+      <c r="O41" t="s">
+        <v>406</v>
+      </c>
+      <c r="P41" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B42">
+        <v>42</v>
+      </c>
+      <c r="C42" t="s">
+        <v>250</v>
+      </c>
+      <c r="D42" t="s">
         <v>14</v>
       </c>
-      <c r="E41" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B42">
-        <v>40</v>
-      </c>
-      <c r="C42" t="s">
-        <v>271</v>
-      </c>
-      <c r="D42" t="s">
-        <v>237</v>
-      </c>
       <c r="E42" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.35">
+        <v>276</v>
+      </c>
+      <c r="F42" t="s">
+        <v>396</v>
+      </c>
+      <c r="G42" t="s">
+        <v>396</v>
+      </c>
+      <c r="H42" t="s">
+        <v>396</v>
+      </c>
+      <c r="I42" t="s">
+        <v>396</v>
+      </c>
+      <c r="J42" t="s">
+        <v>396</v>
+      </c>
+      <c r="K42" t="s">
+        <v>396</v>
+      </c>
+      <c r="L42" t="s">
+        <v>396</v>
+      </c>
+      <c r="M42" t="s">
+        <v>396</v>
+      </c>
+      <c r="N42" t="s">
+        <v>396</v>
+      </c>
+      <c r="O42" t="s">
+        <v>396</v>
+      </c>
+      <c r="P42" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B43">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C43" t="s">
-        <v>271</v>
+        <v>250</v>
       </c>
       <c r="D43" t="s">
+        <v>227</v>
+      </c>
+      <c r="E43" t="s">
+        <v>276</v>
+      </c>
+      <c r="F43" t="s">
+        <v>564</v>
+      </c>
+      <c r="G43" t="s">
+        <v>565</v>
+      </c>
+      <c r="H43" t="s">
+        <v>566</v>
+      </c>
+      <c r="I43" t="s">
+        <v>567</v>
+      </c>
+      <c r="J43" t="s">
+        <v>568</v>
+      </c>
+      <c r="K43" t="s">
+        <v>569</v>
+      </c>
+      <c r="L43" t="s">
+        <v>570</v>
+      </c>
+      <c r="M43" t="s">
+        <v>571</v>
+      </c>
+      <c r="N43" t="s">
+        <v>560</v>
+      </c>
+      <c r="O43" t="s">
+        <v>572</v>
+      </c>
+      <c r="P43" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B44">
+        <v>44</v>
+      </c>
+      <c r="C44" t="s">
+        <v>250</v>
+      </c>
+      <c r="D44" t="s">
+        <v>227</v>
+      </c>
+      <c r="E44" t="s">
+        <v>277</v>
+      </c>
+      <c r="F44" t="s">
+        <v>408</v>
+      </c>
+      <c r="G44" t="s">
+        <v>409</v>
+      </c>
+      <c r="H44" t="s">
+        <v>410</v>
+      </c>
+      <c r="I44" t="s">
+        <v>356</v>
+      </c>
+      <c r="J44" t="s">
+        <v>411</v>
+      </c>
+      <c r="K44" t="s">
+        <v>412</v>
+      </c>
+      <c r="L44" t="s">
+        <v>312</v>
+      </c>
+      <c r="M44" t="s">
+        <v>413</v>
+      </c>
+      <c r="N44" t="s">
+        <v>414</v>
+      </c>
+      <c r="O44" t="s">
+        <v>313</v>
+      </c>
+      <c r="P44" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B45">
+        <v>45</v>
+      </c>
+      <c r="C45" t="s">
+        <v>250</v>
+      </c>
+      <c r="D45" t="s">
+        <v>227</v>
+      </c>
+      <c r="E45" t="s">
+        <v>272</v>
+      </c>
+      <c r="F45" t="s">
+        <v>315</v>
+      </c>
+      <c r="G45" t="s">
+        <v>416</v>
+      </c>
+      <c r="H45" t="s">
+        <v>417</v>
+      </c>
+      <c r="I45" t="s">
+        <v>418</v>
+      </c>
+      <c r="J45" t="s">
+        <v>419</v>
+      </c>
+      <c r="K45" t="s">
+        <v>420</v>
+      </c>
+      <c r="L45" t="s">
+        <v>421</v>
+      </c>
+      <c r="M45" t="s">
+        <v>422</v>
+      </c>
+      <c r="N45" t="s">
+        <v>423</v>
+      </c>
+      <c r="O45" t="s">
+        <v>424</v>
+      </c>
+      <c r="P45" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B46">
+        <v>46</v>
+      </c>
+      <c r="C46" t="s">
+        <v>250</v>
+      </c>
+      <c r="D46" t="s">
         <v>14</v>
       </c>
-      <c r="E43" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B44">
-        <v>42</v>
-      </c>
-      <c r="C44" t="s">
-        <v>271</v>
-      </c>
-      <c r="D44" t="s">
-        <v>237</v>
-      </c>
-      <c r="E44" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B45">
-        <v>43</v>
-      </c>
-      <c r="C45" t="s">
-        <v>271</v>
-      </c>
-      <c r="D45" t="s">
-        <v>14</v>
-      </c>
-      <c r="E45" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.35">
-      <c r="B46">
-        <v>44</v>
-      </c>
-      <c r="C46" t="s">
-        <v>271</v>
-      </c>
-      <c r="D46" t="s">
-        <v>237</v>
-      </c>
       <c r="E46" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.35">
+        <v>278</v>
+      </c>
+      <c r="F46" t="s">
+        <v>396</v>
+      </c>
+      <c r="G46" t="s">
+        <v>396</v>
+      </c>
+      <c r="H46" t="s">
+        <v>396</v>
+      </c>
+      <c r="I46" t="s">
+        <v>396</v>
+      </c>
+      <c r="J46" t="s">
+        <v>396</v>
+      </c>
+      <c r="K46" t="s">
+        <v>396</v>
+      </c>
+      <c r="L46" t="s">
+        <v>396</v>
+      </c>
+      <c r="M46" t="s">
+        <v>396</v>
+      </c>
+      <c r="N46" t="s">
+        <v>396</v>
+      </c>
+      <c r="O46" t="s">
+        <v>396</v>
+      </c>
+      <c r="P46" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B47">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C47" t="s">
-        <v>271</v>
+        <v>250</v>
       </c>
       <c r="D47" t="s">
-        <v>14</v>
+        <v>227</v>
       </c>
       <c r="E47" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.35">
+        <v>278</v>
+      </c>
+      <c r="F47" t="s">
+        <v>396</v>
+      </c>
+      <c r="G47" t="s">
+        <v>396</v>
+      </c>
+      <c r="H47" t="s">
+        <v>396</v>
+      </c>
+      <c r="I47" t="s">
+        <v>396</v>
+      </c>
+      <c r="J47" t="s">
+        <v>396</v>
+      </c>
+      <c r="K47" t="s">
+        <v>396</v>
+      </c>
+      <c r="L47" t="s">
+        <v>396</v>
+      </c>
+      <c r="M47" t="s">
+        <v>396</v>
+      </c>
+      <c r="N47" t="s">
+        <v>396</v>
+      </c>
+      <c r="O47" t="s">
+        <v>396</v>
+      </c>
+      <c r="P47" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B48">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C48" t="s">
-        <v>271</v>
+        <v>250</v>
       </c>
       <c r="D48" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="E48" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.35">
+        <v>279</v>
+      </c>
+      <c r="F48" t="s">
+        <v>309</v>
+      </c>
+      <c r="G48" t="s">
+        <v>425</v>
+      </c>
+      <c r="H48" t="s">
+        <v>426</v>
+      </c>
+      <c r="I48" t="s">
+        <v>427</v>
+      </c>
+      <c r="J48" t="s">
+        <v>311</v>
+      </c>
+      <c r="K48" t="s">
+        <v>428</v>
+      </c>
+      <c r="L48" t="s">
+        <v>429</v>
+      </c>
+      <c r="M48" t="s">
+        <v>310</v>
+      </c>
+      <c r="N48" t="s">
+        <v>430</v>
+      </c>
+      <c r="O48" t="s">
+        <v>431</v>
+      </c>
+      <c r="P48" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="49" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B49">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C49" t="s">
-        <v>271</v>
+        <v>250</v>
       </c>
       <c r="D49" t="s">
         <v>14</v>
       </c>
       <c r="E49" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.35">
+        <v>280</v>
+      </c>
+      <c r="F49" t="s">
+        <v>396</v>
+      </c>
+      <c r="G49" t="s">
+        <v>396</v>
+      </c>
+      <c r="H49" t="s">
+        <v>396</v>
+      </c>
+      <c r="I49" t="s">
+        <v>396</v>
+      </c>
+      <c r="J49" t="s">
+        <v>396</v>
+      </c>
+      <c r="K49" t="s">
+        <v>396</v>
+      </c>
+      <c r="L49" t="s">
+        <v>396</v>
+      </c>
+      <c r="M49" t="s">
+        <v>396</v>
+      </c>
+      <c r="N49" t="s">
+        <v>396</v>
+      </c>
+      <c r="O49" t="s">
+        <v>396</v>
+      </c>
+      <c r="P49" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="50" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B50">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C50" t="s">
-        <v>271</v>
+        <v>250</v>
       </c>
       <c r="D50" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="E50" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.35">
+        <v>280</v>
+      </c>
+      <c r="F50" t="s">
+        <v>396</v>
+      </c>
+      <c r="G50" t="s">
+        <v>396</v>
+      </c>
+      <c r="H50" t="s">
+        <v>396</v>
+      </c>
+      <c r="I50" t="s">
+        <v>396</v>
+      </c>
+      <c r="J50" t="s">
+        <v>396</v>
+      </c>
+      <c r="K50" t="s">
+        <v>396</v>
+      </c>
+      <c r="L50" t="s">
+        <v>396</v>
+      </c>
+      <c r="M50" t="s">
+        <v>396</v>
+      </c>
+      <c r="N50" t="s">
+        <v>396</v>
+      </c>
+      <c r="O50" t="s">
+        <v>396</v>
+      </c>
+      <c r="P50" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="51" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B51">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C51" t="s">
-        <v>271</v>
+        <v>250</v>
       </c>
       <c r="D51" t="s">
+        <v>227</v>
+      </c>
+      <c r="E51" t="s">
+        <v>281</v>
+      </c>
+      <c r="F51" t="s">
+        <v>316</v>
+      </c>
+      <c r="G51" t="s">
+        <v>433</v>
+      </c>
+      <c r="H51" t="s">
+        <v>434</v>
+      </c>
+      <c r="I51" t="s">
+        <v>435</v>
+      </c>
+      <c r="J51" t="s">
+        <v>436</v>
+      </c>
+      <c r="K51" t="s">
+        <v>437</v>
+      </c>
+      <c r="L51" t="s">
+        <v>438</v>
+      </c>
+      <c r="M51" t="s">
+        <v>439</v>
+      </c>
+      <c r="N51" t="s">
+        <v>440</v>
+      </c>
+      <c r="O51" t="s">
+        <v>441</v>
+      </c>
+      <c r="P51" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="52" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B52">
+        <v>52</v>
+      </c>
+      <c r="C52" t="s">
+        <v>250</v>
+      </c>
+      <c r="D52" t="s">
         <v>14</v>
       </c>
-      <c r="E51" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B52">
-        <v>50</v>
-      </c>
-      <c r="C52" t="s">
-        <v>271</v>
-      </c>
-      <c r="D52" t="s">
-        <v>237</v>
-      </c>
       <c r="E52" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.35">
+        <v>270</v>
+      </c>
+      <c r="F52" t="s">
+        <v>396</v>
+      </c>
+      <c r="G52" t="s">
+        <v>396</v>
+      </c>
+      <c r="H52" t="s">
+        <v>396</v>
+      </c>
+      <c r="I52" t="s">
+        <v>396</v>
+      </c>
+      <c r="J52" t="s">
+        <v>396</v>
+      </c>
+      <c r="K52" t="s">
+        <v>396</v>
+      </c>
+      <c r="L52" t="s">
+        <v>396</v>
+      </c>
+      <c r="M52" t="s">
+        <v>396</v>
+      </c>
+      <c r="N52" t="s">
+        <v>396</v>
+      </c>
+      <c r="O52" t="s">
+        <v>396</v>
+      </c>
+      <c r="P52" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="53" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B53">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C53" t="s">
-        <v>271</v>
+        <v>250</v>
       </c>
       <c r="D53" t="s">
+        <v>227</v>
+      </c>
+      <c r="E53" t="s">
+        <v>270</v>
+      </c>
+      <c r="F53" t="s">
+        <v>443</v>
+      </c>
+      <c r="G53" t="s">
+        <v>322</v>
+      </c>
+      <c r="H53" t="s">
+        <v>342</v>
+      </c>
+      <c r="I53" t="s">
+        <v>444</v>
+      </c>
+      <c r="J53" t="s">
+        <v>445</v>
+      </c>
+      <c r="K53" t="s">
+        <v>446</v>
+      </c>
+      <c r="L53" t="s">
+        <v>324</v>
+      </c>
+      <c r="M53" t="s">
+        <v>325</v>
+      </c>
+      <c r="N53" t="s">
+        <v>447</v>
+      </c>
+      <c r="O53" t="s">
+        <v>448</v>
+      </c>
+      <c r="P53" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="54" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B54">
+        <v>54</v>
+      </c>
+      <c r="C54" t="s">
+        <v>250</v>
+      </c>
+      <c r="D54" t="s">
         <v>14</v>
       </c>
-      <c r="E53" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B54">
-        <v>52</v>
-      </c>
-      <c r="C54" t="s">
-        <v>271</v>
-      </c>
-      <c r="D54" t="s">
-        <v>237</v>
-      </c>
       <c r="E54" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.35">
+        <v>282</v>
+      </c>
+      <c r="F54" t="s">
+        <v>396</v>
+      </c>
+      <c r="G54" t="s">
+        <v>396</v>
+      </c>
+      <c r="H54" t="s">
+        <v>396</v>
+      </c>
+      <c r="I54" t="s">
+        <v>396</v>
+      </c>
+      <c r="J54" t="s">
+        <v>396</v>
+      </c>
+      <c r="K54" t="s">
+        <v>396</v>
+      </c>
+      <c r="L54" t="s">
+        <v>396</v>
+      </c>
+      <c r="M54" t="s">
+        <v>396</v>
+      </c>
+      <c r="N54" t="s">
+        <v>396</v>
+      </c>
+      <c r="O54" t="s">
+        <v>396</v>
+      </c>
+      <c r="P54" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="55" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B55">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C55" t="s">
-        <v>271</v>
+        <v>250</v>
       </c>
       <c r="D55" t="s">
+        <v>227</v>
+      </c>
+      <c r="E55" t="s">
+        <v>282</v>
+      </c>
+      <c r="F55" t="s">
+        <v>396</v>
+      </c>
+      <c r="G55" t="s">
+        <v>396</v>
+      </c>
+      <c r="H55" t="s">
+        <v>396</v>
+      </c>
+      <c r="I55" t="s">
+        <v>396</v>
+      </c>
+      <c r="J55" t="s">
+        <v>396</v>
+      </c>
+      <c r="K55" t="s">
+        <v>396</v>
+      </c>
+      <c r="L55" t="s">
+        <v>396</v>
+      </c>
+      <c r="M55" t="s">
+        <v>396</v>
+      </c>
+      <c r="N55" t="s">
+        <v>396</v>
+      </c>
+      <c r="O55" t="s">
+        <v>396</v>
+      </c>
+      <c r="P55" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="56" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B56">
+        <v>56</v>
+      </c>
+      <c r="C56" t="s">
+        <v>250</v>
+      </c>
+      <c r="D56" t="s">
+        <v>227</v>
+      </c>
+      <c r="E56" t="s">
+        <v>283</v>
+      </c>
+      <c r="F56" t="s">
+        <v>449</v>
+      </c>
+      <c r="G56" t="s">
+        <v>450</v>
+      </c>
+      <c r="H56" t="s">
+        <v>451</v>
+      </c>
+      <c r="I56" t="s">
+        <v>318</v>
+      </c>
+      <c r="J56" t="s">
+        <v>452</v>
+      </c>
+      <c r="K56" t="s">
+        <v>453</v>
+      </c>
+      <c r="L56" t="s">
+        <v>454</v>
+      </c>
+      <c r="M56" t="s">
+        <v>455</v>
+      </c>
+      <c r="N56" t="s">
+        <v>456</v>
+      </c>
+      <c r="O56" t="s">
+        <v>457</v>
+      </c>
+      <c r="P56" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="57" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B57">
+        <v>57</v>
+      </c>
+      <c r="C57" t="s">
+        <v>250</v>
+      </c>
+      <c r="D57" t="s">
+        <v>227</v>
+      </c>
+      <c r="E57" t="s">
+        <v>273</v>
+      </c>
+      <c r="F57" t="s">
+        <v>581</v>
+      </c>
+      <c r="G57" t="s">
+        <v>459</v>
+      </c>
+      <c r="H57" t="s">
+        <v>582</v>
+      </c>
+      <c r="I57" t="s">
+        <v>583</v>
+      </c>
+      <c r="J57" t="s">
+        <v>584</v>
+      </c>
+      <c r="K57" t="s">
+        <v>585</v>
+      </c>
+      <c r="L57" t="s">
+        <v>586</v>
+      </c>
+      <c r="M57" t="s">
+        <v>460</v>
+      </c>
+      <c r="N57" t="s">
+        <v>319</v>
+      </c>
+      <c r="O57" t="s">
+        <v>587</v>
+      </c>
+      <c r="P57" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="58" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B58">
+        <v>58</v>
+      </c>
+      <c r="C58" t="s">
+        <v>250</v>
+      </c>
+      <c r="D58" t="s">
         <v>14</v>
       </c>
-      <c r="E55" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B56">
-        <v>54</v>
-      </c>
-      <c r="C56" t="s">
-        <v>271</v>
-      </c>
-      <c r="D56" t="s">
-        <v>237</v>
-      </c>
-      <c r="E56" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B57">
-        <v>55</v>
-      </c>
-      <c r="C57" t="s">
-        <v>271</v>
-      </c>
-      <c r="D57" t="s">
+      <c r="E58" t="s">
+        <v>284</v>
+      </c>
+      <c r="F58" t="s">
+        <v>396</v>
+      </c>
+      <c r="G58" t="s">
+        <v>396</v>
+      </c>
+      <c r="H58" t="s">
+        <v>396</v>
+      </c>
+      <c r="I58" t="s">
+        <v>396</v>
+      </c>
+      <c r="J58" t="s">
+        <v>396</v>
+      </c>
+      <c r="K58" t="s">
+        <v>396</v>
+      </c>
+      <c r="L58" t="s">
+        <v>396</v>
+      </c>
+      <c r="M58" t="s">
+        <v>396</v>
+      </c>
+      <c r="N58" t="s">
+        <v>396</v>
+      </c>
+      <c r="O58" t="s">
+        <v>396</v>
+      </c>
+      <c r="P58" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="59" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B59">
+        <v>59</v>
+      </c>
+      <c r="C59" t="s">
+        <v>250</v>
+      </c>
+      <c r="D59" t="s">
+        <v>227</v>
+      </c>
+      <c r="E59" t="s">
+        <v>284</v>
+      </c>
+      <c r="F59" t="s">
+        <v>396</v>
+      </c>
+      <c r="G59" t="s">
+        <v>396</v>
+      </c>
+      <c r="H59" t="s">
+        <v>396</v>
+      </c>
+      <c r="I59" t="s">
+        <v>396</v>
+      </c>
+      <c r="J59" t="s">
+        <v>396</v>
+      </c>
+      <c r="K59" t="s">
+        <v>396</v>
+      </c>
+      <c r="L59" t="s">
+        <v>396</v>
+      </c>
+      <c r="M59" t="s">
+        <v>396</v>
+      </c>
+      <c r="N59" t="s">
+        <v>396</v>
+      </c>
+      <c r="O59" t="s">
+        <v>396</v>
+      </c>
+      <c r="P59" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="60" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B60">
+        <v>60</v>
+      </c>
+      <c r="C60" t="s">
+        <v>190</v>
+      </c>
+      <c r="D60" t="s">
         <v>14</v>
       </c>
-      <c r="E57" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B58">
-        <v>56</v>
-      </c>
-      <c r="C58" t="s">
-        <v>271</v>
-      </c>
-      <c r="D58" t="s">
-        <v>237</v>
-      </c>
-      <c r="E58" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="59" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B59">
-        <v>57</v>
-      </c>
-      <c r="C59" t="s">
-        <v>271</v>
-      </c>
-      <c r="D59" t="s">
+      <c r="F60" t="s">
+        <v>396</v>
+      </c>
+      <c r="G60" t="s">
+        <v>396</v>
+      </c>
+      <c r="H60" t="s">
+        <v>396</v>
+      </c>
+      <c r="I60" t="s">
+        <v>396</v>
+      </c>
+      <c r="J60" t="s">
+        <v>396</v>
+      </c>
+      <c r="K60" t="s">
+        <v>396</v>
+      </c>
+      <c r="L60" t="s">
+        <v>396</v>
+      </c>
+      <c r="M60" t="s">
+        <v>396</v>
+      </c>
+      <c r="N60" t="s">
+        <v>396</v>
+      </c>
+      <c r="O60" t="s">
+        <v>396</v>
+      </c>
+      <c r="P60" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="61" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B61">
+        <v>61</v>
+      </c>
+      <c r="C61" t="s">
+        <v>190</v>
+      </c>
+      <c r="D61" t="s">
+        <v>227</v>
+      </c>
+      <c r="F61" t="s">
+        <v>396</v>
+      </c>
+      <c r="G61" t="s">
+        <v>396</v>
+      </c>
+      <c r="H61" t="s">
+        <v>396</v>
+      </c>
+      <c r="I61" t="s">
+        <v>396</v>
+      </c>
+      <c r="J61" t="s">
+        <v>396</v>
+      </c>
+      <c r="K61" t="s">
+        <v>396</v>
+      </c>
+      <c r="L61" t="s">
+        <v>396</v>
+      </c>
+      <c r="M61" t="s">
+        <v>396</v>
+      </c>
+      <c r="N61" t="s">
+        <v>396</v>
+      </c>
+      <c r="O61" t="s">
+        <v>396</v>
+      </c>
+      <c r="P61" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="62" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B62">
+        <v>62</v>
+      </c>
+      <c r="C62" t="s">
+        <v>286</v>
+      </c>
+      <c r="D62" t="s">
         <v>14</v>
       </c>
-      <c r="E59" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="60" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B60">
-        <v>58</v>
-      </c>
-      <c r="C60" t="s">
-        <v>271</v>
-      </c>
-      <c r="D60" t="s">
-        <v>237</v>
-      </c>
-      <c r="E60" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="61" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B61">
-        <v>59</v>
-      </c>
-      <c r="C61" t="s">
-        <v>271</v>
-      </c>
-      <c r="D61" t="s">
-        <v>14</v>
-      </c>
-      <c r="E61" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="62" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B62">
-        <v>60</v>
-      </c>
-      <c r="C62" t="s">
-        <v>271</v>
-      </c>
-      <c r="D62" t="s">
-        <v>237</v>
-      </c>
-      <c r="E62" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="63" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="F62" t="s">
+        <v>287</v>
+      </c>
+      <c r="G62" t="s">
+        <v>545</v>
+      </c>
+      <c r="H62" t="s">
+        <v>546</v>
+      </c>
+      <c r="I62" t="s">
+        <v>547</v>
+      </c>
+      <c r="J62" t="s">
+        <v>289</v>
+      </c>
+      <c r="K62" t="s">
+        <v>548</v>
+      </c>
+      <c r="L62" t="s">
+        <v>290</v>
+      </c>
+      <c r="M62" t="s">
+        <v>549</v>
+      </c>
+      <c r="N62" t="s">
+        <v>306</v>
+      </c>
+      <c r="O62" t="s">
+        <v>550</v>
+      </c>
+      <c r="P62" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="63" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B63">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C63" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="D63" t="s">
         <v>14</v>
       </c>
-      <c r="E63" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="64" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="F63" t="s">
+        <v>288</v>
+      </c>
+      <c r="G63" t="s">
+        <v>552</v>
+      </c>
+      <c r="H63" t="s">
+        <v>553</v>
+      </c>
+      <c r="I63" t="s">
+        <v>554</v>
+      </c>
+      <c r="J63" t="s">
+        <v>555</v>
+      </c>
+      <c r="K63" t="s">
+        <v>291</v>
+      </c>
+      <c r="L63" t="s">
+        <v>292</v>
+      </c>
+      <c r="M63" t="s">
+        <v>293</v>
+      </c>
+      <c r="N63" t="s">
+        <v>556</v>
+      </c>
+      <c r="O63" t="s">
+        <v>557</v>
+      </c>
+      <c r="P63" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="64" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B64">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C64" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="D64" t="s">
-        <v>237</v>
-      </c>
-      <c r="E64" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="65" spans="2:5" x14ac:dyDescent="0.35">
+        <v>227</v>
+      </c>
+      <c r="F64" t="s">
+        <v>294</v>
+      </c>
+      <c r="G64" t="s">
+        <v>461</v>
+      </c>
+      <c r="H64" t="s">
+        <v>298</v>
+      </c>
+      <c r="I64" t="s">
+        <v>462</v>
+      </c>
+      <c r="J64" t="s">
+        <v>299</v>
+      </c>
+      <c r="K64" t="s">
+        <v>301</v>
+      </c>
+      <c r="L64" t="s">
+        <v>463</v>
+      </c>
+      <c r="M64" t="s">
+        <v>464</v>
+      </c>
+      <c r="N64" t="s">
+        <v>296</v>
+      </c>
+      <c r="O64" t="s">
+        <v>297</v>
+      </c>
+      <c r="P64" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B65">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C65" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="D65" t="s">
+        <v>227</v>
+      </c>
+      <c r="F65" t="s">
+        <v>295</v>
+      </c>
+      <c r="G65" t="s">
+        <v>465</v>
+      </c>
+      <c r="H65" t="s">
+        <v>466</v>
+      </c>
+      <c r="I65" t="s">
+        <v>467</v>
+      </c>
+      <c r="J65" t="s">
+        <v>468</v>
+      </c>
+      <c r="K65" t="s">
+        <v>304</v>
+      </c>
+      <c r="L65" t="s">
+        <v>305</v>
+      </c>
+      <c r="M65" t="s">
+        <v>469</v>
+      </c>
+      <c r="N65" t="s">
+        <v>470</v>
+      </c>
+      <c r="O65" t="s">
+        <v>303</v>
+      </c>
+      <c r="P65" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B66">
+        <v>66</v>
+      </c>
+      <c r="C66" t="s">
+        <v>159</v>
+      </c>
+      <c r="D66" t="s">
+        <v>589</v>
+      </c>
+      <c r="E66" t="s">
+        <v>590</v>
+      </c>
+      <c r="F66" t="s">
+        <v>396</v>
+      </c>
+      <c r="G66" t="s">
+        <v>396</v>
+      </c>
+      <c r="H66" t="s">
+        <v>396</v>
+      </c>
+      <c r="I66" t="s">
+        <v>396</v>
+      </c>
+      <c r="J66" t="s">
+        <v>396</v>
+      </c>
+      <c r="K66" t="s">
+        <v>396</v>
+      </c>
+      <c r="L66" t="s">
+        <v>396</v>
+      </c>
+      <c r="M66" t="s">
+        <v>396</v>
+      </c>
+      <c r="N66" t="s">
+        <v>396</v>
+      </c>
+      <c r="O66" t="s">
+        <v>396</v>
+      </c>
+      <c r="P66" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B67">
+        <v>67</v>
+      </c>
+      <c r="C67" t="s">
+        <v>159</v>
+      </c>
+      <c r="D67" t="s">
+        <v>227</v>
+      </c>
+      <c r="E67" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B68">
+        <v>68</v>
+      </c>
+      <c r="C68" t="s">
+        <v>159</v>
+      </c>
+      <c r="D68" t="s">
         <v>14</v>
       </c>
-      <c r="E65" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="66" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B66">
-        <v>64</v>
-      </c>
-      <c r="C66" t="s">
-        <v>271</v>
-      </c>
-      <c r="D66" t="s">
-        <v>237</v>
-      </c>
-      <c r="E66" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="67" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B67">
-        <v>65</v>
-      </c>
-      <c r="C67" t="s">
-        <v>271</v>
-      </c>
-      <c r="D67" t="s">
-        <v>14</v>
-      </c>
-      <c r="E67" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="68" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B68">
-        <v>66</v>
-      </c>
-      <c r="C68" t="s">
-        <v>271</v>
-      </c>
-      <c r="D68" t="s">
-        <v>237</v>
-      </c>
       <c r="E68" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="69" spans="2:5" x14ac:dyDescent="0.35">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B69">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C69" t="s">
-        <v>271</v>
+        <v>592</v>
       </c>
       <c r="D69" t="s">
         <v>14</v>
       </c>
       <c r="E69" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="70" spans="2:5" x14ac:dyDescent="0.35">
+        <v>591</v>
+      </c>
+      <c r="T69" t="str">
+        <f>TRIM(T3)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B70">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C70" t="s">
-        <v>271</v>
+        <v>592</v>
       </c>
       <c r="D70" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="E70" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="71" spans="2:5" x14ac:dyDescent="0.35">
+        <v>591</v>
+      </c>
+      <c r="T70" t="str">
+        <f>TRIM(T4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B71">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C71" t="s">
-        <v>271</v>
+        <v>592</v>
       </c>
       <c r="D71" t="s">
         <v>14</v>
       </c>
       <c r="E71" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="72" spans="2:5" x14ac:dyDescent="0.35">
+        <v>593</v>
+      </c>
+      <c r="T71" t="str">
+        <f>TRIM(T5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B72">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C72" t="s">
-        <v>271</v>
+        <v>592</v>
       </c>
       <c r="D72" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="E72" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="73" spans="2:5" x14ac:dyDescent="0.35">
+        <v>593</v>
+      </c>
+      <c r="T72" t="str">
+        <f>TRIM(T6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B73">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C73" t="s">
-        <v>271</v>
+        <v>592</v>
       </c>
       <c r="D73" t="s">
         <v>14</v>
       </c>
       <c r="E73" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="74" spans="2:5" x14ac:dyDescent="0.35">
+        <v>594</v>
+      </c>
+      <c r="T73" t="str">
+        <f>TRIM(T7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B74">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C74" t="s">
-        <v>271</v>
+        <v>592</v>
       </c>
       <c r="D74" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="E74" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="75" spans="2:5" x14ac:dyDescent="0.35">
+        <v>594</v>
+      </c>
+      <c r="T74" t="str">
+        <f>TRIM(T8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B75">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C75" t="s">
-        <v>199</v>
+        <v>592</v>
       </c>
       <c r="D75" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="76" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="E75" t="s">
+        <v>595</v>
+      </c>
+      <c r="T75" t="str">
+        <f>TRIM(T9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B76">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C76" t="s">
-        <v>199</v>
+        <v>592</v>
       </c>
       <c r="D76" t="s">
-        <v>237</v>
+        <v>227</v>
+      </c>
+      <c r="E76" t="s">
+        <v>595</v>
+      </c>
+      <c r="T76" t="str">
+        <f>TRIM(T10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B77">
+        <v>77</v>
+      </c>
+      <c r="C77" t="s">
+        <v>592</v>
+      </c>
+      <c r="D77" t="s">
+        <v>14</v>
+      </c>
+      <c r="E77" t="s">
+        <v>600</v>
+      </c>
+      <c r="T77" t="str">
+        <f>TRIM(T11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B78">
+        <v>78</v>
+      </c>
+      <c r="C78" t="s">
+        <v>592</v>
+      </c>
+      <c r="D78" t="s">
+        <v>227</v>
+      </c>
+      <c r="E78" t="s">
+        <v>600</v>
+      </c>
+      <c r="T78" t="str">
+        <f>TRIM(T12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B79">
+        <v>79</v>
+      </c>
+      <c r="C79" t="s">
+        <v>592</v>
+      </c>
+      <c r="D79" t="s">
+        <v>14</v>
+      </c>
+      <c r="E79" t="s">
+        <v>601</v>
+      </c>
+      <c r="T79" t="str">
+        <f>TRIM(T13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B80">
+        <v>80</v>
+      </c>
+      <c r="C80" t="s">
+        <v>592</v>
+      </c>
+      <c r="D80" t="s">
+        <v>227</v>
+      </c>
+      <c r="E80" t="s">
+        <v>601</v>
+      </c>
+      <c r="T80" t="str">
+        <f>TRIM(T14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B81">
+        <v>81</v>
+      </c>
+      <c r="C81" t="s">
+        <v>592</v>
+      </c>
+      <c r="D81" t="s">
+        <v>14</v>
+      </c>
+      <c r="E81" t="s">
+        <v>602</v>
+      </c>
+      <c r="T81" t="str">
+        <f>TRIM(T15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B82">
+        <v>82</v>
+      </c>
+      <c r="C82" t="s">
+        <v>592</v>
+      </c>
+      <c r="D82" t="s">
+        <v>227</v>
+      </c>
+      <c r="E82" t="s">
+        <v>602</v>
+      </c>
+      <c r="T82" t="str">
+        <f>TRIM(T16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B83">
+        <v>83</v>
+      </c>
+      <c r="C83" t="s">
+        <v>592</v>
+      </c>
+      <c r="D83" t="s">
+        <v>14</v>
+      </c>
+      <c r="E83" t="s">
+        <v>599</v>
+      </c>
+      <c r="T83" t="str">
+        <f>TRIM(T17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B84">
+        <v>84</v>
+      </c>
+      <c r="C84" t="s">
+        <v>592</v>
+      </c>
+      <c r="D84" t="s">
+        <v>227</v>
+      </c>
+      <c r="E84" t="s">
+        <v>599</v>
+      </c>
+      <c r="T84" t="str">
+        <f>TRIM(T18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B85">
+        <v>85</v>
+      </c>
+      <c r="C85" t="s">
+        <v>592</v>
+      </c>
+      <c r="D85" t="s">
+        <v>14</v>
+      </c>
+      <c r="E85" t="s">
+        <v>598</v>
+      </c>
+      <c r="T85" t="str">
+        <f>TRIM(T19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B86">
+        <v>86</v>
+      </c>
+      <c r="C86" t="s">
+        <v>592</v>
+      </c>
+      <c r="D86" t="s">
+        <v>227</v>
+      </c>
+      <c r="E86" t="s">
+        <v>598</v>
+      </c>
+      <c r="T86" t="str">
+        <f>TRIM(T20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B87">
+        <v>87</v>
+      </c>
+      <c r="C87" t="s">
+        <v>592</v>
+      </c>
+      <c r="D87" t="s">
+        <v>14</v>
+      </c>
+      <c r="E87" t="s">
+        <v>597</v>
+      </c>
+      <c r="T87" t="str">
+        <f>TRIM(T21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B88">
+        <v>88</v>
+      </c>
+      <c r="C88" t="s">
+        <v>592</v>
+      </c>
+      <c r="D88" t="s">
+        <v>227</v>
+      </c>
+      <c r="E88" t="s">
+        <v>597</v>
+      </c>
+      <c r="T88" t="str">
+        <f>TRIM(T22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B89">
+        <v>89</v>
+      </c>
+      <c r="C89" t="s">
+        <v>592</v>
+      </c>
+      <c r="D89" t="s">
+        <v>14</v>
+      </c>
+      <c r="E89" t="s">
+        <v>596</v>
+      </c>
+      <c r="T89" t="str">
+        <f>TRIM(T23)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B90">
+        <v>90</v>
+      </c>
+      <c r="C90" t="s">
+        <v>592</v>
+      </c>
+      <c r="D90" t="s">
+        <v>227</v>
+      </c>
+      <c r="E90" t="s">
+        <v>596</v>
+      </c>
+      <c r="T90" t="str">
+        <f>TRIM(T24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B91">
+        <v>91</v>
+      </c>
+      <c r="C91" t="s">
+        <v>603</v>
+      </c>
+      <c r="D91" t="s">
+        <v>227</v>
+      </c>
+      <c r="E91" t="s">
+        <v>592</v>
+      </c>
+      <c r="T91" t="str">
+        <f>TRIM(T25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B92">
+        <v>92</v>
+      </c>
+      <c r="C92" t="s">
+        <v>603</v>
+      </c>
+      <c r="D92" t="s">
+        <v>14</v>
+      </c>
+      <c r="E92" t="s">
+        <v>592</v>
+      </c>
+      <c r="T92" t="str">
+        <f>TRIM(T26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B93">
+        <v>93</v>
+      </c>
+      <c r="D93" t="s">
+        <v>604</v>
+      </c>
+      <c r="T93" t="str">
+        <f>TRIM(T27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B94">
+        <v>95</v>
+      </c>
+      <c r="D94" t="s">
+        <v>604</v>
+      </c>
+      <c r="T94" t="str">
+        <f>TRIM(T28)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="T95" t="str">
+        <f>TRIM(T29)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="T96" t="str">
+        <f>TRIM(T30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T97" t="str">
+        <f>TRIM(T31)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T98" t="str">
+        <f>TRIM(T32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T99" t="str">
+        <f>TRIM(T33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T100" t="str">
+        <f>TRIM(T34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T101" t="str">
+        <f>TRIM(T35)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T102" t="str">
+        <f>TRIM(T36)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T103" t="str">
+        <f>TRIM(T37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T104" t="str">
+        <f>TRIM(T38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T105" t="str">
+        <f>TRIM(T39)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T106" t="str">
+        <f>TRIM(T40)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T107" t="str">
+        <f>TRIM(T41)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T108" t="e">
+        <f>TRIM(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="109" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T109" t="str">
+        <f t="shared" ref="T109:T114" si="0">TRIM(T42)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T110" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="111" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T111" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="112" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T112" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="113" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T113" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="114" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T114" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="115" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T115" t="str">
+        <f t="shared" ref="T115:T130" si="1">TRIM(T48)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T116" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="117" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T117" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="118" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T118" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="119" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T119" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="120" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T120" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="121" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T121" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="122" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T122" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="123" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T123" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="124" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T124" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="125" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T125" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="126" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T126" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="127" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T127" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="128" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T128" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="129" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T129" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="130" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T130" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="131" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T131" t="str">
+        <f t="shared" ref="T131:T133" si="2">TRIM(T64)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="132" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T132" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="133" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T133" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="134" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T134" t="str">
+        <f t="shared" ref="T134:T149" si="3">TRIM(T67)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="135" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T135" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="136" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T136" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="137" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T137" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="138" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T138" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="139" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T139" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="140" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T140" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="141" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T141" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="142" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T142" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="143" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T143" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="144" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T144" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="145" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T145" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="146" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T146" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="147" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T147" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="148" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T148" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="149" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T149" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="150" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T150" t="str">
+        <f t="shared" ref="T150:T156" si="4">TRIM(T83)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="151" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T151" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="152" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T152" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="153" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T153" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="154" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T154" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="155" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T155" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="156" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T156" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="157" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T157" t="str">
+        <f t="shared" ref="T157" si="5">TRIM(T90)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="158" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T158" t="str">
+        <f t="shared" ref="T158:T163" si="6">TRIM(T91)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="159" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T159" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="160" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T160" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="161" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T161" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="162" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T162" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="163" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T163" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+    </row>
+    <row r="164" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T164" t="str">
+        <f t="shared" ref="T164" si="7">TRIM(T97)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="165" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T165" t="str">
+        <f t="shared" ref="T165:T173" si="8">TRIM(T98)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="166" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T166" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="167" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T167" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="168" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T168" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="169" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T169" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="170" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T170" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="171" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T171" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="172" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T172" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="173" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T173" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="174" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T174" t="str">
+        <f t="shared" ref="T174" si="9">TRIM(T107)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="175" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T175" t="e">
+        <f t="shared" ref="T175:T177" si="10">TRIM(T108)</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="176" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T176" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+    </row>
+    <row r="177" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T177" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+    </row>
+    <row r="178" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T178" t="str">
+        <f t="shared" ref="T178" si="11">TRIM(T111)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="179" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T179" t="str">
+        <f t="shared" ref="T179:T189" si="12">TRIM(T112)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="180" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T180" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="181" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T181" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="182" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T182" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="183" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T183" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="184" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T184" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="185" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T185" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="186" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T186" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="187" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T187" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="188" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T188" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="189" spans="20:20" x14ac:dyDescent="0.35">
+      <c r="T189" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="233" spans="6:16" x14ac:dyDescent="0.35">
+      <c r="F233" t="str">
+        <f>TRIM(F166)</f>
+        <v/>
+      </c>
+      <c r="G233" t="str">
+        <f>TRIM(G166)</f>
+        <v/>
+      </c>
+      <c r="H233" t="str">
+        <f>TRIM(H166)</f>
+        <v/>
+      </c>
+      <c r="I233" t="str">
+        <f>TRIM(I166)</f>
+        <v/>
+      </c>
+      <c r="J233" t="str">
+        <f>TRIM(J166)</f>
+        <v/>
+      </c>
+      <c r="K233" t="str">
+        <f>TRIM(K166)</f>
+        <v/>
+      </c>
+      <c r="L233" t="str">
+        <f>TRIM(L166)</f>
+        <v/>
+      </c>
+      <c r="M233" t="str">
+        <f>TRIM(M166)</f>
+        <v/>
+      </c>
+      <c r="N233" t="str">
+        <f>TRIM(N166)</f>
+        <v/>
+      </c>
+      <c r="O233" t="str">
+        <f>TRIM(O166)</f>
+        <v/>
+      </c>
+      <c r="P233" t="str">
+        <f>TRIM(P166)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="234" spans="6:16" x14ac:dyDescent="0.35">
+      <c r="F234" t="str">
+        <f>TRIM(F167)</f>
+        <v/>
+      </c>
+      <c r="G234" t="str">
+        <f>TRIM(G167)</f>
+        <v/>
+      </c>
+      <c r="H234" t="str">
+        <f>TRIM(H167)</f>
+        <v/>
+      </c>
+      <c r="I234" t="str">
+        <f>TRIM(I167)</f>
+        <v/>
+      </c>
+      <c r="J234" t="str">
+        <f>TRIM(J167)</f>
+        <v/>
+      </c>
+      <c r="K234" t="str">
+        <f>TRIM(K167)</f>
+        <v/>
+      </c>
+      <c r="L234" t="str">
+        <f>TRIM(L167)</f>
+        <v/>
+      </c>
+      <c r="M234" t="str">
+        <f>TRIM(M167)</f>
+        <v/>
+      </c>
+      <c r="N234" t="str">
+        <f>TRIM(N167)</f>
+        <v/>
+      </c>
+      <c r="O234" t="str">
+        <f>TRIM(O167)</f>
+        <v/>
+      </c>
+      <c r="P234" t="str">
+        <f>TRIM(P167)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="235" spans="6:16" x14ac:dyDescent="0.35">
+      <c r="F235" t="str">
+        <f>TRIM(F168)</f>
+        <v/>
+      </c>
+      <c r="G235" t="str">
+        <f>TRIM(G168)</f>
+        <v/>
+      </c>
+      <c r="H235" t="str">
+        <f>TRIM(H168)</f>
+        <v/>
+      </c>
+      <c r="I235" t="str">
+        <f>TRIM(I168)</f>
+        <v/>
+      </c>
+      <c r="J235" t="str">
+        <f>TRIM(J168)</f>
+        <v/>
+      </c>
+      <c r="K235" t="str">
+        <f>TRIM(K168)</f>
+        <v/>
+      </c>
+      <c r="L235" t="str">
+        <f>TRIM(L168)</f>
+        <v/>
+      </c>
+      <c r="M235" t="str">
+        <f>TRIM(M168)</f>
+        <v/>
+      </c>
+      <c r="N235" t="str">
+        <f>TRIM(N168)</f>
+        <v/>
+      </c>
+      <c r="O235" t="str">
+        <f>TRIM(O168)</f>
+        <v/>
+      </c>
+      <c r="P235" t="str">
+        <f>TRIM(P168)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="236" spans="6:16" x14ac:dyDescent="0.35">
+      <c r="F236" t="str">
+        <f>TRIM(F169)</f>
+        <v/>
+      </c>
+      <c r="G236" t="str">
+        <f>TRIM(G169)</f>
+        <v/>
+      </c>
+      <c r="H236" t="str">
+        <f>TRIM(H169)</f>
+        <v/>
+      </c>
+      <c r="I236" t="str">
+        <f>TRIM(I169)</f>
+        <v/>
+      </c>
+      <c r="J236" t="str">
+        <f>TRIM(J169)</f>
+        <v/>
+      </c>
+      <c r="K236" t="str">
+        <f>TRIM(K169)</f>
+        <v/>
+      </c>
+      <c r="L236" t="str">
+        <f>TRIM(L169)</f>
+        <v/>
+      </c>
+      <c r="M236" t="str">
+        <f>TRIM(M169)</f>
+        <v/>
+      </c>
+      <c r="N236" t="str">
+        <f>TRIM(N169)</f>
+        <v/>
+      </c>
+      <c r="O236" t="str">
+        <f>TRIM(O169)</f>
+        <v/>
+      </c>
+      <c r="P236" t="str">
+        <f>TRIM(P169)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="237" spans="6:16" x14ac:dyDescent="0.35">
+      <c r="F237" t="str">
+        <f>TRIM(F170)</f>
+        <v/>
+      </c>
+      <c r="G237" t="str">
+        <f>TRIM(G170)</f>
+        <v/>
+      </c>
+      <c r="H237" t="str">
+        <f>TRIM(H170)</f>
+        <v/>
+      </c>
+      <c r="I237" t="str">
+        <f>TRIM(I170)</f>
+        <v/>
+      </c>
+      <c r="J237" t="str">
+        <f>TRIM(J170)</f>
+        <v/>
+      </c>
+      <c r="K237" t="str">
+        <f>TRIM(K170)</f>
+        <v/>
+      </c>
+      <c r="L237" t="str">
+        <f>TRIM(L170)</f>
+        <v/>
+      </c>
+      <c r="M237" t="str">
+        <f>TRIM(M170)</f>
+        <v/>
+      </c>
+      <c r="N237" t="str">
+        <f>TRIM(N170)</f>
+        <v/>
+      </c>
+      <c r="O237" t="str">
+        <f>TRIM(O170)</f>
+        <v/>
+      </c>
+      <c r="P237" t="str">
+        <f>TRIM(P170)</f>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/Daily challenge drafts.xlsx
+++ b/Daily challenge drafts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kurtl\Desktop\statstreaks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01E8FB4C-49AB-4D47-8A2D-7772D36FC0CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3DDD99B-FB1C-4406-BE03-8DB8E61E64A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{09488A7D-DFB6-4DD5-964F-0B9C4180CBFA}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="10170" xr2:uid="{09488A7D-DFB6-4DD5-964F-0B9C4180CBFA}"/>
   </bookViews>
   <sheets>
     <sheet name="Mine" sheetId="3" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="985" uniqueCount="605">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1007" uniqueCount="627">
   <si>
     <t>#</t>
   </si>
@@ -1854,6 +1854,72 @@
   </si>
   <si>
     <t>Transfer fee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thierry Henry 229 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Cesc Fàbregas 57 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Pierre‑Emerick Aubameyang 92 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Freddie Ljungberg 72 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Alexandre Lacazette 71 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Aaron Ramsey 64 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Jack Wilshere 14</t>
+  </si>
+  <si>
+    <t>Patrick Vieira - 32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mesut Ozil 44 </t>
+  </si>
+  <si>
+    <t>David Luiz - 4</t>
+  </si>
+  <si>
+    <t>Mikel Arteta 16</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Christian Eriksen 69 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Gareth Bale 72 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Dimitar Berbatov 46 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Érik Lamela 37 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Luka Modric 17</t>
+  </si>
+  <si>
+    <t>Son Heung-min - 173</t>
+  </si>
+  <si>
+    <t>Teddy Sheringham - 125</t>
+  </si>
+  <si>
+    <t>Gary Lineker 80</t>
+  </si>
+  <si>
+    <t>Peter Crouch - 24</t>
+  </si>
+  <si>
+    <t>Jermaine Jenas 26</t>
+  </si>
+  <si>
+    <t>Dele Alli 67</t>
   </si>
 </sst>
 </file>
@@ -5356,7 +5422,7 @@
         <v>591</v>
       </c>
       <c r="T69" t="str">
-        <f>TRIM(T3)</f>
+        <f t="shared" ref="T69:T107" si="0">TRIM(T3)</f>
         <v/>
       </c>
     </row>
@@ -5374,7 +5440,7 @@
         <v>591</v>
       </c>
       <c r="T70" t="str">
-        <f>TRIM(T4)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -5392,7 +5458,7 @@
         <v>593</v>
       </c>
       <c r="T71" t="str">
-        <f>TRIM(T5)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -5410,7 +5476,7 @@
         <v>593</v>
       </c>
       <c r="T72" t="str">
-        <f>TRIM(T6)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -5427,8 +5493,41 @@
       <c r="E73" t="s">
         <v>594</v>
       </c>
+      <c r="F73" t="s">
+        <v>605</v>
+      </c>
+      <c r="G73" t="s">
+        <v>606</v>
+      </c>
+      <c r="H73" t="s">
+        <v>607</v>
+      </c>
+      <c r="I73" t="s">
+        <v>608</v>
+      </c>
+      <c r="J73" t="s">
+        <v>609</v>
+      </c>
+      <c r="K73" t="s">
+        <v>610</v>
+      </c>
+      <c r="L73" t="s">
+        <v>612</v>
+      </c>
+      <c r="M73" t="s">
+        <v>613</v>
+      </c>
+      <c r="N73" t="s">
+        <v>614</v>
+      </c>
+      <c r="O73" t="s">
+        <v>615</v>
+      </c>
+      <c r="P73" t="s">
+        <v>611</v>
+      </c>
       <c r="T73" t="str">
-        <f>TRIM(T7)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -5446,7 +5545,7 @@
         <v>594</v>
       </c>
       <c r="T74" t="str">
-        <f>TRIM(T8)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -5464,7 +5563,7 @@
         <v>595</v>
       </c>
       <c r="T75" t="str">
-        <f>TRIM(T9)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -5482,7 +5581,7 @@
         <v>595</v>
       </c>
       <c r="T76" t="str">
-        <f>TRIM(T10)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -5500,7 +5599,7 @@
         <v>600</v>
       </c>
       <c r="T77" t="str">
-        <f>TRIM(T11)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -5518,7 +5617,7 @@
         <v>600</v>
       </c>
       <c r="T78" t="str">
-        <f>TRIM(T12)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -5535,8 +5634,41 @@
       <c r="E79" t="s">
         <v>601</v>
       </c>
+      <c r="F79" t="s">
+        <v>621</v>
+      </c>
+      <c r="G79" t="s">
+        <v>616</v>
+      </c>
+      <c r="H79" t="s">
+        <v>617</v>
+      </c>
+      <c r="I79" t="s">
+        <v>622</v>
+      </c>
+      <c r="J79" t="s">
+        <v>623</v>
+      </c>
+      <c r="K79" t="s">
+        <v>618</v>
+      </c>
+      <c r="L79" t="s">
+        <v>626</v>
+      </c>
+      <c r="M79" t="s">
+        <v>619</v>
+      </c>
+      <c r="N79" t="s">
+        <v>625</v>
+      </c>
+      <c r="O79" t="s">
+        <v>624</v>
+      </c>
+      <c r="P79" t="s">
+        <v>620</v>
+      </c>
       <c r="T79" t="str">
-        <f>TRIM(T13)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -5554,7 +5686,7 @@
         <v>601</v>
       </c>
       <c r="T80" t="str">
-        <f>TRIM(T14)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -5572,7 +5704,7 @@
         <v>602</v>
       </c>
       <c r="T81" t="str">
-        <f>TRIM(T15)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -5590,7 +5722,7 @@
         <v>602</v>
       </c>
       <c r="T82" t="str">
-        <f>TRIM(T16)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -5608,7 +5740,7 @@
         <v>599</v>
       </c>
       <c r="T83" t="str">
-        <f>TRIM(T17)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -5626,7 +5758,7 @@
         <v>599</v>
       </c>
       <c r="T84" t="str">
-        <f>TRIM(T18)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -5644,7 +5776,7 @@
         <v>598</v>
       </c>
       <c r="T85" t="str">
-        <f>TRIM(T19)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -5662,7 +5794,7 @@
         <v>598</v>
       </c>
       <c r="T86" t="str">
-        <f>TRIM(T20)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -5680,7 +5812,7 @@
         <v>597</v>
       </c>
       <c r="T87" t="str">
-        <f>TRIM(T21)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -5698,7 +5830,7 @@
         <v>597</v>
       </c>
       <c r="T88" t="str">
-        <f>TRIM(T22)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -5716,7 +5848,7 @@
         <v>596</v>
       </c>
       <c r="T89" t="str">
-        <f>TRIM(T23)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -5734,7 +5866,7 @@
         <v>596</v>
       </c>
       <c r="T90" t="str">
-        <f>TRIM(T24)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -5752,7 +5884,7 @@
         <v>592</v>
       </c>
       <c r="T91" t="str">
-        <f>TRIM(T25)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -5770,7 +5902,7 @@
         <v>592</v>
       </c>
       <c r="T92" t="str">
-        <f>TRIM(T26)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -5782,7 +5914,7 @@
         <v>604</v>
       </c>
       <c r="T93" t="str">
-        <f>TRIM(T27)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
@@ -5794,807 +5926,801 @@
         <v>604</v>
       </c>
       <c r="T94" t="str">
-        <f>TRIM(T28)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="95" spans="2:20" x14ac:dyDescent="0.35">
       <c r="T95" t="str">
-        <f>TRIM(T29)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="96" spans="2:20" x14ac:dyDescent="0.35">
       <c r="T96" t="str">
-        <f>TRIM(T30)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="97" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T97" t="str">
-        <f>TRIM(T31)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="98" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T98" t="str">
-        <f>TRIM(T32)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="99" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T99" t="str">
-        <f>TRIM(T33)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="100" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T100" t="str">
-        <f>TRIM(T34)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="101" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T101" t="str">
-        <f>TRIM(T35)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="102" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T102" t="str">
-        <f>TRIM(T36)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="103" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T103" t="str">
-        <f>TRIM(T37)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="104" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T104" t="str">
-        <f>TRIM(T38)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="105" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T105" t="str">
-        <f>TRIM(T39)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="106" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T106" t="str">
-        <f>TRIM(T40)</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="107" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T107" t="str">
-        <f>TRIM(T41)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="108" spans="20:20" x14ac:dyDescent="0.35">
-      <c r="T108" t="e">
-        <f>TRIM(#REF!)</f>
-        <v>#REF!</v>
+        <f t="shared" si="0"/>
+        <v/>
       </c>
     </row>
     <row r="109" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T109" t="str">
-        <f t="shared" ref="T109:T114" si="0">TRIM(T42)</f>
+        <f t="shared" ref="T109:T114" si="1">TRIM(T42)</f>
         <v/>
       </c>
     </row>
     <row r="110" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T110" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="111" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T111" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="112" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T112" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="113" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T113" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="114" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T114" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
     <row r="115" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T115" t="str">
-        <f t="shared" ref="T115:T130" si="1">TRIM(T48)</f>
+        <f t="shared" ref="T115:T130" si="2">TRIM(T48)</f>
         <v/>
       </c>
     </row>
     <row r="116" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T116" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="117" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T117" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="118" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T118" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="119" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T119" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="120" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T120" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="121" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T121" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="122" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T122" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="123" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T123" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="124" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T124" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="125" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T125" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="126" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T126" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="127" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T127" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="128" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T128" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="129" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T129" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="130" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T130" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="131" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T131" t="str">
-        <f t="shared" ref="T131:T133" si="2">TRIM(T64)</f>
+        <f t="shared" ref="T131:T133" si="3">TRIM(T64)</f>
         <v/>
       </c>
     </row>
     <row r="132" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T132" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="133" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T133" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="134" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T134" t="str">
-        <f t="shared" ref="T134:T149" si="3">TRIM(T67)</f>
+        <f t="shared" ref="T134:T149" si="4">TRIM(T67)</f>
         <v/>
       </c>
     </row>
     <row r="135" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T135" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="136" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T136" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="137" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T137" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="138" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T138" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="139" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T139" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="140" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T140" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="141" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T141" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="142" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T142" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="143" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T143" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="144" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T144" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="145" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T145" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="146" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T146" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="147" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T147" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="148" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T148" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="149" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T149" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="150" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T150" t="str">
-        <f t="shared" ref="T150:T156" si="4">TRIM(T83)</f>
+        <f t="shared" ref="T150:T156" si="5">TRIM(T83)</f>
         <v/>
       </c>
     </row>
     <row r="151" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T151" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="152" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T152" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="153" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T153" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="154" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T154" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="155" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T155" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="156" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T156" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="157" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T157" t="str">
-        <f t="shared" ref="T157" si="5">TRIM(T90)</f>
+        <f t="shared" ref="T157" si="6">TRIM(T90)</f>
         <v/>
       </c>
     </row>
     <row r="158" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T158" t="str">
-        <f t="shared" ref="T158:T163" si="6">TRIM(T91)</f>
+        <f t="shared" ref="T158:T163" si="7">TRIM(T91)</f>
         <v/>
       </c>
     </row>
     <row r="159" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T159" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="160" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T160" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="161" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T161" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="162" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T162" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="163" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T163" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
     <row r="164" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T164" t="str">
-        <f t="shared" ref="T164" si="7">TRIM(T97)</f>
+        <f t="shared" ref="T164" si="8">TRIM(T97)</f>
         <v/>
       </c>
     </row>
     <row r="165" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T165" t="str">
-        <f t="shared" ref="T165:T173" si="8">TRIM(T98)</f>
+        <f t="shared" ref="T165:T173" si="9">TRIM(T98)</f>
         <v/>
       </c>
     </row>
     <row r="166" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T166" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="167" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T167" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="168" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T168" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="169" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T169" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="170" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T170" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="171" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T171" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="172" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T172" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="173" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T173" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
     <row r="174" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T174" t="str">
-        <f t="shared" ref="T174" si="9">TRIM(T107)</f>
+        <f t="shared" ref="T174" si="10">TRIM(T107)</f>
         <v/>
       </c>
     </row>
     <row r="175" spans="20:20" x14ac:dyDescent="0.35">
-      <c r="T175" t="e">
-        <f t="shared" ref="T175:T177" si="10">TRIM(T108)</f>
-        <v>#REF!</v>
+      <c r="T175" t="str">
+        <f t="shared" ref="T175:T177" si="11">TRIM(T108)</f>
+        <v/>
       </c>
     </row>
     <row r="176" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T176" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="177" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T177" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
     <row r="178" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T178" t="str">
-        <f t="shared" ref="T178" si="11">TRIM(T111)</f>
+        <f t="shared" ref="T178" si="12">TRIM(T111)</f>
         <v/>
       </c>
     </row>
     <row r="179" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T179" t="str">
-        <f t="shared" ref="T179:T189" si="12">TRIM(T112)</f>
+        <f t="shared" ref="T179:T189" si="13">TRIM(T112)</f>
         <v/>
       </c>
     </row>
     <row r="180" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T180" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
     <row r="181" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T181" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
     <row r="182" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T182" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
     <row r="183" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T183" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
     <row r="184" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T184" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
     <row r="185" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T185" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
     <row r="186" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T186" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
     <row r="187" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T187" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
     <row r="188" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T188" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
     <row r="189" spans="20:20" x14ac:dyDescent="0.35">
       <c r="T189" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
     <row r="233" spans="6:16" x14ac:dyDescent="0.35">
       <c r="F233" t="str">
-        <f>TRIM(F166)</f>
+        <f t="shared" ref="F233:P233" si="14">TRIM(F166)</f>
         <v/>
       </c>
       <c r="G233" t="str">
-        <f>TRIM(G166)</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="H233" t="str">
-        <f>TRIM(H166)</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="I233" t="str">
-        <f>TRIM(I166)</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J233" t="str">
-        <f>TRIM(J166)</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K233" t="str">
-        <f>TRIM(K166)</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="L233" t="str">
-        <f>TRIM(L166)</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="M233" t="str">
-        <f>TRIM(M166)</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="N233" t="str">
-        <f>TRIM(N166)</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="O233" t="str">
-        <f>TRIM(O166)</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="P233" t="str">
-        <f>TRIM(P166)</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="234" spans="6:16" x14ac:dyDescent="0.35">
       <c r="F234" t="str">
-        <f>TRIM(F167)</f>
+        <f t="shared" ref="F234:P234" si="15">TRIM(F167)</f>
         <v/>
       </c>
       <c r="G234" t="str">
-        <f>TRIM(G167)</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="H234" t="str">
-        <f>TRIM(H167)</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="I234" t="str">
-        <f>TRIM(I167)</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J234" t="str">
-        <f>TRIM(J167)</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K234" t="str">
-        <f>TRIM(K167)</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="L234" t="str">
-        <f>TRIM(L167)</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="M234" t="str">
-        <f>TRIM(M167)</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="N234" t="str">
-        <f>TRIM(N167)</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="O234" t="str">
-        <f>TRIM(O167)</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="P234" t="str">
-        <f>TRIM(P167)</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
     </row>
     <row r="235" spans="6:16" x14ac:dyDescent="0.35">
       <c r="F235" t="str">
-        <f>TRIM(F168)</f>
+        <f t="shared" ref="F235:P235" si="16">TRIM(F168)</f>
         <v/>
       </c>
       <c r="G235" t="str">
-        <f>TRIM(G168)</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="H235" t="str">
-        <f>TRIM(H168)</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="I235" t="str">
-        <f>TRIM(I168)</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J235" t="str">
-        <f>TRIM(J168)</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K235" t="str">
-        <f>TRIM(K168)</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="L235" t="str">
-        <f>TRIM(L168)</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="M235" t="str">
-        <f>TRIM(M168)</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="N235" t="str">
-        <f>TRIM(N168)</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="O235" t="str">
-        <f>TRIM(O168)</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="P235" t="str">
-        <f>TRIM(P168)</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
     </row>
     <row r="236" spans="6:16" x14ac:dyDescent="0.35">
       <c r="F236" t="str">
-        <f>TRIM(F169)</f>
+        <f t="shared" ref="F236:P236" si="17">TRIM(F169)</f>
         <v/>
       </c>
       <c r="G236" t="str">
-        <f>TRIM(G169)</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H236" t="str">
-        <f>TRIM(H169)</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="I236" t="str">
-        <f>TRIM(I169)</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="J236" t="str">
-        <f>TRIM(J169)</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K236" t="str">
-        <f>TRIM(K169)</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="L236" t="str">
-        <f>TRIM(L169)</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="M236" t="str">
-        <f>TRIM(M169)</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="N236" t="str">
-        <f>TRIM(N169)</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="O236" t="str">
-        <f>TRIM(O169)</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P236" t="str">
-        <f>TRIM(P169)</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="237" spans="6:16" x14ac:dyDescent="0.35">
       <c r="F237" t="str">
-        <f>TRIM(F170)</f>
+        <f t="shared" ref="F237:P237" si="18">TRIM(F170)</f>
         <v/>
       </c>
       <c r="G237" t="str">
-        <f>TRIM(G170)</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="H237" t="str">
-        <f>TRIM(H170)</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="I237" t="str">
-        <f>TRIM(I170)</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="J237" t="str">
-        <f>TRIM(J170)</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="K237" t="str">
-        <f>TRIM(K170)</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="L237" t="str">
-        <f>TRIM(L170)</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="M237" t="str">
-        <f>TRIM(M170)</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="N237" t="str">
-        <f>TRIM(N170)</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="O237" t="str">
-        <f>TRIM(O170)</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="P237" t="str">
-        <f>TRIM(P170)</f>
+        <f t="shared" si="18"/>
         <v/>
       </c>
     </row>

--- a/Daily challenge drafts.xlsx
+++ b/Daily challenge drafts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kurtl\Desktop\statstreaks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3DDD99B-FB1C-4406-BE03-8DB8E61E64A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F915D6EC-2C82-49A7-BA69-945227CA14AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="10170" xr2:uid="{09488A7D-DFB6-4DD5-964F-0B9C4180CBFA}"/>
   </bookViews>

--- a/Daily challenge drafts.xlsx
+++ b/Daily challenge drafts.xlsx
@@ -2,18 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kurtl\Desktop\statstreaks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4357F335-BEB6-463D-9AFA-19C66E0A3ABE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DCE4178-DEF3-4CF4-8216-DB5B5D3E9BB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{09488A7D-DFB6-4DD5-964F-0B9C4180CBFA}"/>
   </bookViews>
   <sheets>
     <sheet name="Mine" sheetId="3" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1240" uniqueCount="901">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1300" uniqueCount="959">
   <si>
     <t>Stat</t>
   </si>
@@ -2742,6 +2743,180 @@
   </si>
   <si>
     <t>David Beckham 0</t>
+  </si>
+  <si>
+    <t>International caps</t>
+  </si>
+  <si>
+    <t>UCL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">welsh </t>
+  </si>
+  <si>
+    <t>man u goal</t>
+  </si>
+  <si>
+    <t>Nottingham Forest</t>
+  </si>
+  <si>
+    <t>italian</t>
+  </si>
+  <si>
+    <t>forest goals</t>
+  </si>
+  <si>
+    <t>pl apps</t>
+  </si>
+  <si>
+    <t>newcastle apps</t>
+  </si>
+  <si>
+    <t>Newcastle</t>
+  </si>
+  <si>
+    <t>for assists</t>
+  </si>
+  <si>
+    <t>everton apps</t>
+  </si>
+  <si>
+    <t>spurs goals (19/5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stan Collymore 37 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Nigel Clough 385 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Roy Keane 40 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> John Robertson 350 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Steve Stone 118 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ian Bowyer 564 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Peter Shilton 272 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Stuart Pearce 522 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mark Crossley 352 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Viv Anderson 425 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Des Walker 379</t>
+  </si>
+  <si>
+    <t>Everton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patrick Kluivert 25 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Shola Ameobi 398 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Craig Bellamy 119 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Shay Given 463 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Jonas Gutiérrez 180 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Rob Lee 381 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Nicky Butt 152 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Fabricio Coloccini 273 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Kieron Dyer 222 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Steven Taylor 268 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Tim Krul 182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">James Rodríguez 26 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Tim Howard 414 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Wayne Rooney 117 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Leighton Baines 420 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mikel Arteta 174 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Leon Osman 433 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Andrei Kanchelskis 60 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Phil Jagielka 385 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Steven Pienaar 229 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Joseph Yobo 259 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Tim Cahill 278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diego Forlán 17 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Alexis Sánchez 5 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ruud van Nistelrooy 150 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Nemanja Vidić 21 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Wayne Rooney 253 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Park Ji‑sung 27 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Cristiano Ronaldo 145 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> David Beckham 85 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ryan Giggs 168 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Paul Scholes 155 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ole Gunnar Solskjær 126</t>
   </si>
 </sst>
 </file>
@@ -2777,12 +2952,18 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -2797,7 +2978,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -2807,6 +2988,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3305,7 +3489,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4D10FEC-F30E-46F2-B39D-480DD703DE99}">
-  <dimension ref="B2:P245"/>
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A2:P245"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.7265625" style="1"/>
@@ -3326,7 +3511,7 @@
     <col min="17" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
         <v>698</v>
       </c>
@@ -3373,7 +3558,10 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
       <c r="B3" s="2">
         <v>45406</v>
       </c>
@@ -3420,12 +3608,15 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
       <c r="B4" s="2">
         <v>46137</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>12</v>
+        <v>586</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>224</v>
@@ -3467,12 +3658,15 @@
         <v>678</v>
       </c>
     </row>
-    <row r="5" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
       <c r="B5" s="2">
         <v>46138</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>12</v>
+        <v>586</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>224</v>
@@ -3514,59 +3708,65 @@
         <v>693</v>
       </c>
     </row>
-    <row r="6" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
       <c r="B6" s="2">
         <v>46139</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>12</v>
+        <v>586</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>145</v>
+        <v>585</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>149</v>
+        <v>957</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>150</v>
+        <v>952</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>151</v>
+        <v>954</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>155</v>
+        <v>950</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>153</v>
+        <v>953</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>154</v>
+        <v>955</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>152</v>
+        <v>956</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>148</v>
+        <v>958</v>
+      </c>
+      <c r="N6" t="s">
+        <v>948</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>147</v>
+        <v>951</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.35">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
       <c r="B7" s="2">
         <v>46140</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>12</v>
+        <v>586</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>224</v>
@@ -3608,12 +3808,15 @@
         <v>720</v>
       </c>
     </row>
-    <row r="8" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
       <c r="B8" s="2">
         <v>46141</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>12</v>
+        <v>586</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>224</v>
@@ -3655,60 +3858,63 @@
         <v>730</v>
       </c>
     </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="1">
+        <v>7</v>
+      </c>
       <c r="B9" s="2">
         <v>46142</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>12</v>
+        <v>586</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>13</v>
+        <v>224</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>44</v>
+        <v>905</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>49</v>
+        <v>915</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>45</v>
+        <v>921</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>46</v>
+        <v>923</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>50</v>
+        <v>917</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>52</v>
+        <v>918</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>51</v>
+        <v>919</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>53</v>
+        <v>920</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>54</v>
+        <v>924</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>55</v>
+        <v>922</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="P9" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="10" spans="2:16" x14ac:dyDescent="0.35">
+        <v>916</v>
+      </c>
+      <c r="P9" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A10" s="1">
+        <v>8</v>
+      </c>
       <c r="B10" s="2">
         <v>46143</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="D10" s="1" t="s">
         <v>258</v>
       </c>
@@ -3749,59 +3955,65 @@
         <v>477</v>
       </c>
     </row>
-    <row r="11" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
       <c r="B11" s="2">
         <v>46144</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>12</v>
+        <v>586</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>224</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>201</v>
+        <v>910</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>228</v>
+        <v>935</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>226</v>
+        <v>932</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>227</v>
+        <v>928</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>225</v>
+        <v>929</v>
+      </c>
+      <c r="J11" t="s">
+        <v>926</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>231</v>
+        <v>933</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>230</v>
+        <v>934</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>232</v>
+        <v>930</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>233</v>
+        <v>936</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>235</v>
+        <v>931</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="12" spans="2:16" x14ac:dyDescent="0.35">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A12" s="1">
+        <v>10</v>
+      </c>
       <c r="B12" s="2">
         <v>46145</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>12</v>
+        <v>586</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>13</v>
@@ -3843,12 +4055,15 @@
         <v>610</v>
       </c>
     </row>
-    <row r="13" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A13" s="1">
+        <v>11</v>
+      </c>
       <c r="B13" s="2">
         <v>46146</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>12</v>
+        <v>586</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>224</v>
@@ -3890,12 +4105,15 @@
         <v>670</v>
       </c>
     </row>
-    <row r="14" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A14" s="1">
+        <v>12</v>
+      </c>
       <c r="B14" s="2">
         <v>46147</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>12</v>
+        <v>586</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>224</v>
@@ -3937,12 +4155,15 @@
         <v>646</v>
       </c>
     </row>
-    <row r="15" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A15" s="1">
+        <v>13</v>
+      </c>
       <c r="B15" s="2">
         <v>46148</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>12</v>
+        <v>586</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>224</v>
@@ -3984,12 +4205,15 @@
         <v>742</v>
       </c>
     </row>
-    <row r="16" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A16" s="1">
+        <v>14</v>
+      </c>
       <c r="B16" s="2">
         <v>46149</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>12</v>
+        <v>586</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>224</v>
@@ -4031,7 +4255,10 @@
         <v>706</v>
       </c>
     </row>
-    <row r="17" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A17" s="1">
+        <v>15</v>
+      </c>
       <c r="B17" s="2">
         <v>46150</v>
       </c>
@@ -4078,12 +4305,15 @@
         <v>528</v>
       </c>
     </row>
-    <row r="18" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A18" s="1">
+        <v>16</v>
+      </c>
       <c r="B18" s="2">
         <v>46151</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>12</v>
+        <v>586</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>224</v>
@@ -4125,106 +4355,115 @@
         <v>635</v>
       </c>
     </row>
-    <row r="19" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="1">
+        <v>17</v>
+      </c>
       <c r="B19" s="2">
         <v>46152</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>12</v>
+        <v>586</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>216</v>
+        <v>925</v>
+      </c>
+      <c r="F19" t="s">
+        <v>937</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>214</v>
+        <v>943</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>215</v>
+        <v>939</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>213</v>
+        <v>941</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>217</v>
+        <v>945</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>220</v>
+        <v>946</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>221</v>
+        <v>947</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>222</v>
+        <v>944</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>223</v>
+        <v>938</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>218</v>
+        <v>940</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="20" spans="2:16" x14ac:dyDescent="0.35">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" s="9" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="1">
+        <v>18</v>
+      </c>
       <c r="B20" s="2">
         <v>46153</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>12</v>
+        <v>586</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>13</v>
+        <v>224</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>133</v>
+        <v>594</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>134</v>
+        <v>784</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>135</v>
+        <v>782</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>136</v>
+        <v>779</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>137</v>
+        <v>780</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>141</v>
+        <v>783</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>142</v>
+        <v>785</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>143</v>
+        <v>786</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>144</v>
+        <v>781</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>140</v>
+        <v>787</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>139</v>
+        <v>777</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="21" spans="2:16" x14ac:dyDescent="0.35">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A21" s="1">
+        <v>19</v>
+      </c>
       <c r="B21" s="2">
         <v>46154</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>12</v>
+        <v>586</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>224</v>
@@ -4266,12 +4505,15 @@
         <v>624</v>
       </c>
     </row>
-    <row r="22" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A22" s="1">
+        <v>20</v>
+      </c>
       <c r="B22" s="2">
         <v>46155</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>12</v>
+        <v>584</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>166</v>
@@ -4313,12 +4555,15 @@
         <v>169</v>
       </c>
     </row>
-    <row r="23" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A23" s="1">
+        <v>21</v>
+      </c>
       <c r="B23" s="2">
         <v>46156</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>12</v>
+        <v>584</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>13</v>
@@ -4360,12 +4605,15 @@
         <v>755</v>
       </c>
     </row>
-    <row r="24" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A24" s="1">
+        <v>22</v>
+      </c>
       <c r="B24" s="2">
         <v>46157</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>12</v>
+        <v>584</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>224</v>
@@ -4407,12 +4655,15 @@
         <v>767</v>
       </c>
     </row>
-    <row r="25" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A25" s="1">
+        <v>23</v>
+      </c>
       <c r="B25" s="2">
         <v>46158</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>12</v>
+        <v>584</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>583</v>
@@ -4454,7 +4705,10 @@
         <v>748</v>
       </c>
     </row>
-    <row r="26" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A26" s="1">
+        <v>24</v>
+      </c>
       <c r="B26" s="2">
         <v>46159</v>
       </c>
@@ -4501,7 +4755,10 @@
         <v>539</v>
       </c>
     </row>
-    <row r="27" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A27" s="1">
+        <v>25</v>
+      </c>
       <c r="B27" s="2">
         <v>46160</v>
       </c>
@@ -4548,54 +4805,60 @@
         <v>239</v>
       </c>
     </row>
-    <row r="28" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B28" s="2">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A28" s="1">
+        <v>26</v>
+      </c>
+      <c r="B28" s="8">
         <v>46161</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D28" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>594</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>784</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>782</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>779</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>780</v>
-      </c>
-      <c r="J28" s="1" t="s">
-        <v>783</v>
-      </c>
-      <c r="K28" s="1" t="s">
-        <v>785</v>
-      </c>
-      <c r="L28" s="1" t="s">
-        <v>786</v>
-      </c>
-      <c r="M28" s="1" t="s">
-        <v>781</v>
-      </c>
-      <c r="N28" s="1" t="s">
-        <v>787</v>
-      </c>
-      <c r="O28" s="1" t="s">
-        <v>777</v>
-      </c>
-      <c r="P28" s="1" t="s">
-        <v>778</v>
-      </c>
-    </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="D28" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="I28" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="J28" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="K28" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="L28" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="M28" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="N28" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="O28" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="P28" s="9" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A29" s="1">
+        <v>27</v>
+      </c>
       <c r="B29" s="2">
         <v>46162</v>
       </c>
@@ -4642,7 +4905,10 @@
         <v>466</v>
       </c>
     </row>
-    <row r="30" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A30" s="1">
+        <v>28</v>
+      </c>
       <c r="B30" s="2">
         <v>46163</v>
       </c>
@@ -4689,12 +4955,15 @@
         <v>832</v>
       </c>
     </row>
-    <row r="31" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A31" s="1">
+        <v>29</v>
+      </c>
       <c r="B31" s="2">
         <v>46164</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>12</v>
+        <v>586</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>13</v>
@@ -4736,12 +5005,15 @@
         <v>601</v>
       </c>
     </row>
-    <row r="32" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A32" s="1">
+        <v>30</v>
+      </c>
       <c r="B32" s="2">
         <v>46165</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>12</v>
+        <v>586</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>13</v>
@@ -4783,7 +5055,10 @@
         <v>852</v>
       </c>
     </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A33" s="1">
+        <v>31</v>
+      </c>
       <c r="B33" s="2">
         <v>46166</v>
       </c>
@@ -4830,12 +5105,15 @@
         <v>751</v>
       </c>
     </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A34" s="1">
+        <v>32</v>
+      </c>
       <c r="B34" s="2">
         <v>46167</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>12</v>
+        <v>586</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>224</v>
@@ -4877,18 +5155,21 @@
         <v>797</v>
       </c>
     </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A35" s="1">
+        <v>33</v>
+      </c>
       <c r="B35" s="2">
         <v>46168</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>12</v>
+        <v>586</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>224</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>586</v>
+        <v>901</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>289</v>
@@ -4924,12 +5205,15 @@
         <v>297</v>
       </c>
     </row>
-    <row r="36" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A36" s="1">
+        <v>34</v>
+      </c>
       <c r="B36" s="2">
         <v>46169</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>12</v>
+        <v>902</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>13</v>
@@ -4971,18 +5255,21 @@
         <v>553</v>
       </c>
     </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A37" s="1">
+        <v>35</v>
+      </c>
       <c r="B37" s="2">
         <v>46170</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>12</v>
+        <v>586</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>224</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>586</v>
+        <v>901</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>290</v>
@@ -5018,12 +5305,15 @@
         <v>295</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A38" s="1">
+        <v>36</v>
+      </c>
       <c r="B38" s="2">
         <v>46171</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>12</v>
+        <v>902</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>13</v>
@@ -5065,12 +5355,15 @@
         <v>546</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A39" s="1">
+        <v>37</v>
+      </c>
       <c r="B39" s="2">
         <v>46172</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>12</v>
+        <v>902</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>166</v>
@@ -5112,13 +5405,13 @@
         <v>180</v>
       </c>
     </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A40" s="1">
+        <v>38</v>
+      </c>
       <c r="B40" s="2">
         <v>46173</v>
       </c>
-      <c r="C40" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="D40" s="1" t="s">
         <v>258</v>
       </c>
@@ -5159,12 +5452,15 @@
         <v>484</v>
       </c>
     </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A41" s="1">
+        <v>39</v>
+      </c>
       <c r="B41" s="2">
         <v>46174</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>12</v>
+        <v>586</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>224</v>
@@ -5206,12 +5502,15 @@
         <v>662</v>
       </c>
     </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A42" s="1">
+        <v>40</v>
+      </c>
       <c r="B42" s="2">
         <v>46175</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>12</v>
+        <v>586</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>13</v>
@@ -5253,12 +5552,15 @@
         <v>865</v>
       </c>
     </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A43" s="1">
+        <v>41</v>
+      </c>
       <c r="B43" s="2">
         <v>46176</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>12</v>
+        <v>586</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>13</v>
@@ -5300,18 +5602,21 @@
         <v>900</v>
       </c>
     </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A44" s="1">
+        <v>42</v>
+      </c>
       <c r="B44" s="2">
         <v>46177</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>12</v>
+        <v>586</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>224</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>586</v>
+        <v>901</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>325</v>
@@ -5347,7 +5652,10 @@
         <v>335</v>
       </c>
     </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A45" s="1">
+        <v>43</v>
+      </c>
       <c r="B45" s="2">
         <v>46178</v>
       </c>
@@ -5394,18 +5702,21 @@
         <v>164</v>
       </c>
     </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A46" s="1">
+        <v>44</v>
+      </c>
       <c r="B46" s="2">
         <v>46179</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>12</v>
+        <v>586</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>586</v>
+        <v>247</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>502</v>
@@ -5441,12 +5752,15 @@
         <v>254</v>
       </c>
     </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A47" s="1">
+        <v>45</v>
+      </c>
       <c r="B47" s="2">
         <v>46180</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>12</v>
+        <v>586</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>224</v>
@@ -5488,12 +5802,15 @@
         <v>813</v>
       </c>
     </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A48" s="1">
+        <v>46</v>
+      </c>
       <c r="B48" s="2">
         <v>46181</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>12</v>
+        <v>586</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>224</v>
@@ -5535,18 +5852,21 @@
         <v>354</v>
       </c>
     </row>
-    <row r="49" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A49" s="1">
+        <v>47</v>
+      </c>
       <c r="B49" s="2">
         <v>46182</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>12</v>
+        <v>586</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>586</v>
+        <v>247</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>510</v>
@@ -5582,12 +5902,15 @@
         <v>517</v>
       </c>
     </row>
-    <row r="50" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A50" s="1">
+        <v>48</v>
+      </c>
       <c r="B50" s="2">
         <v>46183</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>12</v>
+        <v>586</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>13</v>
@@ -5629,12 +5952,15 @@
         <v>874</v>
       </c>
     </row>
-    <row r="51" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A51" s="1">
+        <v>49</v>
+      </c>
       <c r="B51" s="2">
         <v>46184</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>12</v>
+        <v>247</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>224</v>
@@ -5676,12 +6002,15 @@
         <v>365</v>
       </c>
     </row>
-    <row r="52" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A52" s="1">
+        <v>50</v>
+      </c>
       <c r="B52" s="2">
         <v>46185</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>12</v>
+        <v>247</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>224</v>
@@ -5723,283 +6052,867 @@
         <v>303</v>
       </c>
     </row>
-    <row r="53" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B53" s="2"/>
-    </row>
-    <row r="54" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B54" s="2"/>
-    </row>
-    <row r="55" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B55" s="2"/>
-    </row>
-    <row r="56" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B56" s="2"/>
-    </row>
-    <row r="57" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B57" s="2"/>
-    </row>
-    <row r="58" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B58" s="2"/>
-    </row>
-    <row r="59" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B59" s="2"/>
-    </row>
-    <row r="60" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B60" s="2"/>
-    </row>
-    <row r="61" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B61" s="2"/>
-    </row>
-    <row r="62" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B62" s="2"/>
-    </row>
-    <row r="63" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B63" s="2"/>
-    </row>
-    <row r="64" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B64" s="2"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B65" s="2"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A53" s="1">
+        <v>51</v>
+      </c>
+      <c r="B53" s="2">
+        <v>46186</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="J53" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="K53" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="L53" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="M53" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="N53" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="O53" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="P53" s="1" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A54" s="1">
+        <v>52</v>
+      </c>
+      <c r="B54" s="2">
+        <v>46187</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="J54" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="L54" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="M54" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="N54" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="O54" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="P54" s="1" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A55" s="1">
+        <v>53</v>
+      </c>
+      <c r="B55" s="2">
+        <v>46188</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>804</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>806</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>801</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>799</v>
+      </c>
+      <c r="J55" s="1" t="s">
+        <v>807</v>
+      </c>
+      <c r="K55" s="1" t="s">
+        <v>805</v>
+      </c>
+      <c r="L55" s="1" t="s">
+        <v>800</v>
+      </c>
+      <c r="M55" s="1" t="s">
+        <v>802</v>
+      </c>
+      <c r="N55" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="O55" s="1" t="s">
+        <v>809</v>
+      </c>
+      <c r="P55" s="1" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A56" s="1">
+        <v>54</v>
+      </c>
+      <c r="B56" s="2">
+        <v>46188</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="J56" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="K56" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="L56" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="M56" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="N56" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="O56" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="P56" s="1" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A57" s="1">
+        <v>55</v>
+      </c>
+      <c r="B57" s="2">
+        <v>46189</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="J57" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="K57" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="L57" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="M57" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="N57" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="O57" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="P57" s="1" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A58" s="1">
+        <v>56</v>
+      </c>
+      <c r="B58" s="2">
+        <v>46190</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>845</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="J58" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="K58" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="L58" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="M58" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="N58" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="O58" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="P58" s="1" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A59" s="1">
+        <v>57</v>
+      </c>
+      <c r="B59" s="2">
+        <v>46191</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="J59" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="K59" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="L59" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="M59" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="N59" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="O59" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="P59" s="1" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A60" s="1">
+        <v>58</v>
+      </c>
+      <c r="B60" s="2">
+        <v>46192</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="J60" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="K60" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="L60" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="M60" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="N60" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="O60" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="P60" s="1" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A61" s="1">
+        <v>59</v>
+      </c>
+      <c r="B61" s="2">
+        <v>46193</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="J61" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="K61" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="L61" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="M61" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="N61" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="O61" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="P61" s="1" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A62" s="1">
+        <v>60</v>
+      </c>
+      <c r="B62" s="2">
+        <v>46194</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="I62" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="J62" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="K62" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="L62" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="M62" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="N62" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="O62" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="P62" s="1" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A63" s="1">
+        <v>61</v>
+      </c>
+      <c r="B63" s="2">
+        <v>46195</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="J63" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="K63" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="L63" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="M63" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="N63" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="O63" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="P63" s="1" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A64" s="1">
+        <v>62</v>
+      </c>
+      <c r="B64" s="2">
+        <v>46196</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="J64" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="K64" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="L64" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="M64" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="N64" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="O64" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="P64" s="1" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A65" s="1">
+        <v>63</v>
+      </c>
+      <c r="B65" s="2">
+        <v>46197</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="I65" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="J65" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="K65" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="L65" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="M65" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="N65" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="O65" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="P65" s="1" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A66" s="1">
+        <v>64</v>
+      </c>
       <c r="B66" s="2">
-        <v>46186</v>
+        <v>46198</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>247</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>13</v>
+        <v>224</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="J66" s="1" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="M66" s="1" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="N66" s="1" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="O66" s="1" t="s">
-        <v>391</v>
+        <v>401</v>
       </c>
       <c r="P66" s="1" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.35">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A67" s="1">
+        <v>65</v>
+      </c>
       <c r="B67" s="2">
-        <v>46187</v>
+        <v>46200</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>247</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>224</v>
+        <v>13</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>559</v>
+        <v>391</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>560</v>
+        <v>391</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>561</v>
+        <v>391</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>562</v>
+        <v>391</v>
       </c>
       <c r="J67" s="1" t="s">
-        <v>563</v>
+        <v>391</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>564</v>
+        <v>391</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>565</v>
+        <v>391</v>
       </c>
       <c r="M67" s="1" t="s">
-        <v>566</v>
+        <v>391</v>
       </c>
       <c r="N67" s="1" t="s">
-        <v>555</v>
+        <v>391</v>
       </c>
       <c r="O67" s="1" t="s">
-        <v>567</v>
+        <v>391</v>
       </c>
       <c r="P67" s="1" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.35">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A68" s="1">
+        <v>66</v>
+      </c>
       <c r="B68" s="2">
-        <v>46188</v>
+        <v>46201</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>247</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>224</v>
+        <v>13</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>804</v>
+        <v>391</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>806</v>
+        <v>391</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>801</v>
+        <v>391</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>799</v>
+        <v>391</v>
       </c>
       <c r="J68" s="1" t="s">
-        <v>807</v>
+        <v>391</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>805</v>
+        <v>391</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>800</v>
+        <v>391</v>
       </c>
       <c r="M68" s="1" t="s">
-        <v>802</v>
+        <v>391</v>
       </c>
       <c r="N68" s="1" t="s">
-        <v>803</v>
+        <v>391</v>
       </c>
       <c r="O68" s="1" t="s">
-        <v>809</v>
+        <v>391</v>
       </c>
       <c r="P68" s="1" t="s">
-        <v>808</v>
-      </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.35">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A69" s="1">
+        <v>67</v>
+      </c>
       <c r="B69" s="2">
-        <v>46188</v>
+        <v>46202</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>247</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>224</v>
+        <v>13</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>310</v>
+        <v>391</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>411</v>
+        <v>391</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>412</v>
+        <v>391</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>413</v>
+        <v>391</v>
       </c>
       <c r="J69" s="1" t="s">
-        <v>414</v>
+        <v>391</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>415</v>
+        <v>391</v>
       </c>
       <c r="L69" s="1" t="s">
-        <v>416</v>
+        <v>391</v>
       </c>
       <c r="M69" s="1" t="s">
-        <v>417</v>
+        <v>391</v>
       </c>
       <c r="N69" s="1" t="s">
-        <v>418</v>
+        <v>391</v>
       </c>
       <c r="O69" s="1" t="s">
-        <v>419</v>
+        <v>391</v>
       </c>
       <c r="P69" s="1" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.35">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A70" s="1">
+        <v>68</v>
+      </c>
       <c r="B70" s="2">
-        <v>46189</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="F70" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="G70" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="H70" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="I70" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="J70" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="K70" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="L70" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="M70" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="N70" s="1" t="s">
-        <v>435</v>
-      </c>
-      <c r="O70" s="1" t="s">
-        <v>436</v>
-      </c>
-      <c r="P70" s="1" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.35">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B71" s="2">
-        <v>46190</v>
+        <v>46204</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>247</v>
@@ -6008,186 +6921,186 @@
         <v>224</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>845</v>
+        <v>568</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>454</v>
+        <v>569</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>576</v>
+        <v>353</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>577</v>
+        <v>570</v>
       </c>
       <c r="J71" s="1" t="s">
-        <v>578</v>
+        <v>571</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>579</v>
+        <v>572</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>580</v>
+        <v>558</v>
       </c>
       <c r="M71" s="1" t="s">
-        <v>455</v>
+        <v>573</v>
       </c>
       <c r="N71" s="1" t="s">
-        <v>314</v>
+        <v>556</v>
       </c>
       <c r="O71" s="1" t="s">
-        <v>581</v>
+        <v>557</v>
       </c>
       <c r="P71" s="1" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.35">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B72" s="2">
-        <v>46191</v>
+        <v>46205</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>247</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>224</v>
+        <v>13</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>444</v>
+        <v>391</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>445</v>
+        <v>391</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>446</v>
+        <v>391</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>313</v>
+        <v>391</v>
       </c>
       <c r="J72" s="1" t="s">
-        <v>447</v>
+        <v>391</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>448</v>
+        <v>391</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>449</v>
+        <v>391</v>
       </c>
       <c r="M72" s="1" t="s">
-        <v>450</v>
+        <v>391</v>
       </c>
       <c r="N72" s="1" t="s">
-        <v>451</v>
+        <v>391</v>
       </c>
       <c r="O72" s="1" t="s">
-        <v>452</v>
+        <v>391</v>
       </c>
       <c r="P72" s="1" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.35">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B73" s="2">
-        <v>46192</v>
+        <v>46206</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>247</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>13</v>
+        <v>224</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>391</v>
+        <v>438</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>391</v>
+        <v>317</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>391</v>
+        <v>337</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>391</v>
+        <v>439</v>
       </c>
       <c r="J73" s="1" t="s">
-        <v>391</v>
+        <v>440</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>391</v>
+        <v>441</v>
       </c>
       <c r="L73" s="1" t="s">
-        <v>391</v>
+        <v>319</v>
       </c>
       <c r="M73" s="1" t="s">
-        <v>391</v>
+        <v>320</v>
       </c>
       <c r="N73" s="1" t="s">
-        <v>391</v>
+        <v>442</v>
       </c>
       <c r="O73" s="1" t="s">
-        <v>391</v>
+        <v>443</v>
       </c>
       <c r="P73" s="1" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.35">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B74" s="2">
-        <v>46193</v>
+        <v>46207</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>247</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>224</v>
+        <v>13</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>403</v>
+        <v>391</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>404</v>
+        <v>391</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>405</v>
+        <v>391</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>351</v>
+        <v>391</v>
       </c>
       <c r="J74" s="1" t="s">
-        <v>406</v>
+        <v>391</v>
       </c>
       <c r="K74" s="1" t="s">
-        <v>407</v>
+        <v>391</v>
       </c>
       <c r="L74" s="1" t="s">
-        <v>307</v>
+        <v>391</v>
       </c>
       <c r="M74" s="1" t="s">
-        <v>408</v>
+        <v>391</v>
       </c>
       <c r="N74" s="1" t="s">
-        <v>409</v>
+        <v>391</v>
       </c>
       <c r="O74" s="1" t="s">
-        <v>308</v>
+        <v>391</v>
       </c>
       <c r="P74" s="1" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.35">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B75" s="2">
-        <v>46194</v>
+        <v>46208</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>247</v>
@@ -6196,186 +7109,183 @@
         <v>224</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>304</v>
+        <v>375</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>420</v>
+        <v>376</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>421</v>
+        <v>377</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>422</v>
+        <v>378</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="K75" s="1" t="s">
-        <v>423</v>
+        <v>379</v>
       </c>
       <c r="L75" s="1" t="s">
-        <v>424</v>
+        <v>315</v>
       </c>
       <c r="M75" s="1" t="s">
-        <v>305</v>
+        <v>380</v>
       </c>
       <c r="N75" s="1" t="s">
-        <v>425</v>
+        <v>381</v>
       </c>
       <c r="O75" s="1" t="s">
-        <v>426</v>
+        <v>382</v>
       </c>
       <c r="P75" s="1" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.35">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B76" s="2">
-        <v>46195</v>
+        <v>46209</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>247</v>
+        <v>12</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>266</v>
+        <v>20</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>391</v>
+        <v>110</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>391</v>
+        <v>111</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>391</v>
+        <v>112</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>391</v>
+        <v>113</v>
       </c>
       <c r="J76" s="1" t="s">
-        <v>391</v>
+        <v>114</v>
       </c>
       <c r="K76" s="1" t="s">
-        <v>391</v>
+        <v>115</v>
       </c>
       <c r="L76" s="1" t="s">
-        <v>391</v>
+        <v>118</v>
       </c>
       <c r="M76" s="1" t="s">
-        <v>391</v>
+        <v>120</v>
       </c>
       <c r="N76" s="1" t="s">
-        <v>391</v>
+        <v>119</v>
       </c>
       <c r="O76" s="1" t="s">
-        <v>391</v>
+        <v>116</v>
       </c>
       <c r="P76" s="1" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.35">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B77" s="2">
-        <v>46196</v>
+        <v>46210</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>247</v>
+        <v>12</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>224</v>
+        <v>13</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>278</v>
+        <v>19</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>391</v>
+        <v>33</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>391</v>
+        <v>34</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>391</v>
+        <v>35</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>391</v>
+        <v>37</v>
       </c>
       <c r="J77" s="1" t="s">
-        <v>391</v>
+        <v>38</v>
       </c>
       <c r="K77" s="1" t="s">
-        <v>391</v>
+        <v>39</v>
       </c>
       <c r="L77" s="1" t="s">
-        <v>391</v>
+        <v>40</v>
       </c>
       <c r="M77" s="1" t="s">
-        <v>391</v>
+        <v>41</v>
       </c>
       <c r="N77" s="1" t="s">
-        <v>391</v>
+        <v>43</v>
       </c>
       <c r="O77" s="1" t="s">
-        <v>391</v>
+        <v>36</v>
       </c>
       <c r="P77" s="1" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="78" spans="2:16" x14ac:dyDescent="0.35">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B78" s="2">
-        <v>46197</v>
+        <v>46211</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>247</v>
+        <v>187</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="E78" s="1" t="s">
-        <v>271</v>
-      </c>
       <c r="F78" s="1" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>321</v>
+        <v>391</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>322</v>
+        <v>391</v>
       </c>
       <c r="J78" s="1" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="K78" s="1" t="s">
-        <v>323</v>
+        <v>391</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>324</v>
+        <v>391</v>
       </c>
       <c r="M78" s="1" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="N78" s="1" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="O78" s="1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="P78" s="1" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.35">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B79" s="2">
-        <v>46198</v>
+        <v>46212</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>247</v>
@@ -6384,426 +7294,465 @@
         <v>224</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="J79" s="1" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="K79" s="1" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="L79" s="1" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="M79" s="1" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="N79" s="1" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="O79" s="1" t="s">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="P79" s="1" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.35">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B80" s="2">
-        <v>46200</v>
+        <v>46213</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>247</v>
+        <v>12</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>274</v>
+        <v>16</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>391</v>
+        <v>56</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>391</v>
+        <v>485</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>391</v>
+        <v>57</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>391</v>
+        <v>58</v>
       </c>
       <c r="J80" s="1" t="s">
-        <v>391</v>
+        <v>64</v>
       </c>
       <c r="K80" s="1" t="s">
-        <v>391</v>
+        <v>59</v>
       </c>
       <c r="L80" s="1" t="s">
-        <v>391</v>
+        <v>60</v>
       </c>
       <c r="M80" s="1" t="s">
-        <v>391</v>
+        <v>61</v>
       </c>
       <c r="N80" s="1" t="s">
-        <v>391</v>
+        <v>63</v>
       </c>
       <c r="O80" s="1" t="s">
-        <v>391</v>
+        <v>62</v>
       </c>
       <c r="P80" s="1" t="s">
-        <v>391</v>
+        <v>486</v>
       </c>
     </row>
     <row r="81" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B81" s="2">
-        <v>46201</v>
+        <v>46214</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>247</v>
+        <v>12</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>278</v>
+        <v>18</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>391</v>
+        <v>88</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>391</v>
+        <v>94</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>391</v>
+        <v>90</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>391</v>
+        <v>91</v>
       </c>
       <c r="J81" s="1" t="s">
-        <v>391</v>
+        <v>92</v>
       </c>
       <c r="K81" s="1" t="s">
-        <v>391</v>
+        <v>93</v>
       </c>
       <c r="L81" s="1" t="s">
-        <v>391</v>
+        <v>95</v>
       </c>
       <c r="M81" s="1" t="s">
-        <v>391</v>
+        <v>89</v>
       </c>
       <c r="N81" s="1" t="s">
-        <v>391</v>
+        <v>98</v>
       </c>
       <c r="O81" s="1" t="s">
-        <v>391</v>
+        <v>97</v>
       </c>
       <c r="P81" s="1" t="s">
-        <v>391</v>
+        <v>96</v>
       </c>
     </row>
     <row r="82" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B82" s="2">
-        <v>46202</v>
+        <v>46215</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>247</v>
+        <v>12</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>272</v>
+        <v>76</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>391</v>
+        <v>77</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>391</v>
+        <v>84</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>391</v>
+        <v>82</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>391</v>
+        <v>83</v>
       </c>
       <c r="J82" s="1" t="s">
-        <v>391</v>
+        <v>81</v>
       </c>
       <c r="K82" s="1" t="s">
-        <v>391</v>
+        <v>87</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>391</v>
+        <v>80</v>
       </c>
       <c r="M82" s="1" t="s">
-        <v>391</v>
+        <v>85</v>
       </c>
       <c r="N82" s="1" t="s">
-        <v>391</v>
+        <v>86</v>
       </c>
       <c r="O82" s="1" t="s">
-        <v>391</v>
+        <v>78</v>
       </c>
       <c r="P82" s="1" t="s">
-        <v>391</v>
+        <v>79</v>
       </c>
     </row>
     <row r="83" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B83" s="2">
-        <v>46203</v>
+        <v>46216</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="I83" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="J83" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="K83" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="L83" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="M83" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="N83" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="O83" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="P83" s="1" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="84" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B84" s="2">
-        <v>46204</v>
+        <v>46217</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>247</v>
+        <v>12</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>224</v>
+        <v>13</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>267</v>
+        <v>21</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>568</v>
+        <v>99</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>569</v>
+        <v>100</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>353</v>
+        <v>101</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>570</v>
+        <v>105</v>
       </c>
       <c r="J84" s="1" t="s">
-        <v>571</v>
+        <v>104</v>
       </c>
       <c r="K84" s="1" t="s">
-        <v>572</v>
+        <v>106</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>558</v>
+        <v>107</v>
       </c>
       <c r="M84" s="1" t="s">
-        <v>573</v>
+        <v>109</v>
       </c>
       <c r="N84" s="1" t="s">
-        <v>556</v>
+        <v>108</v>
       </c>
       <c r="O84" s="1" t="s">
-        <v>557</v>
+        <v>102</v>
       </c>
       <c r="P84" s="1" t="s">
-        <v>574</v>
+        <v>103</v>
       </c>
     </row>
     <row r="85" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B85" s="2">
-        <v>46205</v>
+        <v>46219</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>247</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>13</v>
+        <v>224</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>276</v>
+        <v>586</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>391</v>
+        <v>336</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>391</v>
+        <v>337</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>391</v>
+        <v>338</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>391</v>
+        <v>339</v>
       </c>
       <c r="J85" s="1" t="s">
-        <v>391</v>
+        <v>340</v>
       </c>
       <c r="K85" s="1" t="s">
-        <v>391</v>
+        <v>341</v>
       </c>
       <c r="L85" s="1" t="s">
-        <v>391</v>
+        <v>342</v>
       </c>
       <c r="M85" s="1" t="s">
-        <v>391</v>
+        <v>343</v>
       </c>
       <c r="N85" s="1" t="s">
-        <v>391</v>
+        <v>344</v>
       </c>
       <c r="O85" s="1" t="s">
-        <v>391</v>
+        <v>345</v>
       </c>
       <c r="P85" s="1" t="s">
-        <v>391</v>
+        <v>346</v>
       </c>
     </row>
     <row r="86" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B86" s="2">
-        <v>46206</v>
+        <v>46220</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>247</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>224</v>
+        <v>13</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>266</v>
+        <v>586</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>438</v>
+        <v>492</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>317</v>
+        <v>493</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>337</v>
+        <v>494</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>439</v>
+        <v>252</v>
       </c>
       <c r="J86" s="1" t="s">
-        <v>440</v>
+        <v>495</v>
       </c>
       <c r="K86" s="1" t="s">
-        <v>441</v>
+        <v>496</v>
       </c>
       <c r="L86" s="1" t="s">
-        <v>319</v>
+        <v>497</v>
       </c>
       <c r="M86" s="1" t="s">
-        <v>320</v>
+        <v>498</v>
       </c>
       <c r="N86" s="1" t="s">
-        <v>442</v>
+        <v>499</v>
       </c>
       <c r="O86" s="1" t="s">
-        <v>443</v>
+        <v>500</v>
       </c>
       <c r="P86" s="1" t="s">
-        <v>318</v>
+        <v>501</v>
       </c>
     </row>
     <row r="87" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B87" s="2">
-        <v>46207</v>
+        <v>46221</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>247</v>
+        <v>12</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>267</v>
+        <v>15</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>391</v>
+        <v>66</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>391</v>
+        <v>67</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>391</v>
+        <v>68</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>391</v>
+        <v>69</v>
       </c>
       <c r="J87" s="1" t="s">
-        <v>391</v>
+        <v>73</v>
       </c>
       <c r="K87" s="1" t="s">
-        <v>391</v>
+        <v>74</v>
       </c>
       <c r="L87" s="1" t="s">
-        <v>391</v>
+        <v>70</v>
       </c>
       <c r="M87" s="1" t="s">
-        <v>391</v>
+        <v>71</v>
       </c>
       <c r="N87" s="1" t="s">
-        <v>391</v>
+        <v>75</v>
       </c>
       <c r="O87" s="1" t="s">
-        <v>391</v>
+        <v>72</v>
       </c>
       <c r="P87" s="1" t="s">
-        <v>391</v>
+        <v>65</v>
       </c>
     </row>
     <row r="88" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B88" s="2">
-        <v>46208</v>
+        <v>46222</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>247</v>
+        <v>187</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>224</v>
+        <v>710</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>265</v>
+        <v>188</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>375</v>
+        <v>189</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>376</v>
+        <v>190</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>377</v>
+        <v>191</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>378</v>
+        <v>192</v>
       </c>
       <c r="J88" s="1" t="s">
-        <v>316</v>
+        <v>193</v>
       </c>
       <c r="K88" s="1" t="s">
-        <v>379</v>
+        <v>194</v>
       </c>
       <c r="L88" s="1" t="s">
-        <v>315</v>
+        <v>198</v>
       </c>
       <c r="M88" s="1" t="s">
-        <v>380</v>
+        <v>199</v>
       </c>
       <c r="N88" s="1" t="s">
-        <v>381</v>
+        <v>197</v>
       </c>
       <c r="O88" s="1" t="s">
-        <v>382</v>
+        <v>195</v>
       </c>
       <c r="P88" s="1" t="s">
-        <v>383</v>
+        <v>196</v>
       </c>
     </row>
     <row r="89" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B89" s="2">
-        <v>46209</v>
+        <v>46223</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>12</v>
@@ -6812,740 +7761,333 @@
         <v>13</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>20</v>
+        <v>121</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="J89" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="K89" s="1" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="M89" s="1" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="N89" s="1" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="O89" s="1" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="P89" s="1" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="90" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B90" s="2">
-        <v>46210</v>
+        <v>46224</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>12</v>
+        <v>586</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F90" s="1" t="s">
-        <v>33</v>
+        <v>591</v>
+      </c>
+      <c r="F90" t="s">
+        <v>879</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>34</v>
+        <v>881</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>35</v>
+        <v>880</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>37</v>
+        <v>882</v>
       </c>
       <c r="J90" s="1" t="s">
-        <v>38</v>
+        <v>884</v>
       </c>
       <c r="K90" s="1" t="s">
-        <v>39</v>
+        <v>883</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>40</v>
+        <v>886</v>
       </c>
       <c r="M90" s="1" t="s">
-        <v>41</v>
+        <v>887</v>
       </c>
       <c r="N90" s="1" t="s">
-        <v>43</v>
+        <v>888</v>
       </c>
       <c r="O90" s="1" t="s">
-        <v>36</v>
+        <v>885</v>
       </c>
       <c r="P90" s="1" t="s">
-        <v>42</v>
+        <v>889</v>
       </c>
     </row>
     <row r="91" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B91" s="2">
-        <v>46211</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="D91" s="1" t="s">
+      <c r="B91" s="8"/>
+      <c r="C91" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D91" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E91" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="F91" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="G91" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="H91" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="I91" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="J91" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="K91" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="L91" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="M91" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="N91" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="O91" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="P91" s="9" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="92" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B92" s="8"/>
+      <c r="C92" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D92" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E92" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="F92" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="G92" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="H92" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="I92" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="J92" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="K92" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="L92" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="M92" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="N92" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="O92" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="P92" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="93" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B93" s="8"/>
+      <c r="C93" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D93" s="9" t="s">
         <v>224</v>
       </c>
-      <c r="F91" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="G91" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="H91" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="I91" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="J91" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="K91" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="L91" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="M91" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="N91" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="O91" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="P91" s="1" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="92" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B92" s="2">
-        <v>46212</v>
-      </c>
-      <c r="C92" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="E92" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="F92" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="G92" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="H92" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="I92" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="J92" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="K92" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="L92" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="M92" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="N92" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="O92" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="P92" s="1" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="93" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B93" s="2">
-        <v>46213</v>
-      </c>
-      <c r="C93" s="1" t="s">
+      <c r="E93" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="F93" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="G93" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="H93" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="I93" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="J93" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="K93" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="L93" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="M93" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="N93" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="O93" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="P93" s="9" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="94" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B94" s="8"/>
+      <c r="C94" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D93" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E93" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F93" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="G93" s="1" t="s">
-        <v>485</v>
-      </c>
-      <c r="H93" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I93" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="J93" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="K93" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="L93" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="M93" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="N93" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="O93" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="P93" s="1" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="94" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B94" s="2">
-        <v>46214</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E94" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F94" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="G94" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="H94" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="I94" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="J94" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="K94" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="L94" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="M94" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="N94" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="O94" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="P94" s="1" t="s">
-        <v>96</v>
+      <c r="D94" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="E94" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="F94" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="G94" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="H94" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="I94" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="J94" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="K94" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="L94" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="M94" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="N94" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="O94" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="P94" s="9" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="95" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B95" s="2">
-        <v>46215</v>
-      </c>
+      <c r="B95" s="2"/>
       <c r="C95" s="1" t="s">
-        <v>12</v>
+        <v>586</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F95" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="G95" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="H95" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="I95" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="J95" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="K95" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="L95" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="M95" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="N95" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="O95" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="P95" s="1" t="s">
-        <v>79</v>
+        <v>589</v>
       </c>
     </row>
     <row r="96" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B96" s="2">
-        <v>46216</v>
-      </c>
       <c r="C96" s="1" t="s">
-        <v>187</v>
+        <v>586</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F96" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="G96" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="H96" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="I96" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="J96" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="K96" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="L96" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="M96" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="N96" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="O96" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="P96" s="1" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="97" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B97" s="2">
-        <v>46217</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F97" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="G97" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="H97" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="I97" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="J97" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="K97" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="L97" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="M97" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="N97" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="O97" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="P97" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="98" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B98" s="2">
-        <v>46219</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="E98" s="1" t="s">
-        <v>586</v>
-      </c>
-      <c r="F98" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="G98" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="H98" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="I98" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="J98" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="K98" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="L98" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="M98" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="N98" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="O98" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="P98" s="1" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="99" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B99" s="2">
-        <v>46220</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E99" s="1" t="s">
-        <v>586</v>
-      </c>
-      <c r="F99" s="1" t="s">
-        <v>492</v>
-      </c>
-      <c r="G99" s="1" t="s">
-        <v>493</v>
-      </c>
-      <c r="H99" s="1" t="s">
-        <v>494</v>
-      </c>
-      <c r="I99" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="J99" s="1" t="s">
-        <v>495</v>
-      </c>
-      <c r="K99" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="L99" s="1" t="s">
-        <v>497</v>
-      </c>
-      <c r="M99" s="1" t="s">
-        <v>498</v>
-      </c>
-      <c r="N99" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="O99" s="1" t="s">
-        <v>500</v>
-      </c>
-      <c r="P99" s="1" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="100" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B100" s="2">
-        <v>46221</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E100" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F100" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="G100" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="H100" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="I100" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="J100" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="K100" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="L100" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="M100" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="N100" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="O100" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="P100" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="101" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B101" s="2">
-        <v>46222</v>
-      </c>
-      <c r="C101" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>710</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="F101" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="G101" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="H101" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="I101" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="J101" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="K101" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="L101" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="M101" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="N101" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="O101" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="P101" s="1" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="102" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B102" s="2">
-        <v>46223</v>
-      </c>
-      <c r="C102" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E102" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="F102" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="G102" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="H102" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="I102" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="J102" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="K102" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="L102" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="M102" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="N102" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="O102" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="P102" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="103" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B103" s="2">
-        <v>46224</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>586</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E103" s="1" t="s">
-        <v>591</v>
-      </c>
-      <c r="F103" t="s">
-        <v>879</v>
-      </c>
-      <c r="G103" s="1" t="s">
-        <v>881</v>
-      </c>
-      <c r="H103" s="1" t="s">
-        <v>880</v>
-      </c>
-      <c r="I103" s="1" t="s">
-        <v>882</v>
-      </c>
-      <c r="J103" s="1" t="s">
-        <v>884</v>
-      </c>
-      <c r="K103" s="1" t="s">
-        <v>883</v>
-      </c>
-      <c r="L103" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="M103" s="1" t="s">
-        <v>887</v>
-      </c>
-      <c r="N103" s="1" t="s">
-        <v>888</v>
-      </c>
-      <c r="O103" s="1" t="s">
-        <v>885</v>
-      </c>
-      <c r="P103" s="1" t="s">
-        <v>889</v>
-      </c>
-    </row>
-    <row r="104" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="E96" s="1" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="97" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B97" s="2"/>
+    </row>
+    <row r="98" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B98" s="2"/>
+    </row>
+    <row r="99" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B99" s="2"/>
+    </row>
+    <row r="100" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B100" s="2"/>
+    </row>
+    <row r="101" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B101" s="2"/>
+    </row>
+    <row r="102" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B102" s="2"/>
+    </row>
+    <row r="103" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B103" s="2"/>
+    </row>
+    <row r="104" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B104" s="2"/>
-      <c r="G104" s="6"/>
-    </row>
-    <row r="105" spans="2:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="105" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B105" s="2"/>
-      <c r="G105" s="6"/>
-    </row>
-    <row r="106" spans="2:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="106" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B106" s="2"/>
-      <c r="G106" s="6"/>
-    </row>
-    <row r="108" spans="2:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="107" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B107" s="2"/>
+      <c r="G107" s="6"/>
+    </row>
+    <row r="108" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B108" s="2"/>
-      <c r="C108" s="1" t="s">
-        <v>586</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E108" s="1" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="109" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="G108" s="6"/>
+    </row>
+    <row r="109" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B109" s="2"/>
-      <c r="C109" s="1" t="s">
-        <v>586</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E109" s="1" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="110" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="C110" s="1" t="s">
-        <v>586</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E110" s="1" t="s">
-        <v>593</v>
-      </c>
+      <c r="G109" s="6"/>
     </row>
     <row r="131" spans="3:9" x14ac:dyDescent="0.35">
       <c r="I131"/>
@@ -7795,4 +8337,67 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93CE4D0D-A89D-4343-9340-E2F37B7C8AB3}">
+  <sheetPr codeName="Sheet2"/>
+  <dimension ref="B3:D7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B3" s="7">
+        <v>46139</v>
+      </c>
+      <c r="C3" t="s">
+        <v>903</v>
+      </c>
+      <c r="D3" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B4" s="7">
+        <v>46142</v>
+      </c>
+      <c r="C4" t="s">
+        <v>906</v>
+      </c>
+      <c r="D4" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B5" s="7">
+        <v>46144</v>
+      </c>
+      <c r="C5" t="s">
+        <v>908</v>
+      </c>
+      <c r="D5" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B6" s="7">
+        <v>46152</v>
+      </c>
+      <c r="C6" t="s">
+        <v>911</v>
+      </c>
+      <c r="D6" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B7" s="7">
+        <v>46153</v>
+      </c>
+      <c r="D7" t="s">
+        <v>913</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>